--- a/data/GreatLink/US Income and Growth Fund (Dis).xlsx
+++ b/data/GreatLink/US Income and Growth Fund (Dis).xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PriceHistory" sheetId="1" r:id="GemRid591151"/>
+    <sheet name="PriceHistory" sheetId="1" r:id="GemRid918114"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="825">
   <si>
     <t>Price Date</t>
   </si>
@@ -26,27 +26,96 @@
     <t>Currency - Unit Level</t>
   </si>
   <si>
+    <t>27/02/2026</t>
+  </si>
+  <si>
+    <t>0.997</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>26/02/2026</t>
+  </si>
+  <si>
+    <t>1.004</t>
+  </si>
+  <si>
+    <t>25/02/2026</t>
+  </si>
+  <si>
+    <t>1.009</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>0.999</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>1.002</t>
+  </si>
+  <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>19/02/2026</t>
+  </si>
+  <si>
+    <t>1.007</t>
+  </si>
+  <si>
+    <t>16/02/2026</t>
+  </si>
+  <si>
+    <t>13/02/2026</t>
+  </si>
+  <si>
+    <t>12/02/2026</t>
+  </si>
+  <si>
+    <t>1.013</t>
+  </si>
+  <si>
+    <t>11/02/2026</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>09/02/2026</t>
+  </si>
+  <si>
+    <t>1.011</t>
+  </si>
+  <si>
+    <t>06/02/2026</t>
+  </si>
+  <si>
+    <t>1.003</t>
+  </si>
+  <si>
+    <t>05/02/2026</t>
+  </si>
+  <si>
+    <t>04/02/2026</t>
+  </si>
+  <si>
+    <t>03/02/2026</t>
+  </si>
+  <si>
     <t>02/02/2026</t>
   </si>
   <si>
-    <t>1.009</t>
-  </si>
-  <si>
-    <t>SGD</t>
-  </si>
-  <si>
     <t>30/01/2026</t>
   </si>
   <si>
-    <t>1.011</t>
-  </si>
-  <si>
     <t>29/01/2026</t>
   </si>
   <si>
-    <t>1.013</t>
-  </si>
-  <si>
     <t>28/01/2026</t>
   </si>
   <si>
@@ -65,9 +134,6 @@
     <t>23/01/2026</t>
   </si>
   <si>
-    <t>1.007</t>
-  </si>
-  <si>
     <t>22/01/2026</t>
   </si>
   <si>
@@ -77,15 +143,9 @@
     <t>21/01/2026</t>
   </si>
   <si>
-    <t>1.003</t>
-  </si>
-  <si>
     <t>20/01/2026</t>
   </si>
   <si>
-    <t>1.002</t>
-  </si>
-  <si>
     <t>19/01/2026</t>
   </si>
   <si>
@@ -137,9 +197,6 @@
     <t>31/12/2025</t>
   </si>
   <si>
-    <t>1.004</t>
-  </si>
-  <si>
     <t>30/12/2025</t>
   </si>
   <si>
@@ -164,9 +221,6 @@
     <t>19/12/2025</t>
   </si>
   <si>
-    <t>0.999</t>
-  </si>
-  <si>
     <t>18/12/2025</t>
   </si>
   <si>
@@ -510,9 +564,6 @@
   </si>
   <si>
     <t>04/08/2025</t>
-  </si>
-  <si>
-    <t>0.997</t>
   </si>
   <si>
     <t>01/08/2025</t>
@@ -2824,7 +2875,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -2832,10 +2883,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
         <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -2857,7 +2908,7 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -2865,10 +2916,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -2876,10 +2927,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -2887,10 +2938,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -2898,10 +2949,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -2909,10 +2960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -2920,10 +2971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -2931,10 +2982,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -2942,10 +2993,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -2953,10 +3004,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
@@ -2964,10 +3015,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -2975,10 +3026,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -2986,10 +3037,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -2997,10 +3048,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -3008,10 +3059,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -3019,10 +3070,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
@@ -3030,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
@@ -3041,10 +3092,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -3052,10 +3103,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
@@ -3063,10 +3114,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
@@ -3074,10 +3125,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -3085,10 +3136,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -3096,10 +3147,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -3107,10 +3158,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -3118,10 +3169,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -3129,10 +3180,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -3140,10 +3191,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -3151,10 +3202,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -3162,10 +3213,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -3173,10 +3224,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -3184,10 +3235,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -3195,10 +3246,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
@@ -3206,10 +3257,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
@@ -3217,10 +3268,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -3228,10 +3279,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -3239,10 +3290,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -3250,10 +3301,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -3261,10 +3312,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
@@ -3272,10 +3323,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
@@ -3283,10 +3334,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C48" t="s">
         <v>5</v>
@@ -3294,10 +3345,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>68</v>
+      </c>
+      <c r="B49" t="s">
         <v>69</v>
-      </c>
-      <c r="B49" t="s">
-        <v>70</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
@@ -3305,10 +3356,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" t="s">
         <v>71</v>
-      </c>
-      <c r="B50" t="s">
-        <v>72</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -3316,10 +3367,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B51" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -3327,10 +3378,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
@@ -3338,10 +3389,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="C53" t="s">
         <v>5</v>
@@ -3349,10 +3400,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B54" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
@@ -3360,10 +3411,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B55" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
@@ -3371,10 +3422,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
         <v>5</v>
@@ -3382,10 +3433,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
@@ -3393,10 +3444,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B58" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
@@ -3404,10 +3455,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="C59" t="s">
         <v>5</v>
@@ -3415,10 +3466,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B60" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
@@ -3426,10 +3477,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
@@ -3437,10 +3488,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B62" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
@@ -3448,10 +3499,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -3459,10 +3510,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -3470,10 +3521,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B65" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -3481,10 +3532,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B66" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -3492,10 +3543,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B67" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C67" t="s">
         <v>5</v>
@@ -3503,10 +3554,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B68" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C68" t="s">
         <v>5</v>
@@ -3514,10 +3565,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B69" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="C69" t="s">
         <v>5</v>
@@ -3525,10 +3576,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="C70" t="s">
         <v>5</v>
@@ -3536,10 +3587,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B71" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -3547,10 +3598,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B72" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="C72" t="s">
         <v>5</v>
@@ -3558,10 +3609,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B73" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="C73" t="s">
         <v>5</v>
@@ -3569,10 +3620,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B74" t="s">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="C74" t="s">
         <v>5</v>
@@ -3580,10 +3631,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="C75" t="s">
         <v>5</v>
@@ -3591,10 +3642,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B76" t="s">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="C76" t="s">
         <v>5</v>
@@ -3602,10 +3653,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B77" t="s">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="C77" t="s">
         <v>5</v>
@@ -3613,10 +3664,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C78" t="s">
         <v>5</v>
@@ -3624,10 +3675,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B79" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="C79" t="s">
         <v>5</v>
@@ -3635,10 +3686,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B80" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="C80" t="s">
         <v>5</v>
@@ -3646,10 +3697,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B81" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C81" t="s">
         <v>5</v>
@@ -3657,10 +3708,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="C82" t="s">
         <v>5</v>
@@ -3668,10 +3719,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B83" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C83" t="s">
         <v>5</v>
@@ -3679,10 +3730,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B84" t="s">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="C84" t="s">
         <v>5</v>
@@ -3690,10 +3741,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="C85" t="s">
         <v>5</v>
@@ -3701,10 +3752,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>117</v>
+      </c>
+      <c r="B86" t="s">
         <v>118</v>
-      </c>
-      <c r="B86" t="s">
-        <v>31</v>
       </c>
       <c r="C86" t="s">
         <v>5</v>
@@ -3715,7 +3766,7 @@
         <v>119</v>
       </c>
       <c r="B87" t="s">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="C87" t="s">
         <v>5</v>
@@ -3726,7 +3777,7 @@
         <v>120</v>
       </c>
       <c r="B88" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C88" t="s">
         <v>5</v>
@@ -3737,7 +3788,7 @@
         <v>121</v>
       </c>
       <c r="B89" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C89" t="s">
         <v>5</v>
@@ -3748,7 +3799,7 @@
         <v>122</v>
       </c>
       <c r="B90" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C90" t="s">
         <v>5</v>
@@ -3759,7 +3810,7 @@
         <v>123</v>
       </c>
       <c r="B91" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C91" t="s">
         <v>5</v>
@@ -3770,7 +3821,7 @@
         <v>124</v>
       </c>
       <c r="B92" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="C92" t="s">
         <v>5</v>
@@ -3781,7 +3832,7 @@
         <v>125</v>
       </c>
       <c r="B93" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="C93" t="s">
         <v>5</v>
@@ -3792,7 +3843,7 @@
         <v>126</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="C94" t="s">
         <v>5</v>
@@ -3803,7 +3854,7 @@
         <v>127</v>
       </c>
       <c r="B95" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="C95" t="s">
         <v>5</v>
@@ -3814,7 +3865,7 @@
         <v>128</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="C96" t="s">
         <v>5</v>
@@ -3825,7 +3876,7 @@
         <v>129</v>
       </c>
       <c r="B97" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="C97" t="s">
         <v>5</v>
@@ -3836,7 +3887,7 @@
         <v>130</v>
       </c>
       <c r="B98" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C98" t="s">
         <v>5</v>
@@ -3847,7 +3898,7 @@
         <v>131</v>
       </c>
       <c r="B99" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C99" t="s">
         <v>5</v>
@@ -3858,7 +3909,7 @@
         <v>132</v>
       </c>
       <c r="B100" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="C100" t="s">
         <v>5</v>
@@ -3866,10 +3917,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B101" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C101" t="s">
         <v>5</v>
@@ -3877,10 +3928,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B102" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C102" t="s">
         <v>5</v>
@@ -3888,10 +3939,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B103" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C103" t="s">
         <v>5</v>
@@ -3899,10 +3950,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B104" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C104" t="s">
         <v>5</v>
@@ -3910,10 +3961,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B105" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C105" t="s">
         <v>5</v>
@@ -3921,10 +3972,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B106" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C106" t="s">
         <v>5</v>
@@ -3932,10 +3983,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B107" t="s">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="C107" t="s">
         <v>5</v>
@@ -3946,7 +3997,7 @@
         <v>141</v>
       </c>
       <c r="B108" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C108" t="s">
         <v>5</v>
@@ -3957,7 +4008,7 @@
         <v>142</v>
       </c>
       <c r="B109" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C109" t="s">
         <v>5</v>
@@ -3968,7 +4019,7 @@
         <v>143</v>
       </c>
       <c r="B110" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="C110" t="s">
         <v>5</v>
@@ -3979,7 +4030,7 @@
         <v>144</v>
       </c>
       <c r="B111" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="C111" t="s">
         <v>5</v>
@@ -3990,7 +4041,7 @@
         <v>145</v>
       </c>
       <c r="B112" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C112" t="s">
         <v>5</v>
@@ -4001,7 +4052,7 @@
         <v>146</v>
       </c>
       <c r="B113" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="C113" t="s">
         <v>5</v>
@@ -4012,7 +4063,7 @@
         <v>147</v>
       </c>
       <c r="B114" t="s">
-        <v>148</v>
+        <v>24</v>
       </c>
       <c r="C114" t="s">
         <v>5</v>
@@ -4020,10 +4071,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B115" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C115" t="s">
         <v>5</v>
@@ -4031,10 +4082,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B116" t="s">
-        <v>151</v>
+        <v>46</v>
       </c>
       <c r="C116" t="s">
         <v>5</v>
@@ -4042,10 +4093,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B117" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="C117" t="s">
         <v>5</v>
@@ -4053,10 +4104,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B118" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C118" t="s">
         <v>5</v>
@@ -4064,10 +4115,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B119" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C119" t="s">
         <v>5</v>
@@ -4075,10 +4126,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B120" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C120" t="s">
         <v>5</v>
@@ -4086,10 +4137,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B121" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C121" t="s">
         <v>5</v>
@@ -4097,7 +4148,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B122" t="s">
         <v>16</v>
@@ -4108,10 +4159,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B123" t="s">
-        <v>148</v>
+        <v>13</v>
       </c>
       <c r="C123" t="s">
         <v>5</v>
@@ -4119,10 +4170,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B124" t="s">
-        <v>22</v>
+        <v>158</v>
       </c>
       <c r="C124" t="s">
         <v>5</v>
@@ -4130,10 +4181,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B125" t="s">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="C125" t="s">
         <v>5</v>
@@ -4141,10 +4192,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B126" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C126" t="s">
         <v>5</v>
@@ -4152,10 +4203,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B127" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C127" t="s">
         <v>5</v>
@@ -4163,10 +4214,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B128" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="C128" t="s">
         <v>5</v>
@@ -4174,10 +4225,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B129" t="s">
-        <v>165</v>
+        <v>13</v>
       </c>
       <c r="C129" t="s">
         <v>5</v>
@@ -4185,10 +4236,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B130" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C130" t="s">
         <v>5</v>
@@ -4196,10 +4247,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B131" t="s">
-        <v>38</v>
+        <v>166</v>
       </c>
       <c r="C131" t="s">
         <v>5</v>
@@ -4207,10 +4258,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B132" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="C132" t="s">
         <v>5</v>
@@ -4218,10 +4269,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B133" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="C133" t="s">
         <v>5</v>
@@ -4229,10 +4280,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B134" t="s">
-        <v>40</v>
+        <v>169</v>
       </c>
       <c r="C134" t="s">
         <v>5</v>
@@ -4240,10 +4291,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B135" t="s">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="C135" t="s">
         <v>5</v>
@@ -4251,10 +4302,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B136" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="C136" t="s">
         <v>5</v>
@@ -4262,10 +4313,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B137" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C137" t="s">
         <v>5</v>
@@ -4273,10 +4324,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B138" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C138" t="s">
         <v>5</v>
@@ -4284,10 +4335,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B139" t="s">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="C139" t="s">
         <v>5</v>
@@ -4295,10 +4346,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B140" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="C140" t="s">
         <v>5</v>
@@ -4306,10 +4357,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B141" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="C141" t="s">
         <v>5</v>
@@ -4317,10 +4368,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B142" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C142" t="s">
         <v>5</v>
@@ -4328,10 +4379,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B143" t="s">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="C143" t="s">
         <v>5</v>
@@ -4339,10 +4390,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B144" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="C144" t="s">
         <v>5</v>
@@ -4350,10 +4401,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B145" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="C145" t="s">
         <v>5</v>
@@ -4361,10 +4412,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B146" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="C146" t="s">
         <v>5</v>
@@ -4372,10 +4423,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
+        <v>183</v>
+      </c>
+      <c r="B147" t="s">
         <v>184</v>
-      </c>
-      <c r="B147" t="s">
-        <v>49</v>
       </c>
       <c r="C147" t="s">
         <v>5</v>
@@ -4386,7 +4437,7 @@
         <v>185</v>
       </c>
       <c r="B148" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C148" t="s">
         <v>5</v>
@@ -4397,7 +4448,7 @@
         <v>186</v>
       </c>
       <c r="B149" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C149" t="s">
         <v>5</v>
@@ -4408,7 +4459,7 @@
         <v>187</v>
       </c>
       <c r="B150" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C150" t="s">
         <v>5</v>
@@ -4419,7 +4470,7 @@
         <v>188</v>
       </c>
       <c r="B151" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C151" t="s">
         <v>5</v>
@@ -4430,7 +4481,7 @@
         <v>189</v>
       </c>
       <c r="B152" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="C152" t="s">
         <v>5</v>
@@ -4441,7 +4492,7 @@
         <v>190</v>
       </c>
       <c r="B153" t="s">
-        <v>53</v>
+        <v>166</v>
       </c>
       <c r="C153" t="s">
         <v>5</v>
@@ -4452,7 +4503,7 @@
         <v>191</v>
       </c>
       <c r="B154" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C154" t="s">
         <v>5</v>
@@ -4463,7 +4514,7 @@
         <v>192</v>
       </c>
       <c r="B155" t="s">
-        <v>167</v>
+        <v>96</v>
       </c>
       <c r="C155" t="s">
         <v>5</v>
@@ -4474,7 +4525,7 @@
         <v>193</v>
       </c>
       <c r="B156" t="s">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="C156" t="s">
         <v>5</v>
@@ -4482,10 +4533,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B157" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C157" t="s">
         <v>5</v>
@@ -4493,10 +4544,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B158" t="s">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="C158" t="s">
         <v>5</v>
@@ -4504,10 +4555,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B159" t="s">
-        <v>199</v>
+        <v>4</v>
       </c>
       <c r="C159" t="s">
         <v>5</v>
@@ -4515,10 +4566,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B160" t="s">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="C160" t="s">
         <v>5</v>
@@ -4526,10 +4577,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B161" t="s">
-        <v>202</v>
+        <v>4</v>
       </c>
       <c r="C161" t="s">
         <v>5</v>
@@ -4537,10 +4588,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B162" t="s">
-        <v>202</v>
+        <v>88</v>
       </c>
       <c r="C162" t="s">
         <v>5</v>
@@ -4548,10 +4599,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B163" t="s">
-        <v>205</v>
+        <v>88</v>
       </c>
       <c r="C163" t="s">
         <v>5</v>
@@ -4559,10 +4610,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B164" t="s">
-        <v>207</v>
+        <v>11</v>
       </c>
       <c r="C164" t="s">
         <v>5</v>
@@ -4570,10 +4621,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B165" t="s">
-        <v>209</v>
+        <v>88</v>
       </c>
       <c r="C165" t="s">
         <v>5</v>
@@ -4581,10 +4632,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B166" t="s">
-        <v>197</v>
+        <v>11</v>
       </c>
       <c r="C166" t="s">
         <v>5</v>
@@ -4592,10 +4643,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B167" t="s">
-        <v>212</v>
+        <v>88</v>
       </c>
       <c r="C167" t="s">
         <v>5</v>
@@ -4603,10 +4654,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B168" t="s">
-        <v>197</v>
+        <v>88</v>
       </c>
       <c r="C168" t="s">
         <v>5</v>
@@ -4614,10 +4665,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B169" t="s">
-        <v>207</v>
+        <v>90</v>
       </c>
       <c r="C169" t="s">
         <v>5</v>
@@ -4625,10 +4676,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B170" t="s">
-        <v>207</v>
+        <v>71</v>
       </c>
       <c r="C170" t="s">
         <v>5</v>
@@ -4636,10 +4687,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B171" t="s">
-        <v>209</v>
+        <v>90</v>
       </c>
       <c r="C171" t="s">
         <v>5</v>
@@ -4647,10 +4698,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B172" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C172" t="s">
         <v>5</v>
@@ -4658,10 +4709,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B173" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C173" t="s">
         <v>5</v>
@@ -4669,10 +4720,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B174" t="s">
-        <v>220</v>
+        <v>92</v>
       </c>
       <c r="C174" t="s">
         <v>5</v>
@@ -4680,10 +4731,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B175" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C175" t="s">
         <v>5</v>
@@ -4691,10 +4742,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B176" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C176" t="s">
         <v>5</v>
@@ -4702,10 +4753,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B177" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C177" t="s">
         <v>5</v>
@@ -4713,10 +4764,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B178" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C178" t="s">
         <v>5</v>
@@ -4724,10 +4775,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B179" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C179" t="s">
         <v>5</v>
@@ -4735,10 +4786,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B180" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C180" t="s">
         <v>5</v>
@@ -4746,10 +4797,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B181" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -4757,10 +4808,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B182" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C182" t="s">
         <v>5</v>
@@ -4768,10 +4819,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B183" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="C183" t="s">
         <v>5</v>
@@ -4779,10 +4830,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B184" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="C184" t="s">
         <v>5</v>
@@ -4790,10 +4841,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B185" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C185" t="s">
         <v>5</v>
@@ -4801,10 +4852,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B186" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C186" t="s">
         <v>5</v>
@@ -4812,10 +4863,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B187" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="C187" t="s">
         <v>5</v>
@@ -4823,10 +4874,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B188" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C188" t="s">
         <v>5</v>
@@ -4834,10 +4885,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B189" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="C189" t="s">
         <v>5</v>
@@ -4845,10 +4896,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B190" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="C190" t="s">
         <v>5</v>
@@ -4856,10 +4907,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B191" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C191" t="s">
         <v>5</v>
@@ -4867,10 +4918,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B192" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C192" t="s">
         <v>5</v>
@@ -4878,10 +4929,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B193" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C193" t="s">
         <v>5</v>
@@ -4889,10 +4940,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B194" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C194" t="s">
         <v>5</v>
@@ -4900,10 +4951,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B195" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="C195" t="s">
         <v>5</v>
@@ -4911,10 +4962,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B196" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C196" t="s">
         <v>5</v>
@@ -4922,10 +4973,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B197" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C197" t="s">
         <v>5</v>
@@ -4933,10 +4984,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B198" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C198" t="s">
         <v>5</v>
@@ -4944,10 +4995,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B199" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="C199" t="s">
         <v>5</v>
@@ -4955,10 +5006,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B200" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C200" t="s">
         <v>5</v>
@@ -4966,10 +5017,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B201" t="s">
-        <v>261</v>
+        <v>219</v>
       </c>
       <c r="C201" t="s">
         <v>5</v>
@@ -4977,10 +5028,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B202" t="s">
-        <v>263</v>
+        <v>222</v>
       </c>
       <c r="C202" t="s">
         <v>5</v>
@@ -4988,10 +5039,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B203" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="C203" t="s">
         <v>5</v>
@@ -4999,10 +5050,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B204" t="s">
-        <v>266</v>
+        <v>226</v>
       </c>
       <c r="C204" t="s">
         <v>5</v>
@@ -5010,10 +5061,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B205" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="C205" t="s">
         <v>5</v>
@@ -5021,10 +5072,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B206" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="C206" t="s">
         <v>5</v>
@@ -5032,10 +5083,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="B207" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C207" t="s">
         <v>5</v>
@@ -5043,10 +5094,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="B208" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="C208" t="s">
         <v>5</v>
@@ -5054,10 +5105,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="B209" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="C209" t="s">
         <v>5</v>
@@ -5065,10 +5116,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="B210" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C210" t="s">
         <v>5</v>
@@ -5076,10 +5127,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B211" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="C211" t="s">
         <v>5</v>
@@ -5087,10 +5138,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="B212" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="C212" t="s">
         <v>5</v>
@@ -5098,10 +5149,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="B213" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="C213" t="s">
         <v>5</v>
@@ -5109,10 +5160,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="B214" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="C214" t="s">
         <v>5</v>
@@ -5120,10 +5171,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="B215" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="C215" t="s">
         <v>5</v>
@@ -5131,10 +5182,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="B216" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C216" t="s">
         <v>5</v>
@@ -5142,10 +5193,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B217" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C217" t="s">
         <v>5</v>
@@ -5153,10 +5204,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="B218" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C218" t="s">
         <v>5</v>
@@ -5164,10 +5215,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B219" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C219" t="s">
         <v>5</v>
@@ -5175,10 +5226,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="C220" t="s">
         <v>5</v>
@@ -5186,10 +5237,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B221" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="C221" t="s">
         <v>5</v>
@@ -5197,10 +5248,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="B222" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C222" t="s">
         <v>5</v>
@@ -5208,10 +5259,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B223" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="C223" t="s">
         <v>5</v>
@@ -5219,10 +5270,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="B224" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="C224" t="s">
         <v>5</v>
@@ -5230,10 +5281,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="B225" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C225" t="s">
         <v>5</v>
@@ -5241,10 +5292,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B226" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C226" t="s">
         <v>5</v>
@@ -5252,10 +5303,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="B227" t="s">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="C227" t="s">
         <v>5</v>
@@ -5263,10 +5314,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="B228" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C228" t="s">
         <v>5</v>
@@ -5274,10 +5325,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="B229" t="s">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="C229" t="s">
         <v>5</v>
@@ -5285,10 +5336,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B230" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C230" t="s">
         <v>5</v>
@@ -5296,10 +5347,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B231" t="s">
-        <v>199</v>
+        <v>301</v>
       </c>
       <c r="C231" t="s">
         <v>5</v>
@@ -5307,10 +5358,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B232" t="s">
-        <v>311</v>
+        <v>262</v>
       </c>
       <c r="C232" t="s">
         <v>5</v>
@@ -5318,10 +5369,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B233" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="C233" t="s">
         <v>5</v>
@@ -5329,10 +5380,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B234" t="s">
-        <v>205</v>
+        <v>305</v>
       </c>
       <c r="C234" t="s">
         <v>5</v>
@@ -5340,10 +5391,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B235" t="s">
-        <v>51</v>
+        <v>307</v>
       </c>
       <c r="C235" t="s">
         <v>5</v>
@@ -5351,10 +5402,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B236" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C236" t="s">
         <v>5</v>
@@ -5362,10 +5413,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B237" t="s">
-        <v>72</v>
+        <v>237</v>
       </c>
       <c r="C237" t="s">
         <v>5</v>
@@ -5373,10 +5424,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B238" t="s">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="C238" t="s">
         <v>5</v>
@@ -5384,10 +5435,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B239" t="s">
-        <v>151</v>
+        <v>314</v>
       </c>
       <c r="C239" t="s">
         <v>5</v>
@@ -5395,10 +5446,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B240" t="s">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -5406,10 +5457,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B241" t="s">
-        <v>38</v>
+        <v>317</v>
       </c>
       <c r="C241" t="s">
         <v>5</v>
@@ -5417,10 +5468,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B242" t="s">
-        <v>16</v>
+        <v>319</v>
       </c>
       <c r="C242" t="s">
         <v>5</v>
@@ -5428,10 +5479,10 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B243" t="s">
-        <v>14</v>
+        <v>312</v>
       </c>
       <c r="C243" t="s">
         <v>5</v>
@@ -5439,10 +5490,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B244" t="s">
-        <v>26</v>
+        <v>257</v>
       </c>
       <c r="C244" t="s">
         <v>5</v>
@@ -5450,10 +5501,10 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B245" t="s">
-        <v>11</v>
+        <v>323</v>
       </c>
       <c r="C245" t="s">
         <v>5</v>
@@ -5461,10 +5512,10 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B246" t="s">
-        <v>11</v>
+        <v>257</v>
       </c>
       <c r="C246" t="s">
         <v>5</v>
@@ -5472,10 +5523,10 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B247" t="s">
-        <v>28</v>
+        <v>319</v>
       </c>
       <c r="C247" t="s">
         <v>5</v>
@@ -5483,10 +5534,10 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B248" t="s">
-        <v>18</v>
+        <v>216</v>
       </c>
       <c r="C248" t="s">
         <v>5</v>
@@ -5494,10 +5545,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B249" t="s">
-        <v>7</v>
+        <v>328</v>
       </c>
       <c r="C249" t="s">
         <v>5</v>
@@ -5505,10 +5556,10 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B250" t="s">
-        <v>7</v>
+        <v>214</v>
       </c>
       <c r="C250" t="s">
         <v>5</v>
@@ -5516,10 +5567,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B251" t="s">
-        <v>82</v>
+        <v>222</v>
       </c>
       <c r="C251" t="s">
         <v>5</v>
@@ -5527,10 +5578,10 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B252" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C252" t="s">
         <v>5</v>
@@ -5538,10 +5589,10 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
+        <v>332</v>
+      </c>
+      <c r="B253" t="s">
         <v>333</v>
-      </c>
-      <c r="B253" t="s">
-        <v>4</v>
       </c>
       <c r="C253" t="s">
         <v>5</v>
@@ -5552,7 +5603,7 @@
         <v>334</v>
       </c>
       <c r="B254" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="C254" t="s">
         <v>5</v>
@@ -5563,7 +5614,7 @@
         <v>335</v>
       </c>
       <c r="B255" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="C255" t="s">
         <v>5</v>
@@ -5574,7 +5625,7 @@
         <v>336</v>
       </c>
       <c r="B256" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
       <c r="C256" t="s">
         <v>5</v>
@@ -5585,7 +5636,7 @@
         <v>337</v>
       </c>
       <c r="B257" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C257" t="s">
         <v>5</v>
@@ -5596,7 +5647,7 @@
         <v>338</v>
       </c>
       <c r="B258" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C258" t="s">
         <v>5</v>
@@ -5607,7 +5658,7 @@
         <v>339</v>
       </c>
       <c r="B259" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C259" t="s">
         <v>5</v>
@@ -5618,7 +5669,7 @@
         <v>340</v>
       </c>
       <c r="B260" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C260" t="s">
         <v>5</v>
@@ -5629,7 +5680,7 @@
         <v>341</v>
       </c>
       <c r="B261" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C261" t="s">
         <v>5</v>
@@ -5640,7 +5691,7 @@
         <v>342</v>
       </c>
       <c r="B262" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C262" t="s">
         <v>5</v>
@@ -5651,7 +5702,7 @@
         <v>343</v>
       </c>
       <c r="B263" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C263" t="s">
         <v>5</v>
@@ -5662,7 +5713,7 @@
         <v>344</v>
       </c>
       <c r="B264" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C264" t="s">
         <v>5</v>
@@ -5673,7 +5724,7 @@
         <v>345</v>
       </c>
       <c r="B265" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C265" t="s">
         <v>5</v>
@@ -5684,7 +5735,7 @@
         <v>346</v>
       </c>
       <c r="B266" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="C266" t="s">
         <v>5</v>
@@ -5695,7 +5746,7 @@
         <v>347</v>
       </c>
       <c r="B267" t="s">
-        <v>167</v>
+        <v>24</v>
       </c>
       <c r="C267" t="s">
         <v>5</v>
@@ -5706,7 +5757,7 @@
         <v>348</v>
       </c>
       <c r="B268" t="s">
-        <v>349</v>
+        <v>100</v>
       </c>
       <c r="C268" t="s">
         <v>5</v>
@@ -5714,10 +5765,10 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B269" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="C269" t="s">
         <v>5</v>
@@ -5725,10 +5776,10 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B270" t="s">
-        <v>165</v>
+        <v>9</v>
       </c>
       <c r="C270" t="s">
         <v>5</v>
@@ -5736,10 +5787,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B271" t="s">
-        <v>165</v>
+        <v>16</v>
       </c>
       <c r="C271" t="s">
         <v>5</v>
@@ -5747,10 +5798,10 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B272" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C272" t="s">
         <v>5</v>
@@ -5758,10 +5809,10 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B273" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C273" t="s">
         <v>5</v>
@@ -5769,10 +5820,10 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B274" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="C274" t="s">
         <v>5</v>
@@ -5780,10 +5831,10 @@
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B275" t="s">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="C275" t="s">
         <v>5</v>
@@ -5791,10 +5842,10 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B276" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C276" t="s">
         <v>5</v>
@@ -5802,10 +5853,10 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B277" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="C277" t="s">
         <v>5</v>
@@ -5813,10 +5864,10 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B278" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C278" t="s">
         <v>5</v>
@@ -5824,10 +5875,10 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B279" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C279" t="s">
         <v>5</v>
@@ -5835,10 +5886,10 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B280" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C280" t="s">
         <v>5</v>
@@ -5846,10 +5897,10 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B281" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C281" t="s">
         <v>5</v>
@@ -5857,10 +5908,10 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B282" t="s">
-        <v>151</v>
+        <v>13</v>
       </c>
       <c r="C282" t="s">
         <v>5</v>
@@ -5868,10 +5919,10 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B283" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C283" t="s">
         <v>5</v>
@@ -5879,10 +5930,10 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B284" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="C284" t="s">
         <v>5</v>
@@ -5890,10 +5941,10 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
+        <v>365</v>
+      </c>
+      <c r="B285" t="s">
         <v>366</v>
-      </c>
-      <c r="B285" t="s">
-        <v>115</v>
       </c>
       <c r="C285" t="s">
         <v>5</v>
@@ -5904,7 +5955,7 @@
         <v>367</v>
       </c>
       <c r="B286" t="s">
-        <v>368</v>
+        <v>90</v>
       </c>
       <c r="C286" t="s">
         <v>5</v>
@@ -5912,10 +5963,10 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B287" t="s">
-        <v>368</v>
+        <v>4</v>
       </c>
       <c r="C287" t="s">
         <v>5</v>
@@ -5923,10 +5974,10 @@
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B288" t="s">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="C288" t="s">
         <v>5</v>
@@ -5934,10 +5985,10 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B289" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C289" t="s">
         <v>5</v>
@@ -5945,10 +5996,10 @@
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B290" t="s">
-        <v>368</v>
+        <v>58</v>
       </c>
       <c r="C290" t="s">
         <v>5</v>
@@ -5956,10 +6007,10 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B291" t="s">
-        <v>374</v>
+        <v>4</v>
       </c>
       <c r="C291" t="s">
         <v>5</v>
@@ -5967,10 +6018,10 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B292" t="s">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="C292" t="s">
         <v>5</v>
@@ -5978,10 +6029,10 @@
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B293" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C293" t="s">
         <v>5</v>
@@ -5989,10 +6040,10 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B294" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C294" t="s">
         <v>5</v>
@@ -6000,10 +6051,10 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B295" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C295" t="s">
         <v>5</v>
@@ -6011,10 +6062,10 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B296" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="C296" t="s">
         <v>5</v>
@@ -6022,10 +6073,10 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B297" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C297" t="s">
         <v>5</v>
@@ -6033,10 +6084,10 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B298" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="C298" t="s">
         <v>5</v>
@@ -6044,10 +6095,10 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B299" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -6055,10 +6106,10 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B300" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C300" t="s">
         <v>5</v>
@@ -6066,10 +6117,10 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B301" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C301" t="s">
         <v>5</v>
@@ -6077,10 +6128,10 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B302" t="s">
-        <v>4</v>
+        <v>133</v>
       </c>
       <c r="C302" t="s">
         <v>5</v>
@@ -6088,10 +6139,10 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B303" t="s">
-        <v>38</v>
+        <v>385</v>
       </c>
       <c r="C303" t="s">
         <v>5</v>
@@ -6099,10 +6150,10 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B304" t="s">
-        <v>20</v>
+        <v>385</v>
       </c>
       <c r="C304" t="s">
         <v>5</v>
@@ -6110,10 +6161,10 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B305" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="C305" t="s">
         <v>5</v>
@@ -6121,10 +6172,10 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B306" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="C306" t="s">
         <v>5</v>
@@ -6132,10 +6183,10 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B307" t="s">
-        <v>16</v>
+        <v>385</v>
       </c>
       <c r="C307" t="s">
         <v>5</v>
@@ -6143,10 +6194,10 @@
     </row>
     <row r="308">
       <c r="A308" t="s">
+        <v>390</v>
+      </c>
+      <c r="B308" t="s">
         <v>391</v>
-      </c>
-      <c r="B308" t="s">
-        <v>31</v>
       </c>
       <c r="C308" t="s">
         <v>5</v>
@@ -6157,7 +6208,7 @@
         <v>392</v>
       </c>
       <c r="B309" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="C309" t="s">
         <v>5</v>
@@ -6168,7 +6219,7 @@
         <v>393</v>
       </c>
       <c r="B310" t="s">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="C310" t="s">
         <v>5</v>
@@ -6179,7 +6230,7 @@
         <v>394</v>
       </c>
       <c r="B311" t="s">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="C311" t="s">
         <v>5</v>
@@ -6190,7 +6241,7 @@
         <v>395</v>
       </c>
       <c r="B312" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="C312" t="s">
         <v>5</v>
@@ -6201,7 +6252,7 @@
         <v>396</v>
       </c>
       <c r="B313" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C313" t="s">
         <v>5</v>
@@ -6212,7 +6263,7 @@
         <v>397</v>
       </c>
       <c r="B314" t="s">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="C314" t="s">
         <v>5</v>
@@ -6234,7 +6285,7 @@
         <v>399</v>
       </c>
       <c r="B316" t="s">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="C316" t="s">
         <v>5</v>
@@ -6245,7 +6296,7 @@
         <v>400</v>
       </c>
       <c r="B317" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C317" t="s">
         <v>5</v>
@@ -6256,7 +6307,7 @@
         <v>401</v>
       </c>
       <c r="B318" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C318" t="s">
         <v>5</v>
@@ -6267,7 +6318,7 @@
         <v>402</v>
       </c>
       <c r="B319" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="C319" t="s">
         <v>5</v>
@@ -6278,7 +6329,7 @@
         <v>403</v>
       </c>
       <c r="B320" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="C320" t="s">
         <v>5</v>
@@ -6289,7 +6340,7 @@
         <v>404</v>
       </c>
       <c r="B321" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="C321" t="s">
         <v>5</v>
@@ -6300,7 +6351,7 @@
         <v>405</v>
       </c>
       <c r="B322" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="C322" t="s">
         <v>5</v>
@@ -6311,7 +6362,7 @@
         <v>406</v>
       </c>
       <c r="B323" t="s">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="C323" t="s">
         <v>5</v>
@@ -6322,7 +6373,7 @@
         <v>407</v>
       </c>
       <c r="B324" t="s">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="C324" t="s">
         <v>5</v>
@@ -6333,7 +6384,7 @@
         <v>408</v>
       </c>
       <c r="B325" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C325" t="s">
         <v>5</v>
@@ -6344,7 +6395,7 @@
         <v>409</v>
       </c>
       <c r="B326" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C326" t="s">
         <v>5</v>
@@ -6355,7 +6406,7 @@
         <v>410</v>
       </c>
       <c r="B327" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C327" t="s">
         <v>5</v>
@@ -6366,7 +6417,7 @@
         <v>411</v>
       </c>
       <c r="B328" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="C328" t="s">
         <v>5</v>
@@ -6377,7 +6428,7 @@
         <v>412</v>
       </c>
       <c r="B329" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C329" t="s">
         <v>5</v>
@@ -6388,7 +6439,7 @@
         <v>413</v>
       </c>
       <c r="B330" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C330" t="s">
         <v>5</v>
@@ -6399,7 +6450,7 @@
         <v>414</v>
       </c>
       <c r="B331" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C331" t="s">
         <v>5</v>
@@ -6410,7 +6461,7 @@
         <v>415</v>
       </c>
       <c r="B332" t="s">
-        <v>148</v>
+        <v>69</v>
       </c>
       <c r="C332" t="s">
         <v>5</v>
@@ -6421,7 +6472,7 @@
         <v>416</v>
       </c>
       <c r="B333" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="C333" t="s">
         <v>5</v>
@@ -6432,7 +6483,7 @@
         <v>417</v>
       </c>
       <c r="B334" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C334" t="s">
         <v>5</v>
@@ -6443,7 +6494,7 @@
         <v>418</v>
       </c>
       <c r="B335" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C335" t="s">
         <v>5</v>
@@ -6454,7 +6505,7 @@
         <v>419</v>
       </c>
       <c r="B336" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="C336" t="s">
         <v>5</v>
@@ -6465,7 +6516,7 @@
         <v>420</v>
       </c>
       <c r="B337" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="C337" t="s">
         <v>5</v>
@@ -6476,7 +6527,7 @@
         <v>421</v>
       </c>
       <c r="B338" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="C338" t="s">
         <v>5</v>
@@ -6487,7 +6538,7 @@
         <v>422</v>
       </c>
       <c r="B339" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="C339" t="s">
         <v>5</v>
@@ -6498,7 +6549,7 @@
         <v>423</v>
       </c>
       <c r="B340" t="s">
-        <v>22</v>
+        <v>158</v>
       </c>
       <c r="C340" t="s">
         <v>5</v>
@@ -6509,7 +6560,7 @@
         <v>424</v>
       </c>
       <c r="B341" t="s">
-        <v>22</v>
+        <v>158</v>
       </c>
       <c r="C341" t="s">
         <v>5</v>
@@ -6520,7 +6571,7 @@
         <v>425</v>
       </c>
       <c r="B342" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C342" t="s">
         <v>5</v>
@@ -6531,7 +6582,7 @@
         <v>426</v>
       </c>
       <c r="B343" t="s">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="C343" t="s">
         <v>5</v>
@@ -6542,7 +6593,7 @@
         <v>427</v>
       </c>
       <c r="B344" t="s">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="C344" t="s">
         <v>5</v>
@@ -6553,7 +6604,7 @@
         <v>428</v>
       </c>
       <c r="B345" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="C345" t="s">
         <v>5</v>
@@ -6564,7 +6615,7 @@
         <v>429</v>
       </c>
       <c r="B346" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="C346" t="s">
         <v>5</v>
@@ -6575,7 +6626,7 @@
         <v>430</v>
       </c>
       <c r="B347" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C347" t="s">
         <v>5</v>
@@ -6586,7 +6637,7 @@
         <v>431</v>
       </c>
       <c r="B348" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C348" t="s">
         <v>5</v>
@@ -6597,7 +6648,7 @@
         <v>432</v>
       </c>
       <c r="B349" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C349" t="s">
         <v>5</v>
@@ -6608,7 +6659,7 @@
         <v>433</v>
       </c>
       <c r="B350" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="C350" t="s">
         <v>5</v>
@@ -6619,7 +6670,7 @@
         <v>434</v>
       </c>
       <c r="B351" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C351" t="s">
         <v>5</v>
@@ -6630,7 +6681,7 @@
         <v>435</v>
       </c>
       <c r="B352" t="s">
-        <v>436</v>
+        <v>88</v>
       </c>
       <c r="C352" t="s">
         <v>5</v>
@@ -6638,10 +6689,10 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B353" t="s">
-        <v>438</v>
+        <v>11</v>
       </c>
       <c r="C353" t="s">
         <v>5</v>
@@ -6649,10 +6700,10 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B354" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C354" t="s">
         <v>5</v>
@@ -6660,10 +6711,10 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B355" t="s">
-        <v>441</v>
+        <v>88</v>
       </c>
       <c r="C355" t="s">
         <v>5</v>
@@ -6671,10 +6722,10 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B356" t="s">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="C356" t="s">
         <v>5</v>
@@ -6682,10 +6733,10 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B357" t="s">
-        <v>316</v>
+        <v>13</v>
       </c>
       <c r="C357" t="s">
         <v>5</v>
@@ -6693,10 +6744,10 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B358" t="s">
-        <v>316</v>
+        <v>13</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -6704,10 +6755,10 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B359" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="C359" t="s">
         <v>5</v>
@@ -6715,10 +6766,10 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B360" t="s">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="C360" t="s">
         <v>5</v>
@@ -6726,10 +6777,10 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B361" t="s">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="C361" t="s">
         <v>5</v>
@@ -6737,10 +6788,10 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B362" t="s">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="C362" t="s">
         <v>5</v>
@@ -6748,10 +6799,10 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B363" t="s">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="C363" t="s">
         <v>5</v>
@@ -6759,10 +6810,10 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B364" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="C364" t="s">
         <v>5</v>
@@ -6770,10 +6821,10 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B365" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="C365" t="s">
         <v>5</v>
@@ -6781,10 +6832,10 @@
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B366" t="s">
-        <v>51</v>
+        <v>166</v>
       </c>
       <c r="C366" t="s">
         <v>5</v>
@@ -6792,10 +6843,10 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B367" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C367" t="s">
         <v>5</v>
@@ -6803,10 +6854,10 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B368" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="C368" t="s">
         <v>5</v>
@@ -6814,10 +6865,10 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B369" t="s">
-        <v>51</v>
+        <v>453</v>
       </c>
       <c r="C369" t="s">
         <v>5</v>
@@ -6825,10 +6876,10 @@
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B370" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C370" t="s">
         <v>5</v>
@@ -6836,10 +6887,10 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B371" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="C371" t="s">
         <v>5</v>
@@ -6847,10 +6898,10 @@
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B372" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="C372" t="s">
         <v>5</v>
@@ -6858,10 +6909,10 @@
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B373" t="s">
-        <v>441</v>
+        <v>211</v>
       </c>
       <c r="C373" t="s">
         <v>5</v>
@@ -6869,10 +6920,10 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B374" t="s">
-        <v>205</v>
+        <v>333</v>
       </c>
       <c r="C374" t="s">
         <v>5</v>
@@ -6880,10 +6931,10 @@
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B375" t="s">
-        <v>233</v>
+        <v>333</v>
       </c>
       <c r="C375" t="s">
         <v>5</v>
@@ -6891,10 +6942,10 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B376" t="s">
-        <v>290</v>
+        <v>90</v>
       </c>
       <c r="C376" t="s">
         <v>5</v>
@@ -6902,10 +6953,10 @@
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B377" t="s">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="C377" t="s">
         <v>5</v>
@@ -6913,10 +6964,10 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B378" t="s">
-        <v>288</v>
+        <v>71</v>
       </c>
       <c r="C378" t="s">
         <v>5</v>
@@ -6924,10 +6975,10 @@
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B379" t="s">
-        <v>295</v>
+        <v>71</v>
       </c>
       <c r="C379" t="s">
         <v>5</v>
@@ -6935,10 +6986,10 @@
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B380" t="s">
-        <v>209</v>
+        <v>71</v>
       </c>
       <c r="C380" t="s">
         <v>5</v>
@@ -6946,10 +6997,10 @@
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B381" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C381" t="s">
         <v>5</v>
@@ -6957,10 +7008,10 @@
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B382" t="s">
-        <v>436</v>
+        <v>4</v>
       </c>
       <c r="C382" t="s">
         <v>5</v>
@@ -6968,10 +7019,10 @@
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B383" t="s">
-        <v>349</v>
+        <v>69</v>
       </c>
       <c r="C383" t="s">
         <v>5</v>
@@ -6979,10 +7030,10 @@
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B384" t="s">
-        <v>349</v>
+        <v>96</v>
       </c>
       <c r="C384" t="s">
         <v>5</v>
@@ -6990,10 +7041,10 @@
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B385" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C385" t="s">
         <v>5</v>
@@ -7001,10 +7052,10 @@
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B386" t="s">
-        <v>441</v>
+        <v>69</v>
       </c>
       <c r="C386" t="s">
         <v>5</v>
@@ -7012,10 +7063,10 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
+        <v>473</v>
+      </c>
+      <c r="B387" t="s">
         <v>474</v>
-      </c>
-      <c r="B387" t="s">
-        <v>167</v>
       </c>
       <c r="C387" t="s">
         <v>5</v>
@@ -7026,7 +7077,7 @@
         <v>475</v>
       </c>
       <c r="B388" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="C388" t="s">
         <v>5</v>
@@ -7037,7 +7088,7 @@
         <v>476</v>
       </c>
       <c r="B389" t="s">
-        <v>53</v>
+        <v>458</v>
       </c>
       <c r="C389" t="s">
         <v>5</v>
@@ -7048,7 +7099,7 @@
         <v>477</v>
       </c>
       <c r="B390" t="s">
-        <v>53</v>
+        <v>458</v>
       </c>
       <c r="C390" t="s">
         <v>5</v>
@@ -7059,7 +7110,7 @@
         <v>478</v>
       </c>
       <c r="B391" t="s">
-        <v>148</v>
+        <v>222</v>
       </c>
       <c r="C391" t="s">
         <v>5</v>
@@ -7070,7 +7121,7 @@
         <v>479</v>
       </c>
       <c r="B392" t="s">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="C392" t="s">
         <v>5</v>
@@ -7081,7 +7132,7 @@
         <v>480</v>
       </c>
       <c r="B393" t="s">
-        <v>31</v>
+        <v>307</v>
       </c>
       <c r="C393" t="s">
         <v>5</v>
@@ -7092,7 +7143,7 @@
         <v>481</v>
       </c>
       <c r="B394" t="s">
-        <v>28</v>
+        <v>219</v>
       </c>
       <c r="C394" t="s">
         <v>5</v>
@@ -7103,7 +7154,7 @@
         <v>482</v>
       </c>
       <c r="B395" t="s">
-        <v>14</v>
+        <v>305</v>
       </c>
       <c r="C395" t="s">
         <v>5</v>
@@ -7114,7 +7165,7 @@
         <v>483</v>
       </c>
       <c r="B396" t="s">
-        <v>28</v>
+        <v>312</v>
       </c>
       <c r="C396" t="s">
         <v>5</v>
@@ -7125,7 +7176,7 @@
         <v>484</v>
       </c>
       <c r="B397" t="s">
-        <v>16</v>
+        <v>226</v>
       </c>
       <c r="C397" t="s">
         <v>5</v>
@@ -7136,7 +7187,7 @@
         <v>485</v>
       </c>
       <c r="B398" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="C398" t="s">
         <v>5</v>
@@ -7147,7 +7198,7 @@
         <v>486</v>
       </c>
       <c r="B399" t="s">
-        <v>38</v>
+        <v>453</v>
       </c>
       <c r="C399" t="s">
         <v>5</v>
@@ -7158,7 +7209,7 @@
         <v>487</v>
       </c>
       <c r="B400" t="s">
-        <v>22</v>
+        <v>366</v>
       </c>
       <c r="C400" t="s">
         <v>5</v>
@@ -7169,7 +7220,7 @@
         <v>488</v>
       </c>
       <c r="B401" t="s">
-        <v>140</v>
+        <v>366</v>
       </c>
       <c r="C401" t="s">
         <v>5</v>
@@ -7180,7 +7231,7 @@
         <v>489</v>
       </c>
       <c r="B402" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="C402" t="s">
         <v>5</v>
@@ -7191,7 +7242,7 @@
         <v>490</v>
       </c>
       <c r="B403" t="s">
-        <v>53</v>
+        <v>458</v>
       </c>
       <c r="C403" t="s">
         <v>5</v>
@@ -7202,7 +7253,7 @@
         <v>491</v>
       </c>
       <c r="B404" t="s">
-        <v>53</v>
+        <v>184</v>
       </c>
       <c r="C404" t="s">
         <v>5</v>
@@ -7213,7 +7264,7 @@
         <v>492</v>
       </c>
       <c r="B405" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="C405" t="s">
         <v>5</v>
@@ -7224,7 +7275,7 @@
         <v>493</v>
       </c>
       <c r="B406" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C406" t="s">
         <v>5</v>
@@ -7235,7 +7286,7 @@
         <v>494</v>
       </c>
       <c r="B407" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C407" t="s">
         <v>5</v>
@@ -7246,7 +7297,7 @@
         <v>495</v>
       </c>
       <c r="B408" t="s">
-        <v>51</v>
+        <v>166</v>
       </c>
       <c r="C408" t="s">
         <v>5</v>
@@ -7257,7 +7308,7 @@
         <v>496</v>
       </c>
       <c r="B409" t="s">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="C409" t="s">
         <v>5</v>
@@ -7268,7 +7319,7 @@
         <v>497</v>
       </c>
       <c r="B410" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C410" t="s">
         <v>5</v>
@@ -7279,7 +7330,7 @@
         <v>498</v>
       </c>
       <c r="B411" t="s">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="C411" t="s">
         <v>5</v>
@@ -7290,7 +7341,7 @@
         <v>499</v>
       </c>
       <c r="B412" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="C412" t="s">
         <v>5</v>
@@ -7301,7 +7352,7 @@
         <v>500</v>
       </c>
       <c r="B413" t="s">
-        <v>148</v>
+        <v>48</v>
       </c>
       <c r="C413" t="s">
         <v>5</v>
@@ -7312,7 +7363,7 @@
         <v>501</v>
       </c>
       <c r="B414" t="s">
-        <v>165</v>
+        <v>16</v>
       </c>
       <c r="C414" t="s">
         <v>5</v>
@@ -7323,7 +7374,7 @@
         <v>502</v>
       </c>
       <c r="B415" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C415" t="s">
         <v>5</v>
@@ -7334,7 +7385,7 @@
         <v>503</v>
       </c>
       <c r="B416" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C416" t="s">
         <v>5</v>
@@ -7345,7 +7396,7 @@
         <v>504</v>
       </c>
       <c r="B417" t="s">
-        <v>436</v>
+        <v>13</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -7356,7 +7407,7 @@
         <v>505</v>
       </c>
       <c r="B418" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C418" t="s">
         <v>5</v>
@@ -7367,7 +7418,7 @@
         <v>506</v>
       </c>
       <c r="B419" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C419" t="s">
         <v>5</v>
@@ -7378,7 +7429,7 @@
         <v>507</v>
       </c>
       <c r="B420" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C420" t="s">
         <v>5</v>
@@ -7389,7 +7440,7 @@
         <v>508</v>
       </c>
       <c r="B421" t="s">
-        <v>349</v>
+        <v>71</v>
       </c>
       <c r="C421" t="s">
         <v>5</v>
@@ -7400,7 +7451,7 @@
         <v>509</v>
       </c>
       <c r="B422" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="C422" t="s">
         <v>5</v>
@@ -7411,7 +7462,7 @@
         <v>510</v>
       </c>
       <c r="B423" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C423" t="s">
         <v>5</v>
@@ -7422,7 +7473,7 @@
         <v>511</v>
       </c>
       <c r="B424" t="s">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="C424" t="s">
         <v>5</v>
@@ -7433,7 +7484,7 @@
         <v>512</v>
       </c>
       <c r="B425" t="s">
-        <v>441</v>
+        <v>69</v>
       </c>
       <c r="C425" t="s">
         <v>5</v>
@@ -7444,7 +7495,7 @@
         <v>513</v>
       </c>
       <c r="B426" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C426" t="s">
         <v>5</v>
@@ -7455,7 +7506,7 @@
         <v>514</v>
       </c>
       <c r="B427" t="s">
-        <v>457</v>
+        <v>90</v>
       </c>
       <c r="C427" t="s">
         <v>5</v>
@@ -7466,7 +7517,7 @@
         <v>515</v>
       </c>
       <c r="B428" t="s">
-        <v>316</v>
+        <v>4</v>
       </c>
       <c r="C428" t="s">
         <v>5</v>
@@ -7477,7 +7528,7 @@
         <v>516</v>
       </c>
       <c r="B429" t="s">
-        <v>316</v>
+        <v>166</v>
       </c>
       <c r="C429" t="s">
         <v>5</v>
@@ -7488,7 +7539,7 @@
         <v>517</v>
       </c>
       <c r="B430" t="s">
-        <v>436</v>
+        <v>166</v>
       </c>
       <c r="C430" t="s">
         <v>5</v>
@@ -7499,7 +7550,7 @@
         <v>518</v>
       </c>
       <c r="B431" t="s">
-        <v>151</v>
+        <v>4</v>
       </c>
       <c r="C431" t="s">
         <v>5</v>
@@ -7510,7 +7561,7 @@
         <v>519</v>
       </c>
       <c r="B432" t="s">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="C432" t="s">
         <v>5</v>
@@ -7521,7 +7572,7 @@
         <v>520</v>
       </c>
       <c r="B433" t="s">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="C433" t="s">
         <v>5</v>
@@ -7532,7 +7583,7 @@
         <v>521</v>
       </c>
       <c r="B434" t="s">
-        <v>70</v>
+        <v>453</v>
       </c>
       <c r="C434" t="s">
         <v>5</v>
@@ -7543,7 +7594,7 @@
         <v>522</v>
       </c>
       <c r="B435" t="s">
-        <v>51</v>
+        <v>184</v>
       </c>
       <c r="C435" t="s">
         <v>5</v>
@@ -7554,7 +7605,7 @@
         <v>523</v>
       </c>
       <c r="B436" t="s">
-        <v>436</v>
+        <v>169</v>
       </c>
       <c r="C436" t="s">
         <v>5</v>
@@ -7565,7 +7616,7 @@
         <v>524</v>
       </c>
       <c r="B437" t="s">
-        <v>167</v>
+        <v>90</v>
       </c>
       <c r="C437" t="s">
         <v>5</v>
@@ -7576,7 +7627,7 @@
         <v>525</v>
       </c>
       <c r="B438" t="s">
-        <v>151</v>
+        <v>366</v>
       </c>
       <c r="C438" t="s">
         <v>5</v>
@@ -7587,7 +7638,7 @@
         <v>526</v>
       </c>
       <c r="B439" t="s">
-        <v>349</v>
+        <v>92</v>
       </c>
       <c r="C439" t="s">
         <v>5</v>
@@ -7598,7 +7649,7 @@
         <v>527</v>
       </c>
       <c r="B440" t="s">
-        <v>349</v>
+        <v>92</v>
       </c>
       <c r="C440" t="s">
         <v>5</v>
@@ -7609,7 +7660,7 @@
         <v>528</v>
       </c>
       <c r="B441" t="s">
-        <v>457</v>
+        <v>224</v>
       </c>
       <c r="C441" t="s">
         <v>5</v>
@@ -7620,7 +7671,7 @@
         <v>529</v>
       </c>
       <c r="B442" t="s">
-        <v>316</v>
+        <v>458</v>
       </c>
       <c r="C442" t="s">
         <v>5</v>
@@ -7631,7 +7682,7 @@
         <v>530</v>
       </c>
       <c r="B443" t="s">
-        <v>441</v>
+        <v>92</v>
       </c>
       <c r="C443" t="s">
         <v>5</v>
@@ -7642,7 +7693,7 @@
         <v>531</v>
       </c>
       <c r="B444" t="s">
-        <v>199</v>
+        <v>474</v>
       </c>
       <c r="C444" t="s">
         <v>5</v>
@@ -7653,7 +7704,7 @@
         <v>532</v>
       </c>
       <c r="B445" t="s">
-        <v>207</v>
+        <v>333</v>
       </c>
       <c r="C445" t="s">
         <v>5</v>
@@ -7664,7 +7715,7 @@
         <v>533</v>
       </c>
       <c r="B446" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="C446" t="s">
         <v>5</v>
@@ -7675,7 +7726,7 @@
         <v>534</v>
       </c>
       <c r="B447" t="s">
-        <v>311</v>
+        <v>453</v>
       </c>
       <c r="C447" t="s">
         <v>5</v>
@@ -7686,7 +7737,7 @@
         <v>535</v>
       </c>
       <c r="B448" t="s">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="C448" t="s">
         <v>5</v>
@@ -7697,7 +7748,7 @@
         <v>536</v>
       </c>
       <c r="B449" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C449" t="s">
         <v>5</v>
@@ -7708,7 +7759,7 @@
         <v>537</v>
       </c>
       <c r="B450" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C450" t="s">
         <v>5</v>
@@ -7719,7 +7770,7 @@
         <v>538</v>
       </c>
       <c r="B451" t="s">
-        <v>539</v>
+        <v>88</v>
       </c>
       <c r="C451" t="s">
         <v>5</v>
@@ -7727,10 +7778,10 @@
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B452" t="s">
-        <v>541</v>
+        <v>69</v>
       </c>
       <c r="C452" t="s">
         <v>5</v>
@@ -7738,10 +7789,10 @@
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B453" t="s">
-        <v>292</v>
+        <v>453</v>
       </c>
       <c r="C453" t="s">
         <v>5</v>
@@ -7749,10 +7800,10 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B454" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="C454" t="s">
         <v>5</v>
@@ -7760,10 +7811,10 @@
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B455" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="C455" t="s">
         <v>5</v>
@@ -7771,10 +7822,10 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B456" t="s">
-        <v>72</v>
+        <v>366</v>
       </c>
       <c r="C456" t="s">
         <v>5</v>
@@ -7782,10 +7833,10 @@
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B457" t="s">
-        <v>53</v>
+        <v>366</v>
       </c>
       <c r="C457" t="s">
         <v>5</v>
@@ -7793,10 +7844,10 @@
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B458" t="s">
-        <v>78</v>
+        <v>474</v>
       </c>
       <c r="C458" t="s">
         <v>5</v>
@@ -7804,10 +7855,10 @@
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B459" t="s">
-        <v>22</v>
+        <v>333</v>
       </c>
       <c r="C459" t="s">
         <v>5</v>
@@ -7815,10 +7866,10 @@
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B460" t="s">
-        <v>148</v>
+        <v>458</v>
       </c>
       <c r="C460" t="s">
         <v>5</v>
@@ -7826,10 +7877,10 @@
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B461" t="s">
-        <v>49</v>
+        <v>216</v>
       </c>
       <c r="C461" t="s">
         <v>5</v>
@@ -7837,10 +7888,10 @@
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B462" t="s">
-        <v>40</v>
+        <v>224</v>
       </c>
       <c r="C462" t="s">
         <v>5</v>
@@ -7848,10 +7899,10 @@
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B463" t="s">
-        <v>49</v>
+        <v>229</v>
       </c>
       <c r="C463" t="s">
         <v>5</v>
@@ -7859,10 +7910,10 @@
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B464" t="s">
-        <v>49</v>
+        <v>328</v>
       </c>
       <c r="C464" t="s">
         <v>5</v>
@@ -7870,10 +7921,10 @@
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B465" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="C465" t="s">
         <v>5</v>
@@ -7881,10 +7932,10 @@
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B466" t="s">
-        <v>16</v>
+        <v>222</v>
       </c>
       <c r="C466" t="s">
         <v>5</v>
@@ -7892,10 +7943,10 @@
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B467" t="s">
-        <v>40</v>
+        <v>216</v>
       </c>
       <c r="C467" t="s">
         <v>5</v>
@@ -7903,10 +7954,10 @@
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B468" t="s">
-        <v>44</v>
+        <v>556</v>
       </c>
       <c r="C468" t="s">
         <v>5</v>
@@ -7914,10 +7965,10 @@
     </row>
     <row r="469">
       <c r="A469" t="s">
+        <v>557</v>
+      </c>
+      <c r="B469" t="s">
         <v>558</v>
-      </c>
-      <c r="B469" t="s">
-        <v>40</v>
       </c>
       <c r="C469" t="s">
         <v>5</v>
@@ -7928,7 +7979,7 @@
         <v>559</v>
       </c>
       <c r="B470" t="s">
-        <v>40</v>
+        <v>309</v>
       </c>
       <c r="C470" t="s">
         <v>5</v>
@@ -7939,7 +7990,7 @@
         <v>560</v>
       </c>
       <c r="B471" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="C471" t="s">
         <v>5</v>
@@ -7950,7 +8001,7 @@
         <v>561</v>
       </c>
       <c r="B472" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="C472" t="s">
         <v>5</v>
@@ -7961,7 +8012,7 @@
         <v>562</v>
       </c>
       <c r="B473" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C473" t="s">
         <v>5</v>
@@ -7972,7 +8023,7 @@
         <v>563</v>
       </c>
       <c r="B474" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="C474" t="s">
         <v>5</v>
@@ -7983,7 +8034,7 @@
         <v>564</v>
       </c>
       <c r="B475" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="C475" t="s">
         <v>5</v>
@@ -7994,7 +8045,7 @@
         <v>565</v>
       </c>
       <c r="B476" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C476" t="s">
         <v>5</v>
@@ -8005,7 +8056,7 @@
         <v>566</v>
       </c>
       <c r="B477" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="C477" t="s">
         <v>5</v>
@@ -8016,7 +8067,7 @@
         <v>567</v>
       </c>
       <c r="B478" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C478" t="s">
         <v>5</v>
@@ -8027,7 +8078,7 @@
         <v>568</v>
       </c>
       <c r="B479" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="C479" t="s">
         <v>5</v>
@@ -8038,7 +8089,7 @@
         <v>569</v>
       </c>
       <c r="B480" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C480" t="s">
         <v>5</v>
@@ -8049,7 +8100,7 @@
         <v>570</v>
       </c>
       <c r="B481" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C481" t="s">
         <v>5</v>
@@ -8060,7 +8111,7 @@
         <v>571</v>
       </c>
       <c r="B482" t="s">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="C482" t="s">
         <v>5</v>
@@ -8071,7 +8122,7 @@
         <v>572</v>
       </c>
       <c r="B483" t="s">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="C483" t="s">
         <v>5</v>
@@ -8082,7 +8133,7 @@
         <v>573</v>
       </c>
       <c r="B484" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C484" t="s">
         <v>5</v>
@@ -8093,7 +8144,7 @@
         <v>574</v>
       </c>
       <c r="B485" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C485" t="s">
         <v>5</v>
@@ -8104,7 +8155,7 @@
         <v>575</v>
       </c>
       <c r="B486" t="s">
-        <v>165</v>
+        <v>7</v>
       </c>
       <c r="C486" t="s">
         <v>5</v>
@@ -8115,7 +8166,7 @@
         <v>576</v>
       </c>
       <c r="B487" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="C487" t="s">
         <v>5</v>
@@ -8126,7 +8177,7 @@
         <v>577</v>
       </c>
       <c r="B488" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C488" t="s">
         <v>5</v>
@@ -8137,7 +8188,7 @@
         <v>578</v>
       </c>
       <c r="B489" t="s">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="C489" t="s">
         <v>5</v>
@@ -8148,7 +8199,7 @@
         <v>579</v>
       </c>
       <c r="B490" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C490" t="s">
         <v>5</v>
@@ -8159,7 +8210,7 @@
         <v>580</v>
       </c>
       <c r="B491" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C491" t="s">
         <v>5</v>
@@ -8170,7 +8221,7 @@
         <v>581</v>
       </c>
       <c r="B492" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="C492" t="s">
         <v>5</v>
@@ -8181,7 +8232,7 @@
         <v>582</v>
       </c>
       <c r="B493" t="s">
-        <v>194</v>
+        <v>13</v>
       </c>
       <c r="C493" t="s">
         <v>5</v>
@@ -8192,7 +8243,7 @@
         <v>583</v>
       </c>
       <c r="B494" t="s">
-        <v>436</v>
+        <v>63</v>
       </c>
       <c r="C494" t="s">
         <v>5</v>
@@ -8203,7 +8254,7 @@
         <v>584</v>
       </c>
       <c r="B495" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C495" t="s">
         <v>5</v>
@@ -8214,7 +8265,7 @@
         <v>585</v>
       </c>
       <c r="B496" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="C496" t="s">
         <v>5</v>
@@ -8225,7 +8276,7 @@
         <v>586</v>
       </c>
       <c r="B497" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="C497" t="s">
         <v>5</v>
@@ -8236,7 +8287,7 @@
         <v>587</v>
       </c>
       <c r="B498" t="s">
-        <v>167</v>
+        <v>26</v>
       </c>
       <c r="C498" t="s">
         <v>5</v>
@@ -8247,7 +8298,7 @@
         <v>588</v>
       </c>
       <c r="B499" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C499" t="s">
         <v>5</v>
@@ -8258,7 +8309,7 @@
         <v>589</v>
       </c>
       <c r="B500" t="s">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="C500" t="s">
         <v>5</v>
@@ -8269,7 +8320,7 @@
         <v>590</v>
       </c>
       <c r="B501" t="s">
-        <v>151</v>
+        <v>13</v>
       </c>
       <c r="C501" t="s">
         <v>5</v>
@@ -8280,7 +8331,7 @@
         <v>591</v>
       </c>
       <c r="B502" t="s">
-        <v>457</v>
+        <v>88</v>
       </c>
       <c r="C502" t="s">
         <v>5</v>
@@ -8291,7 +8342,7 @@
         <v>592</v>
       </c>
       <c r="B503" t="s">
-        <v>457</v>
+        <v>4</v>
       </c>
       <c r="C503" t="s">
         <v>5</v>
@@ -8302,7 +8353,7 @@
         <v>593</v>
       </c>
       <c r="B504" t="s">
-        <v>457</v>
+        <v>69</v>
       </c>
       <c r="C504" t="s">
         <v>5</v>
@@ -8313,7 +8364,7 @@
         <v>594</v>
       </c>
       <c r="B505" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C505" t="s">
         <v>5</v>
@@ -8324,7 +8375,7 @@
         <v>595</v>
       </c>
       <c r="B506" t="s">
-        <v>349</v>
+        <v>71</v>
       </c>
       <c r="C506" t="s">
         <v>5</v>
@@ -8335,7 +8386,7 @@
         <v>596</v>
       </c>
       <c r="B507" t="s">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="C507" t="s">
         <v>5</v>
@@ -8346,7 +8397,7 @@
         <v>597</v>
       </c>
       <c r="B508" t="s">
-        <v>316</v>
+        <v>184</v>
       </c>
       <c r="C508" t="s">
         <v>5</v>
@@ -8357,7 +8408,7 @@
         <v>598</v>
       </c>
       <c r="B509" t="s">
-        <v>194</v>
+        <v>92</v>
       </c>
       <c r="C509" t="s">
         <v>5</v>
@@ -8368,7 +8419,7 @@
         <v>599</v>
       </c>
       <c r="B510" t="s">
-        <v>438</v>
+        <v>211</v>
       </c>
       <c r="C510" t="s">
         <v>5</v>
@@ -8379,7 +8430,7 @@
         <v>600</v>
       </c>
       <c r="B511" t="s">
-        <v>74</v>
+        <v>453</v>
       </c>
       <c r="C511" t="s">
         <v>5</v>
@@ -8390,7 +8441,7 @@
         <v>601</v>
       </c>
       <c r="B512" t="s">
-        <v>441</v>
+        <v>96</v>
       </c>
       <c r="C512" t="s">
         <v>5</v>
@@ -8401,7 +8452,7 @@
         <v>602</v>
       </c>
       <c r="B513" t="s">
-        <v>438</v>
+        <v>88</v>
       </c>
       <c r="C513" t="s">
         <v>5</v>
@@ -8412,7 +8463,7 @@
         <v>603</v>
       </c>
       <c r="B514" t="s">
-        <v>604</v>
+        <v>90</v>
       </c>
       <c r="C514" t="s">
         <v>5</v>
@@ -8420,10 +8471,10 @@
     </row>
     <row r="515">
       <c r="A515" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B515" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="C515" t="s">
         <v>5</v>
@@ -8431,10 +8482,10 @@
     </row>
     <row r="516">
       <c r="A516" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B516" t="s">
-        <v>292</v>
+        <v>4</v>
       </c>
       <c r="C516" t="s">
         <v>5</v>
@@ -8442,10 +8493,10 @@
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B517" t="s">
-        <v>212</v>
+        <v>71</v>
       </c>
       <c r="C517" t="s">
         <v>5</v>
@@ -8453,10 +8504,10 @@
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B518" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="C518" t="s">
         <v>5</v>
@@ -8464,10 +8515,10 @@
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B519" t="s">
-        <v>194</v>
+        <v>474</v>
       </c>
       <c r="C519" t="s">
         <v>5</v>
@@ -8475,10 +8526,10 @@
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B520" t="s">
-        <v>74</v>
+        <v>474</v>
       </c>
       <c r="C520" t="s">
         <v>5</v>
@@ -8486,10 +8537,10 @@
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B521" t="s">
-        <v>212</v>
+        <v>474</v>
       </c>
       <c r="C521" t="s">
         <v>5</v>
@@ -8497,10 +8548,10 @@
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B522" t="s">
-        <v>197</v>
+        <v>92</v>
       </c>
       <c r="C522" t="s">
         <v>5</v>
@@ -8508,10 +8559,10 @@
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B523" t="s">
-        <v>233</v>
+        <v>366</v>
       </c>
       <c r="C523" t="s">
         <v>5</v>
@@ -8519,10 +8570,10 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B524" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C524" t="s">
         <v>5</v>
@@ -8530,10 +8581,10 @@
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B525" t="s">
-        <v>233</v>
+        <v>333</v>
       </c>
       <c r="C525" t="s">
         <v>5</v>
@@ -8541,10 +8592,10 @@
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B526" t="s">
-        <v>311</v>
+        <v>211</v>
       </c>
       <c r="C526" t="s">
         <v>5</v>
@@ -8552,10 +8603,10 @@
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B527" t="s">
-        <v>74</v>
+        <v>455</v>
       </c>
       <c r="C527" t="s">
         <v>5</v>
@@ -8563,10 +8614,10 @@
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B528" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="C528" t="s">
         <v>5</v>
@@ -8574,10 +8625,10 @@
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B529" t="s">
-        <v>151</v>
+        <v>458</v>
       </c>
       <c r="C529" t="s">
         <v>5</v>
@@ -8585,10 +8636,10 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B530" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="C530" t="s">
         <v>5</v>
@@ -8596,10 +8647,10 @@
     </row>
     <row r="531">
       <c r="A531" t="s">
+        <v>620</v>
+      </c>
+      <c r="B531" t="s">
         <v>621</v>
-      </c>
-      <c r="B531" t="s">
-        <v>349</v>
       </c>
       <c r="C531" t="s">
         <v>5</v>
@@ -8610,7 +8661,7 @@
         <v>622</v>
       </c>
       <c r="B532" t="s">
-        <v>349</v>
+        <v>219</v>
       </c>
       <c r="C532" t="s">
         <v>5</v>
@@ -8621,7 +8672,7 @@
         <v>623</v>
       </c>
       <c r="B533" t="s">
-        <v>74</v>
+        <v>309</v>
       </c>
       <c r="C533" t="s">
         <v>5</v>
@@ -8632,7 +8683,7 @@
         <v>624</v>
       </c>
       <c r="B534" t="s">
-        <v>316</v>
+        <v>229</v>
       </c>
       <c r="C534" t="s">
         <v>5</v>
@@ -8643,7 +8694,7 @@
         <v>625</v>
       </c>
       <c r="B535" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C535" t="s">
         <v>5</v>
@@ -8654,7 +8705,7 @@
         <v>626</v>
       </c>
       <c r="B536" t="s">
-        <v>457</v>
+        <v>211</v>
       </c>
       <c r="C536" t="s">
         <v>5</v>
@@ -8665,7 +8716,7 @@
         <v>627</v>
       </c>
       <c r="B537" t="s">
-        <v>194</v>
+        <v>92</v>
       </c>
       <c r="C537" t="s">
         <v>5</v>
@@ -8676,7 +8727,7 @@
         <v>628</v>
       </c>
       <c r="B538" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="C538" t="s">
         <v>5</v>
@@ -8687,7 +8738,7 @@
         <v>629</v>
       </c>
       <c r="B539" t="s">
-        <v>292</v>
+        <v>214</v>
       </c>
       <c r="C539" t="s">
         <v>5</v>
@@ -8698,7 +8749,7 @@
         <v>630</v>
       </c>
       <c r="B540" t="s">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="C540" t="s">
         <v>5</v>
@@ -8709,7 +8760,7 @@
         <v>631</v>
       </c>
       <c r="B541" t="s">
-        <v>539</v>
+        <v>216</v>
       </c>
       <c r="C541" t="s">
         <v>5</v>
@@ -8720,7 +8771,7 @@
         <v>632</v>
       </c>
       <c r="B542" t="s">
-        <v>288</v>
+        <v>250</v>
       </c>
       <c r="C542" t="s">
         <v>5</v>
@@ -8731,7 +8782,7 @@
         <v>633</v>
       </c>
       <c r="B543" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="C543" t="s">
         <v>5</v>
@@ -8742,7 +8793,7 @@
         <v>634</v>
       </c>
       <c r="B544" t="s">
-        <v>297</v>
+        <v>92</v>
       </c>
       <c r="C544" t="s">
         <v>5</v>
@@ -8753,7 +8804,7 @@
         <v>635</v>
       </c>
       <c r="B545" t="s">
-        <v>306</v>
+        <v>169</v>
       </c>
       <c r="C545" t="s">
         <v>5</v>
@@ -8764,7 +8815,7 @@
         <v>636</v>
       </c>
       <c r="B546" t="s">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="C546" t="s">
         <v>5</v>
@@ -8775,7 +8826,7 @@
         <v>637</v>
       </c>
       <c r="B547" t="s">
-        <v>240</v>
+        <v>453</v>
       </c>
       <c r="C547" t="s">
         <v>5</v>
@@ -8786,7 +8837,7 @@
         <v>638</v>
       </c>
       <c r="B548" t="s">
-        <v>240</v>
+        <v>366</v>
       </c>
       <c r="C548" t="s">
         <v>5</v>
@@ -8797,7 +8848,7 @@
         <v>639</v>
       </c>
       <c r="B549" t="s">
-        <v>306</v>
+        <v>366</v>
       </c>
       <c r="C549" t="s">
         <v>5</v>
@@ -8808,7 +8859,7 @@
         <v>640</v>
       </c>
       <c r="B550" t="s">
-        <v>245</v>
+        <v>92</v>
       </c>
       <c r="C550" t="s">
         <v>5</v>
@@ -8819,7 +8870,7 @@
         <v>641</v>
       </c>
       <c r="B551" t="s">
-        <v>642</v>
+        <v>333</v>
       </c>
       <c r="C551" t="s">
         <v>5</v>
@@ -8827,10 +8878,10 @@
     </row>
     <row r="552">
       <c r="A552" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B552" t="s">
-        <v>642</v>
+        <v>211</v>
       </c>
       <c r="C552" t="s">
         <v>5</v>
@@ -8838,10 +8889,10 @@
     </row>
     <row r="553">
       <c r="A553" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B553" t="s">
-        <v>642</v>
+        <v>474</v>
       </c>
       <c r="C553" t="s">
         <v>5</v>
@@ -8849,10 +8900,10 @@
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B554" t="s">
-        <v>642</v>
+        <v>211</v>
       </c>
       <c r="C554" t="s">
         <v>5</v>
@@ -8860,10 +8911,10 @@
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B555" t="s">
-        <v>647</v>
+        <v>211</v>
       </c>
       <c r="C555" t="s">
         <v>5</v>
@@ -8871,10 +8922,10 @@
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B556" t="s">
-        <v>649</v>
+        <v>309</v>
       </c>
       <c r="C556" t="s">
         <v>5</v>
@@ -8882,10 +8933,10 @@
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B557" t="s">
-        <v>252</v>
+        <v>307</v>
       </c>
       <c r="C557" t="s">
         <v>5</v>
@@ -8893,10 +8944,10 @@
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B558" t="s">
-        <v>642</v>
+        <v>556</v>
       </c>
       <c r="C558" t="s">
         <v>5</v>
@@ -8904,10 +8955,10 @@
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B559" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="C559" t="s">
         <v>5</v>
@@ -8915,10 +8966,10 @@
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B560" t="s">
-        <v>647</v>
+        <v>319</v>
       </c>
       <c r="C560" t="s">
         <v>5</v>
@@ -8926,10 +8977,10 @@
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B561" t="s">
-        <v>268</v>
+        <v>314</v>
       </c>
       <c r="C561" t="s">
         <v>5</v>
@@ -8937,10 +8988,10 @@
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B562" t="s">
-        <v>656</v>
+        <v>323</v>
       </c>
       <c r="C562" t="s">
         <v>5</v>
@@ -8948,10 +8999,10 @@
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B563" t="s">
-        <v>656</v>
+        <v>244</v>
       </c>
       <c r="C563" t="s">
         <v>5</v>
@@ -8959,7 +9010,7 @@
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B564" t="s">
         <v>257</v>
@@ -8970,10 +9021,10 @@
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B565" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C565" t="s">
         <v>5</v>
@@ -8981,10 +9032,10 @@
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B566" t="s">
-        <v>268</v>
+        <v>323</v>
       </c>
       <c r="C566" t="s">
         <v>5</v>
@@ -8992,10 +9043,10 @@
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B567" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="C567" t="s">
         <v>5</v>
@@ -9003,10 +9054,10 @@
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B568" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C568" t="s">
         <v>5</v>
@@ -9014,10 +9065,10 @@
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B569" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C569" t="s">
         <v>5</v>
@@ -9025,10 +9076,10 @@
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B570" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="C570" t="s">
         <v>5</v>
@@ -9036,10 +9087,10 @@
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B571" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="C571" t="s">
         <v>5</v>
@@ -9047,10 +9098,10 @@
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="B572" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="C572" t="s">
         <v>5</v>
@@ -9058,10 +9109,10 @@
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="B573" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C573" t="s">
         <v>5</v>
@@ -9069,10 +9120,10 @@
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="B574" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C574" t="s">
         <v>5</v>
@@ -9080,10 +9131,10 @@
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="B575" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="C575" t="s">
         <v>5</v>
@@ -9091,10 +9142,10 @@
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="B576" t="s">
-        <v>677</v>
+        <v>301</v>
       </c>
       <c r="C576" t="s">
         <v>5</v>
@@ -9102,10 +9153,10 @@
     </row>
     <row r="577">
       <c r="A577" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="B577" t="s">
-        <v>273</v>
+        <v>664</v>
       </c>
       <c r="C577" t="s">
         <v>5</v>
@@ -9113,10 +9164,10 @@
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="B578" t="s">
-        <v>680</v>
+        <v>285</v>
       </c>
       <c r="C578" t="s">
         <v>5</v>
@@ -9124,10 +9175,10 @@
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="B579" t="s">
-        <v>259</v>
+        <v>673</v>
       </c>
       <c r="C579" t="s">
         <v>5</v>
@@ -9135,10 +9186,10 @@
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="B580" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="C580" t="s">
         <v>5</v>
@@ -9146,10 +9197,10 @@
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="B581" t="s">
-        <v>685</v>
+        <v>274</v>
       </c>
       <c r="C581" t="s">
         <v>5</v>
@@ -9157,10 +9208,10 @@
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="B582" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C582" t="s">
         <v>5</v>
@@ -9168,10 +9219,10 @@
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="B583" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C583" t="s">
         <v>5</v>
@@ -9179,10 +9230,10 @@
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="B584" t="s">
-        <v>683</v>
+        <v>297</v>
       </c>
       <c r="C584" t="s">
         <v>5</v>
@@ -9190,10 +9241,10 @@
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="B585" t="s">
-        <v>273</v>
+        <v>680</v>
       </c>
       <c r="C585" t="s">
         <v>5</v>
@@ -9201,10 +9252,10 @@
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="B586" t="s">
-        <v>273</v>
+        <v>680</v>
       </c>
       <c r="C586" t="s">
         <v>5</v>
@@ -9212,10 +9263,10 @@
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="B587" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="C587" t="s">
         <v>5</v>
@@ -9223,10 +9274,10 @@
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="B588" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="C588" t="s">
         <v>5</v>
@@ -9234,10 +9285,10 @@
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="B589" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="C589" t="s">
         <v>5</v>
@@ -9245,10 +9296,10 @@
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="B590" t="s">
-        <v>257</v>
+        <v>689</v>
       </c>
       <c r="C590" t="s">
         <v>5</v>
@@ -9256,10 +9307,10 @@
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="B591" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C591" t="s">
         <v>5</v>
@@ -9267,10 +9318,10 @@
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="B592" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="C592" t="s">
         <v>5</v>
@@ -9278,10 +9329,10 @@
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="B593" t="s">
-        <v>257</v>
+        <v>694</v>
       </c>
       <c r="C593" t="s">
         <v>5</v>
@@ -9289,10 +9340,10 @@
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="B594" t="s">
-        <v>683</v>
+        <v>290</v>
       </c>
       <c r="C594" t="s">
         <v>5</v>
@@ -9300,10 +9351,10 @@
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="B595" t="s">
-        <v>250</v>
+        <v>697</v>
       </c>
       <c r="C595" t="s">
         <v>5</v>
@@ -9311,10 +9362,10 @@
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="B596" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C596" t="s">
         <v>5</v>
@@ -9322,10 +9373,10 @@
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="B597" t="s">
-        <v>252</v>
+        <v>700</v>
       </c>
       <c r="C597" t="s">
         <v>5</v>
@@ -9333,10 +9384,10 @@
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="B598" t="s">
-        <v>240</v>
+        <v>702</v>
       </c>
       <c r="C598" t="s">
         <v>5</v>
@@ -9344,10 +9395,10 @@
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B599" t="s">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="C599" t="s">
         <v>5</v>
@@ -9355,10 +9406,10 @@
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B600" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C600" t="s">
         <v>5</v>
@@ -9366,10 +9417,10 @@
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B601" t="s">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="C601" t="s">
         <v>5</v>
@@ -9377,10 +9428,10 @@
     </row>
     <row r="602">
       <c r="A602" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B602" t="s">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="C602" t="s">
         <v>5</v>
@@ -9388,10 +9439,10 @@
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B603" t="s">
-        <v>539</v>
+        <v>290</v>
       </c>
       <c r="C603" t="s">
         <v>5</v>
@@ -9399,10 +9450,10 @@
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B604" t="s">
-        <v>220</v>
+        <v>709</v>
       </c>
       <c r="C604" t="s">
         <v>5</v>
@@ -9410,10 +9461,10 @@
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B605" t="s">
-        <v>290</v>
+        <v>711</v>
       </c>
       <c r="C605" t="s">
         <v>5</v>
@@ -9421,10 +9472,10 @@
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B606" t="s">
-        <v>230</v>
+        <v>713</v>
       </c>
       <c r="C606" t="s">
         <v>5</v>
@@ -9432,10 +9483,10 @@
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B607" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="C607" t="s">
         <v>5</v>
@@ -9443,10 +9494,10 @@
     </row>
     <row r="608">
       <c r="A608" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B608" t="s">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="C608" t="s">
         <v>5</v>
@@ -9454,10 +9505,10 @@
     </row>
     <row r="609">
       <c r="A609" t="s">
+        <v>716</v>
+      </c>
+      <c r="B609" t="s">
         <v>717</v>
-      </c>
-      <c r="B609" t="s">
-        <v>202</v>
       </c>
       <c r="C609" t="s">
         <v>5</v>
@@ -9468,7 +9519,7 @@
         <v>718</v>
       </c>
       <c r="B610" t="s">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="C610" t="s">
         <v>5</v>
@@ -9479,7 +9530,7 @@
         <v>719</v>
       </c>
       <c r="B611" t="s">
-        <v>604</v>
+        <v>700</v>
       </c>
       <c r="C611" t="s">
         <v>5</v>
@@ -9490,7 +9541,7 @@
         <v>720</v>
       </c>
       <c r="B612" t="s">
-        <v>202</v>
+        <v>267</v>
       </c>
       <c r="C612" t="s">
         <v>5</v>
@@ -9501,7 +9552,7 @@
         <v>721</v>
       </c>
       <c r="B613" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C613" t="s">
         <v>5</v>
@@ -9512,7 +9563,7 @@
         <v>722</v>
       </c>
       <c r="B614" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="C614" t="s">
         <v>5</v>
@@ -9523,7 +9574,7 @@
         <v>723</v>
       </c>
       <c r="B615" t="s">
-        <v>724</v>
+        <v>257</v>
       </c>
       <c r="C615" t="s">
         <v>5</v>
@@ -9531,10 +9582,10 @@
     </row>
     <row r="616">
       <c r="A616" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B616" t="s">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="C616" t="s">
         <v>5</v>
@@ -9542,10 +9593,10 @@
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B617" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="C617" t="s">
         <v>5</v>
@@ -9553,10 +9604,10 @@
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B618" t="s">
-        <v>724</v>
+        <v>237</v>
       </c>
       <c r="C618" t="s">
         <v>5</v>
@@ -9564,10 +9615,10 @@
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B619" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C619" t="s">
         <v>5</v>
@@ -9575,10 +9626,10 @@
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B620" t="s">
-        <v>245</v>
+        <v>556</v>
       </c>
       <c r="C620" t="s">
         <v>5</v>
@@ -9586,10 +9637,10 @@
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B621" t="s">
-        <v>306</v>
+        <v>237</v>
       </c>
       <c r="C621" t="s">
         <v>5</v>
@@ -9597,10 +9648,10 @@
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B622" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C622" t="s">
         <v>5</v>
@@ -9608,10 +9659,10 @@
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B623" t="s">
-        <v>199</v>
+        <v>247</v>
       </c>
       <c r="C623" t="s">
         <v>5</v>
@@ -9619,10 +9670,10 @@
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B624" t="s">
-        <v>199</v>
+        <v>305</v>
       </c>
       <c r="C624" t="s">
         <v>5</v>
@@ -9630,10 +9681,10 @@
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B625" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="C625" t="s">
         <v>5</v>
@@ -9641,10 +9692,10 @@
     </row>
     <row r="626">
       <c r="A626" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B626" t="s">
-        <v>441</v>
+        <v>219</v>
       </c>
       <c r="C626" t="s">
         <v>5</v>
@@ -9652,10 +9703,10 @@
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B627" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="C627" t="s">
         <v>5</v>
@@ -9663,10 +9714,10 @@
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B628" t="s">
-        <v>205</v>
+        <v>621</v>
       </c>
       <c r="C628" t="s">
         <v>5</v>
@@ -9674,10 +9725,10 @@
     </row>
     <row r="629">
       <c r="A629" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B629" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="C629" t="s">
         <v>5</v>
@@ -9685,10 +9736,10 @@
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B630" t="s">
-        <v>205</v>
+        <v>314</v>
       </c>
       <c r="C630" t="s">
         <v>5</v>
@@ -9696,10 +9747,10 @@
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B631" t="s">
-        <v>194</v>
+        <v>317</v>
       </c>
       <c r="C631" t="s">
         <v>5</v>
@@ -9707,10 +9758,10 @@
     </row>
     <row r="632">
       <c r="A632" t="s">
+        <v>740</v>
+      </c>
+      <c r="B632" t="s">
         <v>741</v>
-      </c>
-      <c r="B632" t="s">
-        <v>72</v>
       </c>
       <c r="C632" t="s">
         <v>5</v>
@@ -9721,7 +9772,7 @@
         <v>742</v>
       </c>
       <c r="B633" t="s">
-        <v>53</v>
+        <v>314</v>
       </c>
       <c r="C633" t="s">
         <v>5</v>
@@ -9732,7 +9783,7 @@
         <v>743</v>
       </c>
       <c r="B634" t="s">
-        <v>72</v>
+        <v>312</v>
       </c>
       <c r="C634" t="s">
         <v>5</v>
@@ -9743,7 +9794,7 @@
         <v>744</v>
       </c>
       <c r="B635" t="s">
-        <v>78</v>
+        <v>741</v>
       </c>
       <c r="C635" t="s">
         <v>5</v>
@@ -9754,7 +9805,7 @@
         <v>745</v>
       </c>
       <c r="B636" t="s">
-        <v>436</v>
+        <v>264</v>
       </c>
       <c r="C636" t="s">
         <v>5</v>
@@ -9765,7 +9816,7 @@
         <v>746</v>
       </c>
       <c r="B637" t="s">
-        <v>457</v>
+        <v>262</v>
       </c>
       <c r="C637" t="s">
         <v>5</v>
@@ -9776,7 +9827,7 @@
         <v>747</v>
       </c>
       <c r="B638" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="C638" t="s">
         <v>5</v>
@@ -9787,7 +9838,7 @@
         <v>748</v>
       </c>
       <c r="B639" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C639" t="s">
         <v>5</v>
@@ -9798,7 +9849,7 @@
         <v>749</v>
       </c>
       <c r="B640" t="s">
-        <v>167</v>
+        <v>216</v>
       </c>
       <c r="C640" t="s">
         <v>5</v>
@@ -9809,7 +9860,7 @@
         <v>750</v>
       </c>
       <c r="B641" t="s">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="C641" t="s">
         <v>5</v>
@@ -9820,7 +9871,7 @@
         <v>751</v>
       </c>
       <c r="B642" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="C642" t="s">
         <v>5</v>
@@ -9831,7 +9882,7 @@
         <v>752</v>
       </c>
       <c r="B643" t="s">
-        <v>51</v>
+        <v>458</v>
       </c>
       <c r="C643" t="s">
         <v>5</v>
@@ -9842,7 +9893,7 @@
         <v>753</v>
       </c>
       <c r="B644" t="s">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="C644" t="s">
         <v>5</v>
@@ -9853,7 +9904,7 @@
         <v>754</v>
       </c>
       <c r="B645" t="s">
-        <v>72</v>
+        <v>222</v>
       </c>
       <c r="C645" t="s">
         <v>5</v>
@@ -9864,7 +9915,7 @@
         <v>755</v>
       </c>
       <c r="B646" t="s">
-        <v>316</v>
+        <v>214</v>
       </c>
       <c r="C646" t="s">
         <v>5</v>
@@ -9875,7 +9926,7 @@
         <v>756</v>
       </c>
       <c r="B647" t="s">
-        <v>311</v>
+        <v>222</v>
       </c>
       <c r="C647" t="s">
         <v>5</v>
@@ -9886,7 +9937,7 @@
         <v>757</v>
       </c>
       <c r="B648" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C648" t="s">
         <v>5</v>
@@ -9897,7 +9948,7 @@
         <v>758</v>
       </c>
       <c r="B649" t="s">
-        <v>199</v>
+        <v>90</v>
       </c>
       <c r="C649" t="s">
         <v>5</v>
@@ -9908,7 +9959,7 @@
         <v>759</v>
       </c>
       <c r="B650" t="s">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="C650" t="s">
         <v>5</v>
@@ -9919,7 +9970,7 @@
         <v>760</v>
       </c>
       <c r="B651" t="s">
-        <v>207</v>
+        <v>90</v>
       </c>
       <c r="C651" t="s">
         <v>5</v>
@@ -9930,7 +9981,7 @@
         <v>761</v>
       </c>
       <c r="B652" t="s">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="C652" t="s">
         <v>5</v>
@@ -9941,7 +9992,7 @@
         <v>762</v>
       </c>
       <c r="B653" t="s">
-        <v>212</v>
+        <v>453</v>
       </c>
       <c r="C653" t="s">
         <v>5</v>
@@ -9952,7 +10003,7 @@
         <v>763</v>
       </c>
       <c r="B654" t="s">
-        <v>197</v>
+        <v>474</v>
       </c>
       <c r="C654" t="s">
         <v>5</v>
@@ -9963,7 +10014,7 @@
         <v>764</v>
       </c>
       <c r="B655" t="s">
-        <v>223</v>
+        <v>333</v>
       </c>
       <c r="C655" t="s">
         <v>5</v>
@@ -9974,7 +10025,7 @@
         <v>765</v>
       </c>
       <c r="B656" t="s">
-        <v>539</v>
+        <v>333</v>
       </c>
       <c r="C656" t="s">
         <v>5</v>
@@ -9985,7 +10036,7 @@
         <v>766</v>
       </c>
       <c r="B657" t="s">
-        <v>541</v>
+        <v>184</v>
       </c>
       <c r="C657" t="s">
         <v>5</v>
@@ -9996,7 +10047,7 @@
         <v>767</v>
       </c>
       <c r="B658" t="s">
-        <v>292</v>
+        <v>96</v>
       </c>
       <c r="C658" t="s">
         <v>5</v>
@@ -10007,7 +10058,7 @@
         <v>768</v>
       </c>
       <c r="B659" t="s">
-        <v>292</v>
+        <v>4</v>
       </c>
       <c r="C659" t="s">
         <v>5</v>
@@ -10018,7 +10069,7 @@
         <v>769</v>
       </c>
       <c r="B660" t="s">
-        <v>199</v>
+        <v>69</v>
       </c>
       <c r="C660" t="s">
         <v>5</v>
@@ -10029,7 +10080,7 @@
         <v>770</v>
       </c>
       <c r="B661" t="s">
-        <v>209</v>
+        <v>4</v>
       </c>
       <c r="C661" t="s">
         <v>5</v>
@@ -10040,7 +10091,7 @@
         <v>771</v>
       </c>
       <c r="B662" t="s">
-        <v>207</v>
+        <v>90</v>
       </c>
       <c r="C662" t="s">
         <v>5</v>
@@ -10051,7 +10102,7 @@
         <v>772</v>
       </c>
       <c r="B663" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="C663" t="s">
         <v>5</v>
@@ -10062,7 +10113,7 @@
         <v>773</v>
       </c>
       <c r="B664" t="s">
-        <v>212</v>
+        <v>328</v>
       </c>
       <c r="C664" t="s">
         <v>5</v>
@@ -10073,7 +10124,7 @@
         <v>774</v>
       </c>
       <c r="B665" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C665" t="s">
         <v>5</v>
@@ -10084,7 +10135,7 @@
         <v>775</v>
       </c>
       <c r="B666" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="C666" t="s">
         <v>5</v>
@@ -10095,7 +10146,7 @@
         <v>776</v>
       </c>
       <c r="B667" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="C667" t="s">
         <v>5</v>
@@ -10106,7 +10157,7 @@
         <v>777</v>
       </c>
       <c r="B668" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="C668" t="s">
         <v>5</v>
@@ -10117,7 +10168,7 @@
         <v>778</v>
       </c>
       <c r="B669" t="s">
-        <v>539</v>
+        <v>229</v>
       </c>
       <c r="C669" t="s">
         <v>5</v>
@@ -10128,7 +10179,7 @@
         <v>779</v>
       </c>
       <c r="B670" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="C670" t="s">
         <v>5</v>
@@ -10139,7 +10190,7 @@
         <v>780</v>
       </c>
       <c r="B671" t="s">
-        <v>541</v>
+        <v>214</v>
       </c>
       <c r="C671" t="s">
         <v>5</v>
@@ -10150,7 +10201,7 @@
         <v>781</v>
       </c>
       <c r="B672" t="s">
-        <v>541</v>
+        <v>240</v>
       </c>
       <c r="C672" t="s">
         <v>5</v>
@@ -10161,7 +10212,7 @@
         <v>782</v>
       </c>
       <c r="B673" t="s">
-        <v>247</v>
+        <v>556</v>
       </c>
       <c r="C673" t="s">
         <v>5</v>
@@ -10172,7 +10223,7 @@
         <v>783</v>
       </c>
       <c r="B674" t="s">
-        <v>247</v>
+        <v>558</v>
       </c>
       <c r="C674" t="s">
         <v>5</v>
@@ -10183,7 +10234,7 @@
         <v>784</v>
       </c>
       <c r="B675" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C675" t="s">
         <v>5</v>
@@ -10194,7 +10245,7 @@
         <v>785</v>
       </c>
       <c r="B676" t="s">
-        <v>642</v>
+        <v>309</v>
       </c>
       <c r="C676" t="s">
         <v>5</v>
@@ -10205,7 +10256,7 @@
         <v>786</v>
       </c>
       <c r="B677" t="s">
-        <v>642</v>
+        <v>216</v>
       </c>
       <c r="C677" t="s">
         <v>5</v>
@@ -10216,7 +10267,7 @@
         <v>787</v>
       </c>
       <c r="B678" t="s">
-        <v>647</v>
+        <v>226</v>
       </c>
       <c r="C678" t="s">
         <v>5</v>
@@ -10227,7 +10278,7 @@
         <v>788</v>
       </c>
       <c r="B679" t="s">
-        <v>649</v>
+        <v>224</v>
       </c>
       <c r="C679" t="s">
         <v>5</v>
@@ -10238,7 +10289,7 @@
         <v>789</v>
       </c>
       <c r="B680" t="s">
-        <v>247</v>
+        <v>366</v>
       </c>
       <c r="C680" t="s">
         <v>5</v>
@@ -10249,7 +10300,7 @@
         <v>790</v>
       </c>
       <c r="B681" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="C681" t="s">
         <v>5</v>
@@ -10260,7 +10311,7 @@
         <v>791</v>
       </c>
       <c r="B682" t="s">
-        <v>724</v>
+        <v>229</v>
       </c>
       <c r="C682" t="s">
         <v>5</v>
@@ -10271,7 +10322,7 @@
         <v>792</v>
       </c>
       <c r="B683" t="s">
-        <v>252</v>
+        <v>214</v>
       </c>
       <c r="C683" t="s">
         <v>5</v>
@@ -10282,7 +10333,7 @@
         <v>793</v>
       </c>
       <c r="B684" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="C684" t="s">
         <v>5</v>
@@ -10293,7 +10344,7 @@
         <v>794</v>
       </c>
       <c r="B685" t="s">
-        <v>284</v>
+        <v>216</v>
       </c>
       <c r="C685" t="s">
         <v>5</v>
@@ -10304,7 +10355,7 @@
         <v>795</v>
       </c>
       <c r="B686" t="s">
-        <v>284</v>
+        <v>556</v>
       </c>
       <c r="C686" t="s">
         <v>5</v>
@@ -10315,7 +10366,7 @@
         <v>796</v>
       </c>
       <c r="B687" t="s">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="C687" t="s">
         <v>5</v>
@@ -10326,7 +10377,7 @@
         <v>797</v>
       </c>
       <c r="B688" t="s">
-        <v>243</v>
+        <v>558</v>
       </c>
       <c r="C688" t="s">
         <v>5</v>
@@ -10337,7 +10388,7 @@
         <v>798</v>
       </c>
       <c r="B689" t="s">
-        <v>247</v>
+        <v>558</v>
       </c>
       <c r="C689" t="s">
         <v>5</v>
@@ -10348,7 +10399,7 @@
         <v>799</v>
       </c>
       <c r="B690" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="C690" t="s">
         <v>5</v>
@@ -10359,7 +10410,7 @@
         <v>800</v>
       </c>
       <c r="B691" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="C691" t="s">
         <v>5</v>
@@ -10370,7 +10421,7 @@
         <v>801</v>
       </c>
       <c r="B692" t="s">
-        <v>802</v>
+        <v>312</v>
       </c>
       <c r="C692" t="s">
         <v>5</v>
@@ -10378,10 +10429,10 @@
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B693" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="C693" t="s">
         <v>5</v>
@@ -10389,10 +10440,10 @@
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B694" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="C694" t="s">
         <v>5</v>
@@ -10400,10 +10451,10 @@
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B695" t="s">
-        <v>806</v>
+        <v>664</v>
       </c>
       <c r="C695" t="s">
         <v>5</v>
@@ -10411,12 +10462,199 @@
     </row>
     <row r="696">
       <c r="A696" t="s">
+        <v>805</v>
+      </c>
+      <c r="B696" t="s">
+        <v>666</v>
+      </c>
+      <c r="C696" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="s">
+        <v>806</v>
+      </c>
+      <c r="B697" t="s">
+        <v>264</v>
+      </c>
+      <c r="C697" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="s">
         <v>807</v>
       </c>
-      <c r="B696" t="s">
-        <v>647</v>
-      </c>
-      <c r="C696" t="s">
+      <c r="B698" t="s">
+        <v>264</v>
+      </c>
+      <c r="C698" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="s">
+        <v>808</v>
+      </c>
+      <c r="B699" t="s">
+        <v>741</v>
+      </c>
+      <c r="C699" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="s">
+        <v>809</v>
+      </c>
+      <c r="B700" t="s">
+        <v>269</v>
+      </c>
+      <c r="C700" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="s">
+        <v>810</v>
+      </c>
+      <c r="B701" t="s">
+        <v>269</v>
+      </c>
+      <c r="C701" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="s">
+        <v>811</v>
+      </c>
+      <c r="B702" t="s">
+        <v>301</v>
+      </c>
+      <c r="C702" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="s">
+        <v>812</v>
+      </c>
+      <c r="B703" t="s">
+        <v>301</v>
+      </c>
+      <c r="C703" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="s">
+        <v>813</v>
+      </c>
+      <c r="B704" t="s">
+        <v>264</v>
+      </c>
+      <c r="C704" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="s">
+        <v>814</v>
+      </c>
+      <c r="B705" t="s">
+        <v>260</v>
+      </c>
+      <c r="C705" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="s">
+        <v>815</v>
+      </c>
+      <c r="B706" t="s">
+        <v>264</v>
+      </c>
+      <c r="C706" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="s">
+        <v>816</v>
+      </c>
+      <c r="B707" t="s">
+        <v>301</v>
+      </c>
+      <c r="C707" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="s">
+        <v>817</v>
+      </c>
+      <c r="B708" t="s">
+        <v>301</v>
+      </c>
+      <c r="C708" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="s">
+        <v>818</v>
+      </c>
+      <c r="B709" t="s">
+        <v>819</v>
+      </c>
+      <c r="C709" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="s">
+        <v>820</v>
+      </c>
+      <c r="B710" t="s">
+        <v>666</v>
+      </c>
+      <c r="C710" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="s">
+        <v>821</v>
+      </c>
+      <c r="B711" t="s">
+        <v>666</v>
+      </c>
+      <c r="C711" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="s">
+        <v>822</v>
+      </c>
+      <c r="B712" t="s">
+        <v>823</v>
+      </c>
+      <c r="C712" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="s">
+        <v>824</v>
+      </c>
+      <c r="B713" t="s">
+        <v>664</v>
+      </c>
+      <c r="C713" t="s">
         <v>5</v>
       </c>
     </row>

--- a/data/GreatLink/US Income and Growth Fund (Dis).xlsx
+++ b/data/GreatLink/US Income and Growth Fund (Dis).xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PriceHistory" sheetId="1" r:id="GemRid918114"/>
+    <sheet name="PriceHistory" sheetId="1" r:id="GemRid602688"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="854">
   <si>
     <t>Price Date</t>
   </si>
@@ -26,15 +26,165 @@
     <t>Currency - Unit Level</t>
   </si>
   <si>
+    <t>09/04/2026</t>
+  </si>
+  <si>
+    <t>0.989</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>0.987</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>0.966</t>
+  </si>
+  <si>
+    <t>06/04/2026</t>
+  </si>
+  <si>
+    <t>0.959</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>01/04/2026</t>
+  </si>
+  <si>
+    <t>0.963</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>0.948</t>
+  </si>
+  <si>
+    <t>30/03/2026</t>
+  </si>
+  <si>
+    <t>0.944</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>26/03/2026</t>
+  </si>
+  <si>
+    <t>0.961</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
+    <t>0.971</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>0.965</t>
+  </si>
+  <si>
+    <t>23/03/2026</t>
+  </si>
+  <si>
+    <t>0.970</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>0.968</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>0.975</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>0.984</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>0.980</t>
+  </si>
+  <si>
+    <t>13/03/2026</t>
+  </si>
+  <si>
+    <t>0.976</t>
+  </si>
+  <si>
+    <t>12/03/2026</t>
+  </si>
+  <si>
+    <t>0.978</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>0.990</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>05/03/2026</t>
+  </si>
+  <si>
+    <t>0.994</t>
+  </si>
+  <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
+    <t>0.992</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>0.986</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>0.996</t>
+  </si>
+  <si>
     <t>27/02/2026</t>
   </si>
   <si>
     <t>0.997</t>
   </si>
   <si>
-    <t>SGD</t>
-  </si>
-  <si>
     <t>26/02/2026</t>
   </si>
   <si>
@@ -224,9 +374,6 @@
     <t>18/12/2025</t>
   </si>
   <si>
-    <t>0.994</t>
-  </si>
-  <si>
     <t>17/12/2025</t>
   </si>
   <si>
@@ -305,9 +452,6 @@
     <t>18/11/2025</t>
   </si>
   <si>
-    <t>0.996</t>
-  </si>
-  <si>
     <t>17/11/2025</t>
   </si>
   <si>
@@ -524,9 +668,6 @@
     <t>21/08/2025</t>
   </si>
   <si>
-    <t>0.992</t>
-  </si>
-  <si>
     <t>20/08/2025</t>
   </si>
   <si>
@@ -650,18 +791,12 @@
     <t>26/06/2025</t>
   </si>
   <si>
-    <t>0.986</t>
-  </si>
-  <si>
     <t>25/06/2025</t>
   </si>
   <si>
     <t>24/06/2025</t>
   </si>
   <si>
-    <t>0.980</t>
-  </si>
-  <si>
     <t>23/06/2025</t>
   </si>
   <si>
@@ -749,27 +884,18 @@
     <t>26/05/2025</t>
   </si>
   <si>
-    <t>0.961</t>
-  </si>
-  <si>
     <t>23/05/2025</t>
   </si>
   <si>
     <t>22/05/2025</t>
   </si>
   <si>
-    <t>0.966</t>
-  </si>
-  <si>
     <t>21/05/2025</t>
   </si>
   <si>
     <t>20/05/2025</t>
   </si>
   <si>
-    <t>0.975</t>
-  </si>
-  <si>
     <t>19/05/2025</t>
   </si>
   <si>
@@ -932,30 +1058,18 @@
     <t>27/03/2025</t>
   </si>
   <si>
-    <t>0.965</t>
-  </si>
-  <si>
     <t>26/03/2025</t>
   </si>
   <si>
-    <t>0.968</t>
-  </si>
-  <si>
     <t>25/03/2025</t>
   </si>
   <si>
-    <t>0.971</t>
-  </si>
-  <si>
     <t>24/03/2025</t>
   </si>
   <si>
     <t>21/03/2025</t>
   </si>
   <si>
-    <t>0.959</t>
-  </si>
-  <si>
     <t>20/03/2025</t>
   </si>
   <si>
@@ -974,9 +1088,6 @@
     <t>17/03/2025</t>
   </si>
   <si>
-    <t>0.963</t>
-  </si>
-  <si>
     <t>14/03/2025</t>
   </si>
   <si>
@@ -1001,9 +1112,6 @@
     <t>06/03/2025</t>
   </si>
   <si>
-    <t>0.978</t>
-  </si>
-  <si>
     <t>05/03/2025</t>
   </si>
   <si>
@@ -1016,9 +1124,6 @@
     <t>28/02/2025</t>
   </si>
   <si>
-    <t>0.987</t>
-  </si>
-  <si>
     <t>27/02/2025</t>
   </si>
   <si>
@@ -1376,15 +1481,9 @@
     <t>12/09/2024</t>
   </si>
   <si>
-    <t>0.990</t>
-  </si>
-  <si>
     <t>11/09/2024</t>
   </si>
   <si>
-    <t>0.984</t>
-  </si>
-  <si>
     <t>10/09/2024</t>
   </si>
   <si>
@@ -1439,9 +1538,6 @@
     <t>19/08/2024</t>
   </si>
   <si>
-    <t>0.989</t>
-  </si>
-  <si>
     <t>16/08/2024</t>
   </si>
   <si>
@@ -1691,9 +1787,6 @@
     <t>19/04/2024</t>
   </si>
   <si>
-    <t>0.970</t>
-  </si>
-  <si>
     <t>18/04/2024</t>
   </si>
   <si>
@@ -1880,9 +1973,6 @@
     <t>19/01/2024</t>
   </si>
   <si>
-    <t>0.976</t>
-  </si>
-  <si>
     <t>18/01/2024</t>
   </si>
   <si>
@@ -2013,9 +2103,6 @@
   </si>
   <si>
     <t>20/11/2023</t>
-  </si>
-  <si>
-    <t>0.948</t>
   </si>
   <si>
     <t>17/11/2023</t>
@@ -2875,7 +2962,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -2883,10 +2970,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
         <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -2908,7 +2995,7 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -2916,10 +3003,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -2927,10 +3014,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -2938,10 +3025,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -2949,10 +3036,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -2960,10 +3047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -2971,10 +3058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -2982,10 +3069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -2993,10 +3080,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -3004,10 +3091,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
@@ -3015,10 +3102,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -3026,10 +3113,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -3037,10 +3124,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -3048,10 +3135,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -3059,10 +3146,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -3070,10 +3157,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
@@ -3081,10 +3168,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
@@ -3092,10 +3179,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -3103,10 +3190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
@@ -3114,10 +3201,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
@@ -3125,10 +3212,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -3136,10 +3223,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -3147,10 +3234,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -3158,10 +3245,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -3169,10 +3256,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -3180,10 +3267,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -3191,10 +3278,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -3202,10 +3289,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -3213,10 +3300,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -3224,10 +3311,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -3235,10 +3322,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -3246,10 +3333,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
@@ -3257,10 +3344,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
@@ -3268,10 +3355,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -3279,10 +3366,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -3290,10 +3377,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -3301,10 +3388,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -3312,10 +3399,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B46" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
@@ -3323,10 +3410,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
@@ -3334,10 +3421,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="C48" t="s">
         <v>5</v>
@@ -3345,10 +3432,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B49" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
@@ -3356,10 +3443,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -3367,10 +3454,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -3378,10 +3465,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B52" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
@@ -3389,10 +3476,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="C53" t="s">
         <v>5</v>
@@ -3400,10 +3487,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="B54" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
@@ -3411,10 +3498,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>91</v>
+      </c>
+      <c r="B55" t="s">
         <v>76</v>
-      </c>
-      <c r="B55" t="s">
-        <v>37</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
@@ -3422,10 +3509,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="C56" t="s">
         <v>5</v>
@@ -3433,10 +3520,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
@@ -3444,10 +3531,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
@@ -3455,10 +3542,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="C59" t="s">
         <v>5</v>
@@ -3466,10 +3553,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B60" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
@@ -3477,10 +3564,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
@@ -3488,10 +3575,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
@@ -3499,10 +3586,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="B63" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -3510,10 +3597,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="B64" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -3521,10 +3608,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -3532,10 +3619,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="B66" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -3543,7 +3630,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="B67" t="s">
         <v>90</v>
@@ -3554,10 +3641,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C68" t="s">
         <v>5</v>
@@ -3565,10 +3652,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C69" t="s">
         <v>5</v>
@@ -3576,10 +3663,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="C70" t="s">
         <v>5</v>
@@ -3587,10 +3674,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B71" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -3598,10 +3685,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B72" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="C72" t="s">
         <v>5</v>
@@ -3609,10 +3696,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="B73" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="C73" t="s">
         <v>5</v>
@@ -3620,10 +3707,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B74" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C74" t="s">
         <v>5</v>
@@ -3631,10 +3718,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B75" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C75" t="s">
         <v>5</v>
@@ -3642,10 +3729,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B76" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="C76" t="s">
         <v>5</v>
@@ -3653,10 +3740,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B77" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="C77" t="s">
         <v>5</v>
@@ -3664,10 +3751,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="B78" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="C78" t="s">
         <v>5</v>
@@ -3675,10 +3762,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="B79" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="C79" t="s">
         <v>5</v>
@@ -3686,10 +3773,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>122</v>
+      </c>
+      <c r="B80" t="s">
         <v>108</v>
-      </c>
-      <c r="B80" t="s">
-        <v>100</v>
       </c>
       <c r="C80" t="s">
         <v>5</v>
@@ -3697,10 +3784,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C81" t="s">
         <v>5</v>
@@ -3708,10 +3795,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="B82" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="C82" t="s">
         <v>5</v>
@@ -3719,10 +3806,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B83" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="C83" t="s">
         <v>5</v>
@@ -3730,10 +3817,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B84" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="C84" t="s">
         <v>5</v>
@@ -3741,10 +3828,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B85" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="C85" t="s">
         <v>5</v>
@@ -3752,10 +3839,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B86" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="C86" t="s">
         <v>5</v>
@@ -3763,10 +3850,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B87" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
         <v>5</v>
@@ -3774,10 +3861,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B88" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C88" t="s">
         <v>5</v>
@@ -3785,10 +3872,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="C89" t="s">
         <v>5</v>
@@ -3796,10 +3883,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B90" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C90" t="s">
         <v>5</v>
@@ -3807,10 +3894,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B91" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="C91" t="s">
         <v>5</v>
@@ -3818,10 +3905,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B92" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="C92" t="s">
         <v>5</v>
@@ -3829,10 +3916,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="C93" t="s">
         <v>5</v>
@@ -3840,10 +3927,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="C94" t="s">
         <v>5</v>
@@ -3851,10 +3938,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B95" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="C95" t="s">
         <v>5</v>
@@ -3862,10 +3949,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B96" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
       <c r="C96" t="s">
         <v>5</v>
@@ -3873,10 +3960,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B97" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C97" t="s">
         <v>5</v>
@@ -3884,10 +3971,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B98" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="C98" t="s">
         <v>5</v>
@@ -3895,10 +3982,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B99" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C99" t="s">
         <v>5</v>
@@ -3906,10 +3993,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B100" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="C100" t="s">
         <v>5</v>
@@ -3917,10 +4004,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B101" t="s">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="C101" t="s">
         <v>5</v>
@@ -3928,10 +4015,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B102" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="C102" t="s">
         <v>5</v>
@@ -3939,10 +4026,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="B103" t="s">
-        <v>51</v>
+        <v>150</v>
       </c>
       <c r="C103" t="s">
         <v>5</v>
@@ -3950,10 +4037,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="B104" t="s">
-        <v>37</v>
+        <v>152</v>
       </c>
       <c r="C104" t="s">
         <v>5</v>
@@ -3961,10 +4048,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="C105" t="s">
         <v>5</v>
@@ -3972,10 +4059,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B106" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="C106" t="s">
         <v>5</v>
@@ -3983,10 +4070,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="B107" t="s">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="C107" t="s">
         <v>5</v>
@@ -3994,10 +4081,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="B108" t="s">
-        <v>63</v>
+        <v>148</v>
       </c>
       <c r="C108" t="s">
         <v>5</v>
@@ -4005,10 +4092,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="B109" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C109" t="s">
         <v>5</v>
@@ -4016,10 +4103,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="B110" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="C110" t="s">
         <v>5</v>
@@ -4027,10 +4114,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="B111" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="C111" t="s">
         <v>5</v>
@@ -4038,10 +4125,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="B112" t="s">
-        <v>51</v>
+        <v>159</v>
       </c>
       <c r="C112" t="s">
         <v>5</v>
@@ -4049,10 +4136,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B113" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="C113" t="s">
         <v>5</v>
@@ -4060,10 +4147,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="B114" t="s">
-        <v>24</v>
+        <v>166</v>
       </c>
       <c r="C114" t="s">
         <v>5</v>
@@ -4071,10 +4158,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="B115" t="s">
-        <v>46</v>
+        <v>159</v>
       </c>
       <c r="C115" t="s">
         <v>5</v>
@@ -4082,10 +4169,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="B116" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="C116" t="s">
         <v>5</v>
@@ -4093,10 +4180,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="B117" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="C117" t="s">
         <v>5</v>
@@ -4104,10 +4191,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="B118" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="C118" t="s">
         <v>5</v>
@@ -4115,10 +4202,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="B119" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C119" t="s">
         <v>5</v>
@@ -4126,10 +4213,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="B120" t="s">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="C120" t="s">
         <v>5</v>
@@ -4137,10 +4224,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="B121" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C121" t="s">
         <v>5</v>
@@ -4148,10 +4235,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="B122" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -4159,10 +4246,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B123" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="C123" t="s">
         <v>5</v>
@@ -4170,10 +4257,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="B124" t="s">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="C124" t="s">
         <v>5</v>
@@ -4181,10 +4268,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B125" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C125" t="s">
         <v>5</v>
@@ -4192,10 +4279,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="B126" t="s">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="C126" t="s">
         <v>5</v>
@@ -4203,10 +4290,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B127" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="C127" t="s">
         <v>5</v>
@@ -4214,10 +4301,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="B128" t="s">
-        <v>7</v>
+        <v>181</v>
       </c>
       <c r="C128" t="s">
         <v>5</v>
@@ -4225,10 +4312,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="B129" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="C129" t="s">
         <v>5</v>
@@ -4236,10 +4323,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="B130" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="C130" t="s">
         <v>5</v>
@@ -4247,10 +4334,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B131" t="s">
-        <v>166</v>
+        <v>101</v>
       </c>
       <c r="C131" t="s">
         <v>5</v>
@@ -4258,10 +4345,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="B132" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C132" t="s">
         <v>5</v>
@@ -4269,10 +4356,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="B133" t="s">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="C133" t="s">
         <v>5</v>
@@ -4280,10 +4367,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B134" t="s">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="C134" t="s">
         <v>5</v>
@@ -4291,10 +4378,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="B135" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="C135" t="s">
         <v>5</v>
@@ -4302,10 +4389,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="B136" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="C136" t="s">
         <v>5</v>
@@ -4313,10 +4400,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="B137" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="C137" t="s">
         <v>5</v>
@@ -4324,10 +4411,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="B138" t="s">
-        <v>58</v>
+        <v>181</v>
       </c>
       <c r="C138" t="s">
         <v>5</v>
@@ -4335,10 +4422,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="B139" t="s">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="C139" t="s">
         <v>5</v>
@@ -4346,10 +4433,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="B140" t="s">
-        <v>166</v>
+        <v>101</v>
       </c>
       <c r="C140" t="s">
         <v>5</v>
@@ -4357,10 +4444,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C141" t="s">
         <v>5</v>
@@ -4368,10 +4455,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="B142" t="s">
-        <v>166</v>
+        <v>74</v>
       </c>
       <c r="C142" t="s">
         <v>5</v>
@@ -4379,10 +4466,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="B143" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="C143" t="s">
         <v>5</v>
@@ -4390,10 +4477,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="B144" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C144" t="s">
         <v>5</v>
@@ -4401,10 +4488,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="B145" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="C145" t="s">
         <v>5</v>
@@ -4412,10 +4499,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="B146" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="C146" t="s">
         <v>5</v>
@@ -4423,10 +4510,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="B147" t="s">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="C147" t="s">
         <v>5</v>
@@ -4434,10 +4521,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="B148" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="C148" t="s">
         <v>5</v>
@@ -4445,10 +4532,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="B149" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="C149" t="s">
         <v>5</v>
@@ -4456,10 +4543,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="B150" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C150" t="s">
         <v>5</v>
@@ -4467,10 +4554,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="B151" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="C151" t="s">
         <v>5</v>
@@ -4478,10 +4565,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="B152" t="s">
-        <v>166</v>
+        <v>206</v>
       </c>
       <c r="C152" t="s">
         <v>5</v>
@@ -4489,10 +4576,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="B153" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="C153" t="s">
         <v>5</v>
@@ -4500,10 +4587,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B154" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C154" t="s">
         <v>5</v>
@@ -4511,10 +4598,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="B155" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="C155" t="s">
         <v>5</v>
@@ -4522,10 +4609,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B156" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="C156" t="s">
         <v>5</v>
@@ -4533,10 +4620,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B157" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="C157" t="s">
         <v>5</v>
@@ -4544,10 +4631,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="B158" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="C158" t="s">
         <v>5</v>
@@ -4555,10 +4642,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B159" t="s">
-        <v>4</v>
+        <v>214</v>
       </c>
       <c r="C159" t="s">
         <v>5</v>
@@ -4566,10 +4653,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="B160" t="s">
-        <v>158</v>
+        <v>47</v>
       </c>
       <c r="C160" t="s">
         <v>5</v>
@@ -4577,10 +4664,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B161" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C161" t="s">
         <v>5</v>
@@ -4588,10 +4675,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B162" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="C162" t="s">
         <v>5</v>
@@ -4599,10 +4686,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="B163" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="C163" t="s">
         <v>5</v>
@@ -4610,10 +4697,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="B164" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="C164" t="s">
         <v>5</v>
@@ -4621,10 +4708,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="B165" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C165" t="s">
         <v>5</v>
@@ -4632,10 +4719,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B166" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="C166" t="s">
         <v>5</v>
@@ -4643,10 +4730,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="B167" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="C167" t="s">
         <v>5</v>
@@ -4654,10 +4741,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B168" t="s">
-        <v>88</v>
+        <v>214</v>
       </c>
       <c r="C168" t="s">
         <v>5</v>
@@ -4665,10 +4752,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="B169" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="C169" t="s">
         <v>5</v>
@@ -4676,10 +4763,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="B170" t="s">
-        <v>71</v>
+        <v>214</v>
       </c>
       <c r="C170" t="s">
         <v>5</v>
@@ -4687,10 +4774,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="B171" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C171" t="s">
         <v>5</v>
@@ -4698,10 +4785,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B172" t="s">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="C172" t="s">
         <v>5</v>
@@ -4709,10 +4796,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="B173" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C173" t="s">
         <v>5</v>
@@ -4720,10 +4807,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="B174" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="C174" t="s">
         <v>5</v>
@@ -4731,10 +4818,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B175" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C175" t="s">
         <v>5</v>
@@ -4742,10 +4829,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="B176" t="s">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="C176" t="s">
         <v>5</v>
@@ -4753,10 +4840,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B177" t="s">
-        <v>216</v>
+        <v>63</v>
       </c>
       <c r="C177" t="s">
         <v>5</v>
@@ -4764,10 +4851,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B178" t="s">
-        <v>219</v>
+        <v>113</v>
       </c>
       <c r="C178" t="s">
         <v>5</v>
@@ -4775,10 +4862,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="B179" t="s">
-        <v>219</v>
+        <v>57</v>
       </c>
       <c r="C179" t="s">
         <v>5</v>
@@ -4786,10 +4873,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="B180" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C180" t="s">
         <v>5</v>
@@ -4797,10 +4884,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B181" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -4808,10 +4895,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B182" t="s">
-        <v>226</v>
+        <v>137</v>
       </c>
       <c r="C182" t="s">
         <v>5</v>
@@ -4819,10 +4906,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B183" t="s">
-        <v>214</v>
+        <v>53</v>
       </c>
       <c r="C183" t="s">
         <v>5</v>
@@ -4830,10 +4917,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B184" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="C184" t="s">
         <v>5</v>
@@ -4841,10 +4928,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B185" t="s">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="C185" t="s">
         <v>5</v>
@@ -4852,10 +4939,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="B186" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="C186" t="s">
         <v>5</v>
@@ -4863,10 +4950,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="B187" t="s">
-        <v>224</v>
+        <v>55</v>
       </c>
       <c r="C187" t="s">
         <v>5</v>
@@ -4874,10 +4961,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B188" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="C188" t="s">
         <v>5</v>
@@ -4885,10 +4972,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B189" t="s">
-        <v>222</v>
+        <v>55</v>
       </c>
       <c r="C189" t="s">
         <v>5</v>
@@ -4896,10 +4983,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="B190" t="s">
-        <v>216</v>
+        <v>137</v>
       </c>
       <c r="C190" t="s">
         <v>5</v>
@@ -4907,10 +4994,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B191" t="s">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="C191" t="s">
         <v>5</v>
@@ -4918,10 +5005,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B192" t="s">
-        <v>237</v>
+        <v>61</v>
       </c>
       <c r="C192" t="s">
         <v>5</v>
@@ -4929,10 +5016,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B193" t="s">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="C193" t="s">
         <v>5</v>
@@ -4940,10 +5027,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B194" t="s">
-        <v>240</v>
+        <v>61</v>
       </c>
       <c r="C194" t="s">
         <v>5</v>
@@ -4951,10 +5038,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B195" t="s">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="C195" t="s">
         <v>5</v>
@@ -4962,10 +5049,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B196" t="s">
-        <v>244</v>
+        <v>137</v>
       </c>
       <c r="C196" t="s">
         <v>5</v>
@@ -4973,10 +5060,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B197" t="s">
-        <v>244</v>
+        <v>139</v>
       </c>
       <c r="C197" t="s">
         <v>5</v>
@@ -4984,10 +5071,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B198" t="s">
-        <v>247</v>
+        <v>120</v>
       </c>
       <c r="C198" t="s">
         <v>5</v>
@@ -4995,10 +5082,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B199" t="s">
-        <v>240</v>
+        <v>139</v>
       </c>
       <c r="C199" t="s">
         <v>5</v>
@@ -5006,10 +5093,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B200" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="C200" t="s">
         <v>5</v>
@@ -5017,10 +5104,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B201" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
       <c r="C201" t="s">
         <v>5</v>
@@ -5028,10 +5115,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B202" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="C202" t="s">
         <v>5</v>
@@ -5039,10 +5126,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B203" t="s">
-        <v>250</v>
+        <v>36</v>
       </c>
       <c r="C203" t="s">
         <v>5</v>
@@ -5050,10 +5137,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B204" t="s">
-        <v>226</v>
+        <v>261</v>
       </c>
       <c r="C204" t="s">
         <v>5</v>
@@ -5061,10 +5148,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B205" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C205" t="s">
         <v>5</v>
@@ -5072,10 +5159,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B206" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C206" t="s">
         <v>5</v>
@@ -5083,10 +5170,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B207" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C207" t="s">
         <v>5</v>
@@ -5094,10 +5181,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B208" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C208" t="s">
         <v>5</v>
@@ -5105,10 +5192,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B209" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C209" t="s">
         <v>5</v>
@@ -5116,10 +5203,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B210" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C210" t="s">
         <v>5</v>
@@ -5127,10 +5214,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B211" t="s">
-        <v>264</v>
+        <v>36</v>
       </c>
       <c r="C211" t="s">
         <v>5</v>
@@ -5138,10 +5225,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B212" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C212" t="s">
         <v>5</v>
@@ -5149,10 +5236,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B213" t="s">
-        <v>269</v>
+        <v>36</v>
       </c>
       <c r="C213" t="s">
         <v>5</v>
@@ -5160,7 +5247,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B214" t="s">
         <v>269</v>
@@ -5171,10 +5258,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B215" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C215" t="s">
         <v>5</v>
@@ -5182,10 +5269,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B216" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C216" t="s">
         <v>5</v>
@@ -5193,10 +5280,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B217" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C217" t="s">
         <v>5</v>
@@ -5204,10 +5291,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B218" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="C218" t="s">
         <v>5</v>
@@ -5215,10 +5302,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B219" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C219" t="s">
         <v>5</v>
@@ -5226,10 +5313,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B220" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C220" t="s">
         <v>5</v>
@@ -5237,10 +5324,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B221" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C221" t="s">
         <v>5</v>
@@ -5248,7 +5335,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B222" t="s">
         <v>285</v>
@@ -5259,10 +5346,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B223" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C223" t="s">
         <v>5</v>
@@ -5273,7 +5360,7 @@
         <v>288</v>
       </c>
       <c r="B224" t="s">
-        <v>280</v>
+        <v>21</v>
       </c>
       <c r="C224" t="s">
         <v>5</v>
@@ -5284,7 +5371,7 @@
         <v>289</v>
       </c>
       <c r="B225" t="s">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="C225" t="s">
         <v>5</v>
@@ -5292,10 +5379,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B226" t="s">
-        <v>292</v>
+        <v>9</v>
       </c>
       <c r="C226" t="s">
         <v>5</v>
@@ -5303,10 +5390,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B227" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C227" t="s">
         <v>5</v>
@@ -5314,10 +5401,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B228" t="s">
-        <v>295</v>
+        <v>32</v>
       </c>
       <c r="C228" t="s">
         <v>5</v>
@@ -5325,10 +5412,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B229" t="s">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="C229" t="s">
         <v>5</v>
@@ -5336,10 +5423,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B230" t="s">
-        <v>299</v>
+        <v>267</v>
       </c>
       <c r="C230" t="s">
         <v>5</v>
@@ -5347,10 +5434,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B231" t="s">
-        <v>301</v>
+        <v>32</v>
       </c>
       <c r="C231" t="s">
         <v>5</v>
@@ -5358,10 +5445,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B232" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="C232" t="s">
         <v>5</v>
@@ -5369,10 +5456,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B233" t="s">
-        <v>301</v>
+        <v>32</v>
       </c>
       <c r="C233" t="s">
         <v>5</v>
@@ -5380,10 +5467,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B234" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C234" t="s">
         <v>5</v>
@@ -5391,10 +5478,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B235" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C235" t="s">
         <v>5</v>
@@ -5402,10 +5489,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B236" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C236" t="s">
         <v>5</v>
@@ -5413,10 +5500,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="C237" t="s">
         <v>5</v>
@@ -5424,10 +5511,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B238" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C238" t="s">
         <v>5</v>
@@ -5435,10 +5522,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B239" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C239" t="s">
         <v>5</v>
@@ -5446,10 +5533,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B240" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -5457,10 +5544,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B241" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C241" t="s">
         <v>5</v>
@@ -5468,10 +5555,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B242" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C242" t="s">
         <v>5</v>
@@ -5479,10 +5566,10 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B243" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C243" t="s">
         <v>5</v>
@@ -5490,10 +5577,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B244" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="C244" t="s">
         <v>5</v>
@@ -5501,10 +5588,10 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B245" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C245" t="s">
         <v>5</v>
@@ -5512,10 +5599,10 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B246" t="s">
-        <v>257</v>
+        <v>320</v>
       </c>
       <c r="C246" t="s">
         <v>5</v>
@@ -5523,10 +5610,10 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B247" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C247" t="s">
         <v>5</v>
@@ -5534,10 +5621,10 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B248" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="C248" t="s">
         <v>5</v>
@@ -5545,10 +5632,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B249" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C249" t="s">
         <v>5</v>
@@ -5556,10 +5643,10 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B250" t="s">
-        <v>214</v>
+        <v>327</v>
       </c>
       <c r="C250" t="s">
         <v>5</v>
@@ -5567,10 +5654,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B251" t="s">
-        <v>222</v>
+        <v>329</v>
       </c>
       <c r="C251" t="s">
         <v>5</v>
@@ -5578,10 +5665,10 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B252" t="s">
-        <v>69</v>
+        <v>322</v>
       </c>
       <c r="C252" t="s">
         <v>5</v>
@@ -5589,10 +5676,10 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
+        <v>331</v>
+      </c>
+      <c r="B253" t="s">
         <v>332</v>
-      </c>
-      <c r="B253" t="s">
-        <v>333</v>
       </c>
       <c r="C253" t="s">
         <v>5</v>
@@ -5600,10 +5687,10 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
+        <v>333</v>
+      </c>
+      <c r="B254" t="s">
         <v>334</v>
-      </c>
-      <c r="B254" t="s">
-        <v>90</v>
       </c>
       <c r="C254" t="s">
         <v>5</v>
@@ -5614,7 +5701,7 @@
         <v>335</v>
       </c>
       <c r="B255" t="s">
-        <v>96</v>
+        <v>322</v>
       </c>
       <c r="C255" t="s">
         <v>5</v>
@@ -5625,7 +5712,7 @@
         <v>336</v>
       </c>
       <c r="B256" t="s">
-        <v>169</v>
+        <v>337</v>
       </c>
       <c r="C256" t="s">
         <v>5</v>
@@ -5633,10 +5720,10 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B257" t="s">
-        <v>96</v>
+        <v>339</v>
       </c>
       <c r="C257" t="s">
         <v>5</v>
@@ -5644,10 +5731,10 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B258" t="s">
-        <v>58</v>
+        <v>341</v>
       </c>
       <c r="C258" t="s">
         <v>5</v>
@@ -5655,10 +5742,10 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B259" t="s">
-        <v>16</v>
+        <v>343</v>
       </c>
       <c r="C259" t="s">
         <v>5</v>
@@ -5666,10 +5753,10 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B260" t="s">
-        <v>37</v>
+        <v>304</v>
       </c>
       <c r="C260" t="s">
         <v>5</v>
@@ -5677,10 +5764,10 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B261" t="s">
-        <v>46</v>
+        <v>343</v>
       </c>
       <c r="C261" t="s">
         <v>5</v>
@@ -5688,10 +5775,10 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B262" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C262" t="s">
         <v>5</v>
@@ -5699,10 +5786,10 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B263" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C263" t="s">
         <v>5</v>
@@ -5710,10 +5797,10 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B264" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C264" t="s">
         <v>5</v>
@@ -5721,10 +5808,10 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B265" t="s">
-        <v>40</v>
+        <v>282</v>
       </c>
       <c r="C265" t="s">
         <v>5</v>
@@ -5732,10 +5819,10 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B266" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C266" t="s">
         <v>5</v>
@@ -5743,10 +5830,10 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B267" t="s">
-        <v>24</v>
+        <v>352</v>
       </c>
       <c r="C267" t="s">
         <v>5</v>
@@ -5754,10 +5841,10 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B268" t="s">
-        <v>100</v>
+        <v>299</v>
       </c>
       <c r="C268" t="s">
         <v>5</v>
@@ -5765,10 +5852,10 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B269" t="s">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="C269" t="s">
         <v>5</v>
@@ -5776,10 +5863,10 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B270" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C270" t="s">
         <v>5</v>
@@ -5787,10 +5874,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B271" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C271" t="s">
         <v>5</v>
@@ -5798,10 +5885,10 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B272" t="s">
-        <v>13</v>
+        <v>299</v>
       </c>
       <c r="C272" t="s">
         <v>5</v>
@@ -5809,10 +5896,10 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B273" t="s">
-        <v>51</v>
+        <v>360</v>
       </c>
       <c r="C273" t="s">
         <v>5</v>
@@ -5820,10 +5907,10 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B274" t="s">
-        <v>58</v>
+        <v>299</v>
       </c>
       <c r="C274" t="s">
         <v>5</v>
@@ -5831,10 +5918,10 @@
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B275" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C275" t="s">
         <v>5</v>
@@ -5842,10 +5929,10 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B276" t="s">
-        <v>51</v>
+        <v>261</v>
       </c>
       <c r="C276" t="s">
         <v>5</v>
@@ -5853,10 +5940,10 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B277" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C277" t="s">
         <v>5</v>
@@ -5864,10 +5951,10 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B278" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C278" t="s">
         <v>5</v>
@@ -5875,10 +5962,10 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B279" t="s">
-        <v>58</v>
+        <v>267</v>
       </c>
       <c r="C279" t="s">
         <v>5</v>
@@ -5886,10 +5973,10 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B280" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C280" t="s">
         <v>5</v>
@@ -5897,10 +5984,10 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B281" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C281" t="s">
         <v>5</v>
@@ -5908,10 +5995,10 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B282" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="C282" t="s">
         <v>5</v>
@@ -5919,10 +6006,10 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="B283" t="s">
-        <v>158</v>
+        <v>53</v>
       </c>
       <c r="C283" t="s">
         <v>5</v>
@@ -5930,10 +6017,10 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B284" t="s">
-        <v>184</v>
+        <v>49</v>
       </c>
       <c r="C284" t="s">
         <v>5</v>
@@ -5941,10 +6028,10 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B285" t="s">
-        <v>366</v>
+        <v>53</v>
       </c>
       <c r="C285" t="s">
         <v>5</v>
@@ -5952,10 +6039,10 @@
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B286" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C286" t="s">
         <v>5</v>
@@ -5963,10 +6050,10 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B287" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C287" t="s">
         <v>5</v>
@@ -5974,10 +6061,10 @@
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B288" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="C288" t="s">
         <v>5</v>
@@ -5985,10 +6072,10 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B289" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="C289" t="s">
         <v>5</v>
@@ -5996,10 +6083,10 @@
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B290" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C290" t="s">
         <v>5</v>
@@ -6007,10 +6094,10 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B291" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="C291" t="s">
         <v>5</v>
@@ -6018,10 +6105,10 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B292" t="s">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="C292" t="s">
         <v>5</v>
@@ -6029,10 +6116,10 @@
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B293" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C293" t="s">
         <v>5</v>
@@ -6040,10 +6127,10 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B294" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C294" t="s">
         <v>5</v>
@@ -6051,10 +6138,10 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B295" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="C295" t="s">
         <v>5</v>
@@ -6062,10 +6149,10 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B296" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="C296" t="s">
         <v>5</v>
@@ -6073,10 +6160,10 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B297" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C297" t="s">
         <v>5</v>
@@ -6084,10 +6171,10 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B298" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="C298" t="s">
         <v>5</v>
@@ -6095,10 +6182,10 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B299" t="s">
-        <v>169</v>
+        <v>66</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -6106,10 +6193,10 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B300" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="C300" t="s">
         <v>5</v>
@@ -6117,10 +6204,10 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B301" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="C301" t="s">
         <v>5</v>
@@ -6128,10 +6215,10 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B302" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="C302" t="s">
         <v>5</v>
@@ -6139,10 +6226,10 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B303" t="s">
-        <v>385</v>
+        <v>113</v>
       </c>
       <c r="C303" t="s">
         <v>5</v>
@@ -6150,10 +6237,10 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B304" t="s">
-        <v>385</v>
+        <v>101</v>
       </c>
       <c r="C304" t="s">
         <v>5</v>
@@ -6161,10 +6248,10 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B305" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C305" t="s">
         <v>5</v>
@@ -6172,10 +6259,10 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B306" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C306" t="s">
         <v>5</v>
@@ -6183,10 +6270,10 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B307" t="s">
-        <v>385</v>
+        <v>108</v>
       </c>
       <c r="C307" t="s">
         <v>5</v>
@@ -6194,10 +6281,10 @@
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B308" t="s">
-        <v>391</v>
+        <v>63</v>
       </c>
       <c r="C308" t="s">
         <v>5</v>
@@ -6205,10 +6292,10 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B309" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="C309" t="s">
         <v>5</v>
@@ -6216,10 +6303,10 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B310" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="C310" t="s">
         <v>5</v>
@@ -6227,10 +6314,10 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B311" t="s">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="C311" t="s">
         <v>5</v>
@@ -6238,10 +6325,10 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B312" t="s">
-        <v>46</v>
+        <v>231</v>
       </c>
       <c r="C312" t="s">
         <v>5</v>
@@ -6249,10 +6336,10 @@
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B313" t="s">
-        <v>34</v>
+        <v>401</v>
       </c>
       <c r="C313" t="s">
         <v>5</v>
@@ -6260,10 +6347,10 @@
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B314" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="C314" t="s">
         <v>5</v>
@@ -6271,10 +6358,10 @@
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B315" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C315" t="s">
         <v>5</v>
@@ -6282,10 +6369,10 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B316" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C316" t="s">
         <v>5</v>
@@ -6293,10 +6380,10 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B317" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="C317" t="s">
         <v>5</v>
@@ -6304,10 +6391,10 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B318" t="s">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="C318" t="s">
         <v>5</v>
@@ -6315,10 +6402,10 @@
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B319" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C319" t="s">
         <v>5</v>
@@ -6326,10 +6413,10 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B320" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C320" t="s">
         <v>5</v>
@@ -6337,10 +6424,10 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B321" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C321" t="s">
         <v>5</v>
@@ -6348,10 +6435,10 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B322" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="C322" t="s">
         <v>5</v>
@@ -6359,10 +6446,10 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B323" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="C323" t="s">
         <v>5</v>
@@ -6370,10 +6457,10 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B324" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="C324" t="s">
         <v>5</v>
@@ -6381,10 +6468,10 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B325" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="C325" t="s">
         <v>5</v>
@@ -6392,10 +6479,10 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B326" t="s">
-        <v>46</v>
+        <v>137</v>
       </c>
       <c r="C326" t="s">
         <v>5</v>
@@ -6403,10 +6490,10 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B327" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C327" t="s">
         <v>5</v>
@@ -6414,10 +6501,10 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B328" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="C328" t="s">
         <v>5</v>
@@ -6425,10 +6512,10 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B329" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="C329" t="s">
         <v>5</v>
@@ -6436,10 +6523,10 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B330" t="s">
-        <v>9</v>
+        <v>181</v>
       </c>
       <c r="C330" t="s">
         <v>5</v>
@@ -6447,10 +6534,10 @@
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B331" t="s">
-        <v>13</v>
+        <v>420</v>
       </c>
       <c r="C331" t="s">
         <v>5</v>
@@ -6458,10 +6545,10 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B332" t="s">
-        <v>69</v>
+        <v>420</v>
       </c>
       <c r="C332" t="s">
         <v>5</v>
@@ -6469,10 +6556,10 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B333" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C333" t="s">
         <v>5</v>
@@ -6480,10 +6567,10 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B334" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="C334" t="s">
         <v>5</v>
@@ -6491,10 +6578,10 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B335" t="s">
-        <v>13</v>
+        <v>420</v>
       </c>
       <c r="C335" t="s">
         <v>5</v>
@@ -6502,10 +6589,10 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B336" t="s">
-        <v>11</v>
+        <v>426</v>
       </c>
       <c r="C336" t="s">
         <v>5</v>
@@ -6513,10 +6600,10 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B337" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C337" t="s">
         <v>5</v>
@@ -6524,10 +6611,10 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="B338" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C338" t="s">
         <v>5</v>
@@ -6535,10 +6622,10 @@
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B339" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="C339" t="s">
         <v>5</v>
@@ -6546,10 +6633,10 @@
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="B340" t="s">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="C340" t="s">
         <v>5</v>
@@ -6557,10 +6644,10 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B341" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="C341" t="s">
         <v>5</v>
@@ -6568,10 +6655,10 @@
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B342" t="s">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="C342" t="s">
         <v>5</v>
@@ -6579,10 +6666,10 @@
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B343" t="s">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="C343" t="s">
         <v>5</v>
@@ -6590,10 +6677,10 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B344" t="s">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="C344" t="s">
         <v>5</v>
@@ -6601,10 +6688,10 @@
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B345" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="C345" t="s">
         <v>5</v>
@@ -6612,10 +6699,10 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B346" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="C346" t="s">
         <v>5</v>
@@ -6623,10 +6710,10 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="B347" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C347" t="s">
         <v>5</v>
@@ -6634,10 +6721,10 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="B348" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="C348" t="s">
         <v>5</v>
@@ -6645,10 +6732,10 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B349" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
       <c r="C349" t="s">
         <v>5</v>
@@ -6656,10 +6743,10 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B350" t="s">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="C350" t="s">
         <v>5</v>
@@ -6667,10 +6754,10 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B351" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C351" t="s">
         <v>5</v>
@@ -6678,10 +6765,10 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B352" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="C352" t="s">
         <v>5</v>
@@ -6689,10 +6776,10 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B353" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="C353" t="s">
         <v>5</v>
@@ -6700,10 +6787,10 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B354" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C354" t="s">
         <v>5</v>
@@ -6711,10 +6798,10 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="B355" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C355" t="s">
         <v>5</v>
@@ -6722,10 +6809,10 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B356" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="C356" t="s">
         <v>5</v>
@@ -6733,10 +6820,10 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B357" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C357" t="s">
         <v>5</v>
@@ -6744,10 +6831,10 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="B358" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -6755,10 +6842,10 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="B359" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="C359" t="s">
         <v>5</v>
@@ -6766,10 +6853,10 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B360" t="s">
-        <v>158</v>
+        <v>47</v>
       </c>
       <c r="C360" t="s">
         <v>5</v>
@@ -6777,10 +6864,10 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B361" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="C361" t="s">
         <v>5</v>
@@ -6788,10 +6875,10 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="B362" t="s">
-        <v>158</v>
+        <v>63</v>
       </c>
       <c r="C362" t="s">
         <v>5</v>
@@ -6799,10 +6886,10 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="B363" t="s">
-        <v>158</v>
+        <v>63</v>
       </c>
       <c r="C363" t="s">
         <v>5</v>
@@ -6810,10 +6897,10 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B364" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="C364" t="s">
         <v>5</v>
@@ -6821,10 +6908,10 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="B365" t="s">
-        <v>90</v>
+        <v>214</v>
       </c>
       <c r="C365" t="s">
         <v>5</v>
@@ -6832,10 +6919,10 @@
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B366" t="s">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="C366" t="s">
         <v>5</v>
@@ -6843,10 +6930,10 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="B367" t="s">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="C367" t="s">
         <v>5</v>
@@ -6854,10 +6941,10 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="B368" t="s">
-        <v>96</v>
+        <v>206</v>
       </c>
       <c r="C368" t="s">
         <v>5</v>
@@ -6865,10 +6952,10 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B369" t="s">
-        <v>453</v>
+        <v>206</v>
       </c>
       <c r="C369" t="s">
         <v>5</v>
@@ -6876,10 +6963,10 @@
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="B370" t="s">
-        <v>455</v>
+        <v>57</v>
       </c>
       <c r="C370" t="s">
         <v>5</v>
@@ -6887,10 +6974,10 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B371" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="C371" t="s">
         <v>5</v>
@@ -6898,10 +6985,10 @@
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B372" t="s">
-        <v>458</v>
+        <v>57</v>
       </c>
       <c r="C372" t="s">
         <v>5</v>
@@ -6909,10 +6996,10 @@
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B373" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C373" t="s">
         <v>5</v>
@@ -6920,10 +7007,10 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B374" t="s">
-        <v>333</v>
+        <v>87</v>
       </c>
       <c r="C374" t="s">
         <v>5</v>
@@ -6931,10 +7018,10 @@
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B375" t="s">
-        <v>333</v>
+        <v>76</v>
       </c>
       <c r="C375" t="s">
         <v>5</v>
@@ -6942,10 +7029,10 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B376" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C376" t="s">
         <v>5</v>
@@ -6953,10 +7040,10 @@
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B377" t="s">
-        <v>71</v>
+        <v>214</v>
       </c>
       <c r="C377" t="s">
         <v>5</v>
@@ -6964,10 +7051,10 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B378" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="C378" t="s">
         <v>5</v>
@@ -6975,10 +7062,10 @@
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B379" t="s">
-        <v>71</v>
+        <v>137</v>
       </c>
       <c r="C379" t="s">
         <v>5</v>
@@ -6986,10 +7073,10 @@
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B380" t="s">
-        <v>71</v>
+        <v>137</v>
       </c>
       <c r="C380" t="s">
         <v>5</v>
@@ -6997,10 +7084,10 @@
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B381" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C381" t="s">
         <v>5</v>
@@ -7008,10 +7095,10 @@
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B382" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="C382" t="s">
         <v>5</v>
@@ -7019,10 +7106,10 @@
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B383" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="C383" t="s">
         <v>5</v>
@@ -7030,10 +7117,10 @@
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B384" t="s">
-        <v>96</v>
+        <v>206</v>
       </c>
       <c r="C384" t="s">
         <v>5</v>
@@ -7041,10 +7128,10 @@
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B385" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C385" t="s">
         <v>5</v>
@@ -7052,10 +7139,10 @@
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B386" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C386" t="s">
         <v>5</v>
@@ -7063,10 +7150,10 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B387" t="s">
-        <v>474</v>
+        <v>63</v>
       </c>
       <c r="C387" t="s">
         <v>5</v>
@@ -7074,10 +7161,10 @@
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B388" t="s">
-        <v>169</v>
+        <v>206</v>
       </c>
       <c r="C388" t="s">
         <v>5</v>
@@ -7085,10 +7172,10 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B389" t="s">
-        <v>458</v>
+        <v>206</v>
       </c>
       <c r="C389" t="s">
         <v>5</v>
@@ -7096,10 +7183,10 @@
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B390" t="s">
-        <v>458</v>
+        <v>206</v>
       </c>
       <c r="C390" t="s">
         <v>5</v>
@@ -7107,10 +7194,10 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B391" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C391" t="s">
         <v>5</v>
@@ -7118,10 +7205,10 @@
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B392" t="s">
-        <v>250</v>
+        <v>61</v>
       </c>
       <c r="C392" t="s">
         <v>5</v>
@@ -7129,10 +7216,10 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B393" t="s">
-        <v>307</v>
+        <v>139</v>
       </c>
       <c r="C393" t="s">
         <v>5</v>
@@ -7140,10 +7227,10 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B394" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C394" t="s">
         <v>5</v>
@@ -7151,10 +7238,10 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B395" t="s">
-        <v>305</v>
+        <v>137</v>
       </c>
       <c r="C395" t="s">
         <v>5</v>
@@ -7162,10 +7249,10 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B396" t="s">
-        <v>312</v>
+        <v>53</v>
       </c>
       <c r="C396" t="s">
         <v>5</v>
@@ -7173,10 +7260,10 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B397" t="s">
-        <v>226</v>
+        <v>43</v>
       </c>
       <c r="C397" t="s">
         <v>5</v>
@@ -7184,10 +7271,10 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B398" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="C398" t="s">
         <v>5</v>
@@ -7195,10 +7282,10 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B399" t="s">
-        <v>453</v>
+        <v>141</v>
       </c>
       <c r="C399" t="s">
         <v>5</v>
@@ -7206,10 +7293,10 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B400" t="s">
-        <v>366</v>
+        <v>491</v>
       </c>
       <c r="C400" t="s">
         <v>5</v>
@@ -7217,10 +7304,10 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B401" t="s">
-        <v>366</v>
+        <v>51</v>
       </c>
       <c r="C401" t="s">
         <v>5</v>
@@ -7228,10 +7315,10 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B402" t="s">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="C402" t="s">
         <v>5</v>
@@ -7239,10 +7326,10 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B403" t="s">
-        <v>458</v>
+        <v>7</v>
       </c>
       <c r="C403" t="s">
         <v>5</v>
@@ -7250,10 +7337,10 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B404" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="C404" t="s">
         <v>5</v>
@@ -7261,10 +7348,10 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B405" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C405" t="s">
         <v>5</v>
@@ -7272,10 +7359,10 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B406" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="C406" t="s">
         <v>5</v>
@@ -7283,10 +7370,10 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B407" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="C407" t="s">
         <v>5</v>
@@ -7294,10 +7381,10 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B408" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="C408" t="s">
         <v>5</v>
@@ -7305,10 +7392,10 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B409" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C409" t="s">
         <v>5</v>
@@ -7316,10 +7403,10 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B410" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C410" t="s">
         <v>5</v>
@@ -7327,10 +7414,10 @@
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B411" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C411" t="s">
         <v>5</v>
@@ -7338,10 +7425,10 @@
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B412" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C412" t="s">
         <v>5</v>
@@ -7349,10 +7436,10 @@
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B413" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C413" t="s">
         <v>5</v>
@@ -7360,10 +7447,10 @@
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B414" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C414" t="s">
         <v>5</v>
@@ -7371,10 +7458,10 @@
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B415" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C415" t="s">
         <v>5</v>
@@ -7382,10 +7469,10 @@
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B416" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C416" t="s">
         <v>5</v>
@@ -7393,10 +7480,10 @@
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B417" t="s">
-        <v>13</v>
+        <v>491</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -7404,10 +7491,10 @@
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B418" t="s">
-        <v>158</v>
+        <v>491</v>
       </c>
       <c r="C418" t="s">
         <v>5</v>
@@ -7415,10 +7502,10 @@
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B419" t="s">
-        <v>158</v>
+        <v>267</v>
       </c>
       <c r="C419" t="s">
         <v>5</v>
@@ -7426,10 +7513,10 @@
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B420" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C420" t="s">
         <v>5</v>
@@ -7437,10 +7524,10 @@
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B421" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="C421" t="s">
         <v>5</v>
@@ -7448,10 +7535,10 @@
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B422" t="s">
-        <v>4</v>
+        <v>264</v>
       </c>
       <c r="C422" t="s">
         <v>5</v>
@@ -7459,10 +7546,10 @@
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B423" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="C423" t="s">
         <v>5</v>
@@ -7470,10 +7557,10 @@
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B424" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="C424" t="s">
         <v>5</v>
@@ -7481,10 +7568,10 @@
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B425" t="s">
-        <v>69</v>
+        <v>271</v>
       </c>
       <c r="C425" t="s">
         <v>5</v>
@@ -7492,10 +7579,10 @@
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B426" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C426" t="s">
         <v>5</v>
@@ -7503,10 +7590,10 @@
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B427" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="C427" t="s">
         <v>5</v>
@@ -7514,10 +7601,10 @@
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B428" t="s">
-        <v>4</v>
+        <v>401</v>
       </c>
       <c r="C428" t="s">
         <v>5</v>
@@ -7525,10 +7612,10 @@
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B429" t="s">
-        <v>166</v>
+        <v>401</v>
       </c>
       <c r="C429" t="s">
         <v>5</v>
@@ -7536,10 +7623,10 @@
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B430" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="C430" t="s">
         <v>5</v>
@@ -7547,10 +7634,10 @@
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B431" t="s">
-        <v>4</v>
+        <v>491</v>
       </c>
       <c r="C431" t="s">
         <v>5</v>
@@ -7558,10 +7645,10 @@
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B432" t="s">
-        <v>11</v>
+        <v>231</v>
       </c>
       <c r="C432" t="s">
         <v>5</v>
@@ -7569,10 +7656,10 @@
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B433" t="s">
-        <v>11</v>
+        <v>137</v>
       </c>
       <c r="C433" t="s">
         <v>5</v>
@@ -7580,10 +7667,10 @@
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B434" t="s">
-        <v>453</v>
+        <v>120</v>
       </c>
       <c r="C434" t="s">
         <v>5</v>
@@ -7591,10 +7678,10 @@
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B435" t="s">
-        <v>184</v>
+        <v>120</v>
       </c>
       <c r="C435" t="s">
         <v>5</v>
@@ -7602,10 +7689,10 @@
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B436" t="s">
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="C436" t="s">
         <v>5</v>
@@ -7613,10 +7700,10 @@
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B437" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="C437" t="s">
         <v>5</v>
@@ -7624,10 +7711,10 @@
     </row>
     <row r="438">
       <c r="A438" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B438" t="s">
-        <v>366</v>
+        <v>101</v>
       </c>
       <c r="C438" t="s">
         <v>5</v>
@@ -7635,10 +7722,10 @@
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B439" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C439" t="s">
         <v>5</v>
@@ -7646,10 +7733,10 @@
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B440" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C440" t="s">
         <v>5</v>
@@ -7657,10 +7744,10 @@
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B441" t="s">
-        <v>224</v>
+        <v>98</v>
       </c>
       <c r="C441" t="s">
         <v>5</v>
@@ -7668,10 +7755,10 @@
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B442" t="s">
-        <v>458</v>
+        <v>66</v>
       </c>
       <c r="C442" t="s">
         <v>5</v>
@@ -7679,10 +7766,10 @@
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B443" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="C443" t="s">
         <v>5</v>
@@ -7690,10 +7777,10 @@
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B444" t="s">
-        <v>474</v>
+        <v>108</v>
       </c>
       <c r="C444" t="s">
         <v>5</v>
@@ -7701,10 +7788,10 @@
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B445" t="s">
-        <v>333</v>
+        <v>63</v>
       </c>
       <c r="C445" t="s">
         <v>5</v>
@@ -7712,10 +7799,10 @@
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B446" t="s">
-        <v>333</v>
+        <v>206</v>
       </c>
       <c r="C446" t="s">
         <v>5</v>
@@ -7723,10 +7810,10 @@
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B447" t="s">
-        <v>453</v>
+        <v>206</v>
       </c>
       <c r="C447" t="s">
         <v>5</v>
@@ -7734,10 +7821,10 @@
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B448" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="C448" t="s">
         <v>5</v>
@@ -7745,10 +7832,10 @@
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B449" t="s">
-        <v>184</v>
+        <v>120</v>
       </c>
       <c r="C449" t="s">
         <v>5</v>
@@ -7756,10 +7843,10 @@
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B450" t="s">
-        <v>184</v>
+        <v>55</v>
       </c>
       <c r="C450" t="s">
         <v>5</v>
@@ -7767,10 +7854,10 @@
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B451" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C451" t="s">
         <v>5</v>
@@ -7778,10 +7865,10 @@
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B452" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C452" t="s">
         <v>5</v>
@@ -7789,10 +7876,10 @@
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B453" t="s">
-        <v>453</v>
+        <v>47</v>
       </c>
       <c r="C453" t="s">
         <v>5</v>
@@ -7800,10 +7887,10 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B454" t="s">
-        <v>184</v>
+        <v>53</v>
       </c>
       <c r="C454" t="s">
         <v>5</v>
@@ -7811,10 +7898,10 @@
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B455" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="C455" t="s">
         <v>5</v>
@@ -7822,10 +7909,10 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B456" t="s">
-        <v>366</v>
+        <v>55</v>
       </c>
       <c r="C456" t="s">
         <v>5</v>
@@ -7833,10 +7920,10 @@
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B457" t="s">
-        <v>366</v>
+        <v>214</v>
       </c>
       <c r="C457" t="s">
         <v>5</v>
@@ -7844,10 +7931,10 @@
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B458" t="s">
-        <v>474</v>
+        <v>214</v>
       </c>
       <c r="C458" t="s">
         <v>5</v>
@@ -7855,10 +7942,10 @@
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B459" t="s">
-        <v>333</v>
+        <v>55</v>
       </c>
       <c r="C459" t="s">
         <v>5</v>
@@ -7866,10 +7953,10 @@
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B460" t="s">
-        <v>458</v>
+        <v>61</v>
       </c>
       <c r="C460" t="s">
         <v>5</v>
@@ -7877,10 +7964,10 @@
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B461" t="s">
-        <v>216</v>
+        <v>61</v>
       </c>
       <c r="C461" t="s">
         <v>5</v>
@@ -7888,10 +7975,10 @@
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B462" t="s">
-        <v>224</v>
+        <v>43</v>
       </c>
       <c r="C462" t="s">
         <v>5</v>
@@ -7899,10 +7986,10 @@
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B463" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C463" t="s">
         <v>5</v>
@@ -7910,10 +7997,10 @@
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B464" t="s">
-        <v>328</v>
+        <v>49</v>
       </c>
       <c r="C464" t="s">
         <v>5</v>
@@ -7921,10 +8008,10 @@
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B465" t="s">
-        <v>240</v>
+        <v>139</v>
       </c>
       <c r="C465" t="s">
         <v>5</v>
@@ -7932,10 +8019,10 @@
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B466" t="s">
-        <v>222</v>
+        <v>401</v>
       </c>
       <c r="C466" t="s">
         <v>5</v>
@@ -7943,10 +8030,10 @@
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B467" t="s">
-        <v>216</v>
+        <v>141</v>
       </c>
       <c r="C467" t="s">
         <v>5</v>
@@ -7954,10 +8041,10 @@
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B468" t="s">
-        <v>556</v>
+        <v>141</v>
       </c>
       <c r="C468" t="s">
         <v>5</v>
@@ -7965,10 +8052,10 @@
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B469" t="s">
-        <v>558</v>
+        <v>269</v>
       </c>
       <c r="C469" t="s">
         <v>5</v>
@@ -7976,10 +8063,10 @@
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B470" t="s">
-        <v>309</v>
+        <v>491</v>
       </c>
       <c r="C470" t="s">
         <v>5</v>
@@ -7987,10 +8074,10 @@
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B471" t="s">
-        <v>250</v>
+        <v>141</v>
       </c>
       <c r="C471" t="s">
         <v>5</v>
@@ -7998,10 +8085,10 @@
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B472" t="s">
-        <v>224</v>
+        <v>4</v>
       </c>
       <c r="C472" t="s">
         <v>5</v>
@@ -8009,10 +8096,10 @@
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B473" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="C473" t="s">
         <v>5</v>
@@ -8020,10 +8107,10 @@
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B474" t="s">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="C474" t="s">
         <v>5</v>
@@ -8031,10 +8118,10 @@
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B475" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="C475" t="s">
         <v>5</v>
@@ -8042,10 +8129,10 @@
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B476" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C476" t="s">
         <v>5</v>
@@ -8053,10 +8140,10 @@
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B477" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="C477" t="s">
         <v>5</v>
@@ -8064,10 +8151,10 @@
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B478" t="s">
-        <v>11</v>
+        <v>231</v>
       </c>
       <c r="C478" t="s">
         <v>5</v>
@@ -8075,10 +8162,10 @@
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B479" t="s">
-        <v>7</v>
+        <v>137</v>
       </c>
       <c r="C479" t="s">
         <v>5</v>
@@ -8086,10 +8173,10 @@
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B480" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C480" t="s">
         <v>5</v>
@@ -8097,10 +8184,10 @@
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B481" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C481" t="s">
         <v>5</v>
@@ -8108,10 +8195,10 @@
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B482" t="s">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c r="C482" t="s">
         <v>5</v>
@@ -8119,10 +8206,10 @@
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B483" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C483" t="s">
         <v>5</v>
@@ -8130,10 +8217,10 @@
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B484" t="s">
-        <v>7</v>
+        <v>401</v>
       </c>
       <c r="C484" t="s">
         <v>5</v>
@@ -8141,10 +8228,10 @@
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B485" t="s">
-        <v>63</v>
+        <v>401</v>
       </c>
       <c r="C485" t="s">
         <v>5</v>
@@ -8152,10 +8239,10 @@
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B486" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C486" t="s">
         <v>5</v>
@@ -8163,7 +8250,7 @@
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B487" t="s">
         <v>7</v>
@@ -8174,10 +8261,10 @@
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B488" t="s">
-        <v>58</v>
+        <v>491</v>
       </c>
       <c r="C488" t="s">
         <v>5</v>
@@ -8185,10 +8272,10 @@
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B489" t="s">
-        <v>4</v>
+        <v>261</v>
       </c>
       <c r="C489" t="s">
         <v>5</v>
@@ -8196,10 +8283,10 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B490" t="s">
-        <v>90</v>
+        <v>269</v>
       </c>
       <c r="C490" t="s">
         <v>5</v>
@@ -8207,10 +8294,10 @@
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B491" t="s">
-        <v>158</v>
+        <v>274</v>
       </c>
       <c r="C491" t="s">
         <v>5</v>
@@ -8218,10 +8305,10 @@
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B492" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C492" t="s">
         <v>5</v>
@@ -8229,10 +8316,10 @@
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B493" t="s">
-        <v>13</v>
+        <v>285</v>
       </c>
       <c r="C493" t="s">
         <v>5</v>
@@ -8240,10 +8327,10 @@
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B494" t="s">
-        <v>63</v>
+        <v>267</v>
       </c>
       <c r="C494" t="s">
         <v>5</v>
@@ -8251,10 +8338,10 @@
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B495" t="s">
-        <v>63</v>
+        <v>261</v>
       </c>
       <c r="C495" t="s">
         <v>5</v>
@@ -8262,10 +8349,10 @@
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B496" t="s">
-        <v>166</v>
+        <v>588</v>
       </c>
       <c r="C496" t="s">
         <v>5</v>
@@ -8273,10 +8360,10 @@
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B497" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C497" t="s">
         <v>5</v>
@@ -8284,10 +8371,10 @@
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B498" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C498" t="s">
         <v>5</v>
@@ -8295,10 +8382,10 @@
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B499" t="s">
-        <v>158</v>
+        <v>32</v>
       </c>
       <c r="C499" t="s">
         <v>5</v>
@@ -8306,10 +8393,10 @@
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B500" t="s">
-        <v>158</v>
+        <v>269</v>
       </c>
       <c r="C500" t="s">
         <v>5</v>
@@ -8317,10 +8404,10 @@
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B501" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="C501" t="s">
         <v>5</v>
@@ -8328,10 +8415,10 @@
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B502" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C502" t="s">
         <v>5</v>
@@ -8339,10 +8426,10 @@
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B503" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="C503" t="s">
         <v>5</v>
@@ -8350,10 +8437,10 @@
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B504" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C504" t="s">
         <v>5</v>
@@ -8361,10 +8448,10 @@
     </row>
     <row r="505">
       <c r="A505" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B505" t="s">
-        <v>71</v>
+        <v>214</v>
       </c>
       <c r="C505" t="s">
         <v>5</v>
@@ -8372,10 +8459,10 @@
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B506" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C506" t="s">
         <v>5</v>
@@ -8383,10 +8470,10 @@
     </row>
     <row r="507">
       <c r="A507" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B507" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C507" t="s">
         <v>5</v>
@@ -8394,10 +8481,10 @@
     </row>
     <row r="508">
       <c r="A508" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B508" t="s">
-        <v>184</v>
+        <v>61</v>
       </c>
       <c r="C508" t="s">
         <v>5</v>
@@ -8405,10 +8492,10 @@
     </row>
     <row r="509">
       <c r="A509" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B509" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="C509" t="s">
         <v>5</v>
@@ -8416,10 +8503,10 @@
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="B510" t="s">
-        <v>211</v>
+        <v>66</v>
       </c>
       <c r="C510" t="s">
         <v>5</v>
@@ -8427,10 +8514,10 @@
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B511" t="s">
-        <v>453</v>
+        <v>66</v>
       </c>
       <c r="C511" t="s">
         <v>5</v>
@@ -8438,10 +8525,10 @@
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B512" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="C512" t="s">
         <v>5</v>
@@ -8449,10 +8536,10 @@
     </row>
     <row r="513">
       <c r="A513" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="B513" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="C513" t="s">
         <v>5</v>
@@ -8460,10 +8547,10 @@
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B514" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="C514" t="s">
         <v>5</v>
@@ -8471,10 +8558,10 @@
     </row>
     <row r="515">
       <c r="A515" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B515" t="s">
-        <v>184</v>
+        <v>57</v>
       </c>
       <c r="C515" t="s">
         <v>5</v>
@@ -8482,10 +8569,10 @@
     </row>
     <row r="516">
       <c r="A516" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B516" t="s">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="C516" t="s">
         <v>5</v>
@@ -8493,10 +8580,10 @@
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B517" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C517" t="s">
         <v>5</v>
@@ -8504,10 +8591,10 @@
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B518" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="C518" t="s">
         <v>5</v>
@@ -8515,10 +8602,10 @@
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B519" t="s">
-        <v>474</v>
+        <v>206</v>
       </c>
       <c r="C519" t="s">
         <v>5</v>
@@ -8526,10 +8613,10 @@
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B520" t="s">
-        <v>474</v>
+        <v>61</v>
       </c>
       <c r="C520" t="s">
         <v>5</v>
@@ -8537,10 +8624,10 @@
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B521" t="s">
-        <v>474</v>
+        <v>63</v>
       </c>
       <c r="C521" t="s">
         <v>5</v>
@@ -8548,10 +8635,10 @@
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B522" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C522" t="s">
         <v>5</v>
@@ -8559,10 +8646,10 @@
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B523" t="s">
-        <v>366</v>
+        <v>113</v>
       </c>
       <c r="C523" t="s">
         <v>5</v>
@@ -8570,10 +8657,10 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B524" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="C524" t="s">
         <v>5</v>
@@ -8581,10 +8668,10 @@
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B525" t="s">
-        <v>333</v>
+        <v>90</v>
       </c>
       <c r="C525" t="s">
         <v>5</v>
@@ -8592,10 +8679,10 @@
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B526" t="s">
-        <v>211</v>
+        <v>76</v>
       </c>
       <c r="C526" t="s">
         <v>5</v>
@@ -8603,10 +8690,10 @@
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B527" t="s">
-        <v>455</v>
+        <v>206</v>
       </c>
       <c r="C527" t="s">
         <v>5</v>
@@ -8614,10 +8701,10 @@
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B528" t="s">
-        <v>92</v>
+        <v>206</v>
       </c>
       <c r="C528" t="s">
         <v>5</v>
@@ -8625,10 +8712,10 @@
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B529" t="s">
-        <v>458</v>
+        <v>63</v>
       </c>
       <c r="C529" t="s">
         <v>5</v>
@@ -8636,10 +8723,10 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B530" t="s">
-        <v>455</v>
+        <v>137</v>
       </c>
       <c r="C530" t="s">
         <v>5</v>
@@ -8647,10 +8734,10 @@
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B531" t="s">
-        <v>621</v>
+        <v>55</v>
       </c>
       <c r="C531" t="s">
         <v>5</v>
@@ -8658,10 +8745,10 @@
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B532" t="s">
-        <v>219</v>
+        <v>47</v>
       </c>
       <c r="C532" t="s">
         <v>5</v>
@@ -8669,10 +8756,10 @@
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B533" t="s">
-        <v>309</v>
+        <v>120</v>
       </c>
       <c r="C533" t="s">
         <v>5</v>
@@ -8680,10 +8767,10 @@
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B534" t="s">
-        <v>229</v>
+        <v>120</v>
       </c>
       <c r="C534" t="s">
         <v>5</v>
@@ -8691,10 +8778,10 @@
     </row>
     <row r="535">
       <c r="A535" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B535" t="s">
-        <v>211</v>
+        <v>120</v>
       </c>
       <c r="C535" t="s">
         <v>5</v>
@@ -8702,10 +8789,10 @@
     </row>
     <row r="536">
       <c r="A536" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B536" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C536" t="s">
         <v>5</v>
@@ -8713,10 +8800,10 @@
     </row>
     <row r="537">
       <c r="A537" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B537" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="C537" t="s">
         <v>5</v>
@@ -8724,10 +8811,10 @@
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B538" t="s">
-        <v>229</v>
+        <v>51</v>
       </c>
       <c r="C538" t="s">
         <v>5</v>
@@ -8735,10 +8822,10 @@
     </row>
     <row r="539">
       <c r="A539" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B539" t="s">
-        <v>214</v>
+        <v>43</v>
       </c>
       <c r="C539" t="s">
         <v>5</v>
@@ -8746,10 +8833,10 @@
     </row>
     <row r="540">
       <c r="A540" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B540" t="s">
-        <v>250</v>
+        <v>53</v>
       </c>
       <c r="C540" t="s">
         <v>5</v>
@@ -8757,10 +8844,10 @@
     </row>
     <row r="541">
       <c r="A541" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B541" t="s">
-        <v>216</v>
+        <v>137</v>
       </c>
       <c r="C541" t="s">
         <v>5</v>
@@ -8768,10 +8855,10 @@
     </row>
     <row r="542">
       <c r="A542" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B542" t="s">
-        <v>250</v>
+        <v>139</v>
       </c>
       <c r="C542" t="s">
         <v>5</v>
@@ -8779,10 +8866,10 @@
     </row>
     <row r="543">
       <c r="A543" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B543" t="s">
-        <v>328</v>
+        <v>231</v>
       </c>
       <c r="C543" t="s">
         <v>5</v>
@@ -8790,10 +8877,10 @@
     </row>
     <row r="544">
       <c r="A544" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B544" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="C544" t="s">
         <v>5</v>
@@ -8801,10 +8888,10 @@
     </row>
     <row r="545">
       <c r="A545" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B545" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="C545" t="s">
         <v>5</v>
@@ -8812,10 +8899,10 @@
     </row>
     <row r="546">
       <c r="A546" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B546" t="s">
-        <v>169</v>
+        <v>49</v>
       </c>
       <c r="C546" t="s">
         <v>5</v>
@@ -8823,10 +8910,10 @@
     </row>
     <row r="547">
       <c r="A547" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B547" t="s">
-        <v>453</v>
+        <v>4</v>
       </c>
       <c r="C547" t="s">
         <v>5</v>
@@ -8834,10 +8921,10 @@
     </row>
     <row r="548">
       <c r="A548" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B548" t="s">
-        <v>366</v>
+        <v>4</v>
       </c>
       <c r="C548" t="s">
         <v>5</v>
@@ -8845,10 +8932,10 @@
     </row>
     <row r="549">
       <c r="A549" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B549" t="s">
-        <v>366</v>
+        <v>4</v>
       </c>
       <c r="C549" t="s">
         <v>5</v>
@@ -8856,10 +8943,10 @@
     </row>
     <row r="550">
       <c r="A550" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B550" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="C550" t="s">
         <v>5</v>
@@ -8867,10 +8954,10 @@
     </row>
     <row r="551">
       <c r="A551" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B551" t="s">
-        <v>333</v>
+        <v>401</v>
       </c>
       <c r="C551" t="s">
         <v>5</v>
@@ -8878,10 +8965,10 @@
     </row>
     <row r="552">
       <c r="A552" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B552" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C552" t="s">
         <v>5</v>
@@ -8889,10 +8976,10 @@
     </row>
     <row r="553">
       <c r="A553" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B553" t="s">
-        <v>474</v>
+        <v>7</v>
       </c>
       <c r="C553" t="s">
         <v>5</v>
@@ -8900,10 +8987,10 @@
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B554" t="s">
-        <v>211</v>
+        <v>51</v>
       </c>
       <c r="C554" t="s">
         <v>5</v>
@@ -8911,10 +8998,10 @@
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B555" t="s">
-        <v>211</v>
+        <v>34</v>
       </c>
       <c r="C555" t="s">
         <v>5</v>
@@ -8922,10 +9009,10 @@
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B556" t="s">
-        <v>309</v>
+        <v>141</v>
       </c>
       <c r="C556" t="s">
         <v>5</v>
@@ -8933,10 +9020,10 @@
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B557" t="s">
-        <v>307</v>
+        <v>491</v>
       </c>
       <c r="C557" t="s">
         <v>5</v>
@@ -8944,10 +9031,10 @@
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B558" t="s">
-        <v>556</v>
+        <v>34</v>
       </c>
       <c r="C558" t="s">
         <v>5</v>
@@ -8955,10 +9042,10 @@
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B559" t="s">
-        <v>305</v>
+        <v>38</v>
       </c>
       <c r="C559" t="s">
         <v>5</v>
@@ -8966,10 +9053,10 @@
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B560" t="s">
-        <v>319</v>
+        <v>264</v>
       </c>
       <c r="C560" t="s">
         <v>5</v>
@@ -8977,10 +9064,10 @@
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B561" t="s">
-        <v>314</v>
+        <v>23</v>
       </c>
       <c r="C561" t="s">
         <v>5</v>
@@ -8988,10 +9075,10 @@
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B562" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="C562" t="s">
         <v>5</v>
@@ -8999,10 +9086,10 @@
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B563" t="s">
-        <v>244</v>
+        <v>51</v>
       </c>
       <c r="C563" t="s">
         <v>5</v>
@@ -9010,10 +9097,10 @@
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B564" t="s">
-        <v>257</v>
+        <v>51</v>
       </c>
       <c r="C564" t="s">
         <v>5</v>
@@ -9021,10 +9108,10 @@
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B565" t="s">
-        <v>257</v>
+        <v>141</v>
       </c>
       <c r="C565" t="s">
         <v>5</v>
@@ -9032,10 +9119,10 @@
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B566" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="C566" t="s">
         <v>5</v>
@@ -9043,10 +9130,10 @@
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B567" t="s">
-        <v>262</v>
+        <v>36</v>
       </c>
       <c r="C567" t="s">
         <v>5</v>
@@ -9054,10 +9141,10 @@
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B568" t="s">
-        <v>659</v>
+        <v>32</v>
       </c>
       <c r="C568" t="s">
         <v>5</v>
@@ -9065,10 +9152,10 @@
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B569" t="s">
-        <v>659</v>
+        <v>261</v>
       </c>
       <c r="C569" t="s">
         <v>5</v>
@@ -9076,10 +9163,10 @@
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B570" t="s">
-        <v>659</v>
+        <v>32</v>
       </c>
       <c r="C570" t="s">
         <v>5</v>
@@ -9087,10 +9174,10 @@
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B571" t="s">
-        <v>659</v>
+        <v>40</v>
       </c>
       <c r="C571" t="s">
         <v>5</v>
@@ -9098,10 +9185,10 @@
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B572" t="s">
-        <v>664</v>
+        <v>141</v>
       </c>
       <c r="C572" t="s">
         <v>5</v>
@@ -9112,7 +9199,7 @@
         <v>665</v>
       </c>
       <c r="B573" t="s">
-        <v>666</v>
+        <v>49</v>
       </c>
       <c r="C573" t="s">
         <v>5</v>
@@ -9120,10 +9207,10 @@
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B574" t="s">
-        <v>269</v>
+        <v>49</v>
       </c>
       <c r="C574" t="s">
         <v>5</v>
@@ -9131,10 +9218,10 @@
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B575" t="s">
-        <v>659</v>
+        <v>43</v>
       </c>
       <c r="C575" t="s">
         <v>5</v>
@@ -9142,10 +9229,10 @@
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B576" t="s">
-        <v>301</v>
+        <v>401</v>
       </c>
       <c r="C576" t="s">
         <v>5</v>
@@ -9153,10 +9240,10 @@
     </row>
     <row r="577">
       <c r="A577" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B577" t="s">
-        <v>664</v>
+        <v>401</v>
       </c>
       <c r="C577" t="s">
         <v>5</v>
@@ -9164,10 +9251,10 @@
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B578" t="s">
-        <v>285</v>
+        <v>141</v>
       </c>
       <c r="C578" t="s">
         <v>5</v>
@@ -9175,10 +9262,10 @@
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B579" t="s">
-        <v>673</v>
+        <v>7</v>
       </c>
       <c r="C579" t="s">
         <v>5</v>
@@ -9186,10 +9273,10 @@
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B580" t="s">
-        <v>673</v>
+        <v>51</v>
       </c>
       <c r="C580" t="s">
         <v>5</v>
@@ -9197,10 +9284,10 @@
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B581" t="s">
-        <v>274</v>
+        <v>4</v>
       </c>
       <c r="C581" t="s">
         <v>5</v>
@@ -9208,10 +9295,10 @@
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B582" t="s">
-        <v>276</v>
+        <v>51</v>
       </c>
       <c r="C582" t="s">
         <v>5</v>
@@ -9219,10 +9306,10 @@
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B583" t="s">
-        <v>285</v>
+        <v>51</v>
       </c>
       <c r="C583" t="s">
         <v>5</v>
@@ -9230,10 +9317,10 @@
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B584" t="s">
-        <v>297</v>
+        <v>23</v>
       </c>
       <c r="C584" t="s">
         <v>5</v>
@@ -9241,10 +9328,10 @@
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B585" t="s">
-        <v>680</v>
+        <v>30</v>
       </c>
       <c r="C585" t="s">
         <v>5</v>
@@ -9252,10 +9339,10 @@
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B586" t="s">
-        <v>680</v>
+        <v>588</v>
       </c>
       <c r="C586" t="s">
         <v>5</v>
@@ -9263,10 +9350,10 @@
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B587" t="s">
-        <v>683</v>
+        <v>25</v>
       </c>
       <c r="C587" t="s">
         <v>5</v>
@@ -9274,10 +9361,10 @@
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B588" t="s">
-        <v>685</v>
+        <v>14</v>
       </c>
       <c r="C588" t="s">
         <v>5</v>
@@ -9285,10 +9372,10 @@
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="B589" t="s">
-        <v>687</v>
+        <v>352</v>
       </c>
       <c r="C589" t="s">
         <v>5</v>
@@ -9296,10 +9383,10 @@
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="B590" t="s">
-        <v>689</v>
+        <v>360</v>
       </c>
       <c r="C590" t="s">
         <v>5</v>
@@ -9307,10 +9394,10 @@
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="B591" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="C591" t="s">
         <v>5</v>
@@ -9318,10 +9405,10 @@
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="B592" t="s">
-        <v>692</v>
+        <v>299</v>
       </c>
       <c r="C592" t="s">
         <v>5</v>
@@ -9329,10 +9416,10 @@
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="B593" t="s">
-        <v>694</v>
+        <v>299</v>
       </c>
       <c r="C593" t="s">
         <v>5</v>
@@ -9340,10 +9427,10 @@
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="B594" t="s">
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="C594" t="s">
         <v>5</v>
@@ -9351,10 +9438,10 @@
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="B595" t="s">
-        <v>697</v>
+        <v>304</v>
       </c>
       <c r="C595" t="s">
         <v>5</v>
@@ -9362,10 +9449,10 @@
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="B596" t="s">
-        <v>276</v>
+        <v>689</v>
       </c>
       <c r="C596" t="s">
         <v>5</v>
@@ -9373,10 +9460,10 @@
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="B597" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="C597" t="s">
         <v>5</v>
@@ -9384,10 +9471,10 @@
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="B598" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="C598" t="s">
         <v>5</v>
@@ -9395,10 +9482,10 @@
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="B599" t="s">
-        <v>299</v>
+        <v>689</v>
       </c>
       <c r="C599" t="s">
         <v>5</v>
@@ -9406,10 +9493,10 @@
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="B600" t="s">
-        <v>299</v>
+        <v>694</v>
       </c>
       <c r="C600" t="s">
         <v>5</v>
@@ -9417,10 +9504,10 @@
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="B601" t="s">
-        <v>700</v>
+        <v>16</v>
       </c>
       <c r="C601" t="s">
         <v>5</v>
@@ -9428,10 +9515,10 @@
     </row>
     <row r="602">
       <c r="A602" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="B602" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="C602" t="s">
         <v>5</v>
@@ -9439,10 +9526,10 @@
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="B603" t="s">
-        <v>290</v>
+        <v>689</v>
       </c>
       <c r="C603" t="s">
         <v>5</v>
@@ -9450,10 +9537,10 @@
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="B604" t="s">
-        <v>709</v>
+        <v>343</v>
       </c>
       <c r="C604" t="s">
         <v>5</v>
@@ -9461,10 +9548,10 @@
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="B605" t="s">
-        <v>711</v>
+        <v>694</v>
       </c>
       <c r="C605" t="s">
         <v>5</v>
@@ -9472,10 +9559,10 @@
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="B606" t="s">
-        <v>713</v>
+        <v>327</v>
       </c>
       <c r="C606" t="s">
         <v>5</v>
@@ -9483,10 +9570,10 @@
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="B607" t="s">
-        <v>274</v>
+        <v>702</v>
       </c>
       <c r="C607" t="s">
         <v>5</v>
@@ -9494,10 +9581,10 @@
     </row>
     <row r="608">
       <c r="A608" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="B608" t="s">
-        <v>299</v>
+        <v>702</v>
       </c>
       <c r="C608" t="s">
         <v>5</v>
@@ -9505,10 +9592,10 @@
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="B609" t="s">
-        <v>717</v>
+        <v>316</v>
       </c>
       <c r="C609" t="s">
         <v>5</v>
@@ -9516,10 +9603,10 @@
     </row>
     <row r="610">
       <c r="A610" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="B610" t="s">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="C610" t="s">
         <v>5</v>
@@ -9527,10 +9614,10 @@
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="B611" t="s">
-        <v>700</v>
+        <v>327</v>
       </c>
       <c r="C611" t="s">
         <v>5</v>
@@ -9538,10 +9625,10 @@
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="B612" t="s">
-        <v>267</v>
+        <v>339</v>
       </c>
       <c r="C612" t="s">
         <v>5</v>
@@ -9549,10 +9636,10 @@
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="B613" t="s">
-        <v>299</v>
+        <v>709</v>
       </c>
       <c r="C613" t="s">
         <v>5</v>
@@ -9560,10 +9647,10 @@
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="B614" t="s">
-        <v>269</v>
+        <v>709</v>
       </c>
       <c r="C614" t="s">
         <v>5</v>
@@ -9571,10 +9658,10 @@
     </row>
     <row r="615">
       <c r="A615" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="B615" t="s">
-        <v>257</v>
+        <v>712</v>
       </c>
       <c r="C615" t="s">
         <v>5</v>
@@ -9582,10 +9669,10 @@
     </row>
     <row r="616">
       <c r="A616" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="B616" t="s">
-        <v>264</v>
+        <v>714</v>
       </c>
       <c r="C616" t="s">
         <v>5</v>
@@ -9593,10 +9680,10 @@
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="B617" t="s">
-        <v>314</v>
+        <v>716</v>
       </c>
       <c r="C617" t="s">
         <v>5</v>
@@ -9604,10 +9691,10 @@
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="B618" t="s">
-        <v>237</v>
+        <v>718</v>
       </c>
       <c r="C618" t="s">
         <v>5</v>
@@ -9615,10 +9702,10 @@
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="B619" t="s">
-        <v>237</v>
+        <v>320</v>
       </c>
       <c r="C619" t="s">
         <v>5</v>
@@ -9626,10 +9713,10 @@
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="B620" t="s">
-        <v>556</v>
+        <v>721</v>
       </c>
       <c r="C620" t="s">
         <v>5</v>
@@ -9637,10 +9724,10 @@
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="B621" t="s">
-        <v>237</v>
+        <v>723</v>
       </c>
       <c r="C621" t="s">
         <v>5</v>
@@ -9648,10 +9735,10 @@
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="B622" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="C622" t="s">
         <v>5</v>
@@ -9659,10 +9746,10 @@
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="B623" t="s">
-        <v>247</v>
+        <v>726</v>
       </c>
       <c r="C623" t="s">
         <v>5</v>
@@ -9670,10 +9757,10 @@
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B624" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="C624" t="s">
         <v>5</v>
@@ -9681,10 +9768,10 @@
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="B625" t="s">
-        <v>240</v>
+        <v>729</v>
       </c>
       <c r="C625" t="s">
         <v>5</v>
@@ -9692,10 +9779,10 @@
     </row>
     <row r="626">
       <c r="A626" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B626" t="s">
-        <v>219</v>
+        <v>731</v>
       </c>
       <c r="C626" t="s">
         <v>5</v>
@@ -9703,10 +9790,10 @@
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B627" t="s">
-        <v>226</v>
+        <v>341</v>
       </c>
       <c r="C627" t="s">
         <v>5</v>
@@ -9714,10 +9801,10 @@
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B628" t="s">
-        <v>621</v>
+        <v>341</v>
       </c>
       <c r="C628" t="s">
         <v>5</v>
@@ -9725,10 +9812,10 @@
     </row>
     <row r="629">
       <c r="A629" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B629" t="s">
-        <v>219</v>
+        <v>729</v>
       </c>
       <c r="C629" t="s">
         <v>5</v>
@@ -9736,10 +9823,10 @@
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B630" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="C630" t="s">
         <v>5</v>
@@ -9747,10 +9834,10 @@
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B631" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="C631" t="s">
         <v>5</v>
@@ -9758,10 +9845,10 @@
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="B632" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C632" t="s">
         <v>5</v>
@@ -9769,10 +9856,10 @@
     </row>
     <row r="633">
       <c r="A633" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B633" t="s">
-        <v>314</v>
+        <v>740</v>
       </c>
       <c r="C633" t="s">
         <v>5</v>
@@ -9780,10 +9867,10 @@
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B634" t="s">
-        <v>312</v>
+        <v>742</v>
       </c>
       <c r="C634" t="s">
         <v>5</v>
@@ -9791,10 +9878,10 @@
     </row>
     <row r="635">
       <c r="A635" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B635" t="s">
-        <v>741</v>
+        <v>316</v>
       </c>
       <c r="C635" t="s">
         <v>5</v>
@@ -9802,10 +9889,10 @@
     </row>
     <row r="636">
       <c r="A636" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B636" t="s">
-        <v>264</v>
+        <v>341</v>
       </c>
       <c r="C636" t="s">
         <v>5</v>
@@ -9813,10 +9900,10 @@
     </row>
     <row r="637">
       <c r="A637" t="s">
+        <v>745</v>
+      </c>
+      <c r="B637" t="s">
         <v>746</v>
-      </c>
-      <c r="B637" t="s">
-        <v>262</v>
       </c>
       <c r="C637" t="s">
         <v>5</v>
@@ -9827,7 +9914,7 @@
         <v>747</v>
       </c>
       <c r="B638" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C638" t="s">
         <v>5</v>
@@ -9838,7 +9925,7 @@
         <v>748</v>
       </c>
       <c r="B639" t="s">
-        <v>309</v>
+        <v>729</v>
       </c>
       <c r="C639" t="s">
         <v>5</v>
@@ -9849,7 +9936,7 @@
         <v>749</v>
       </c>
       <c r="B640" t="s">
-        <v>216</v>
+        <v>309</v>
       </c>
       <c r="C640" t="s">
         <v>5</v>
@@ -9860,7 +9947,7 @@
         <v>750</v>
       </c>
       <c r="B641" t="s">
-        <v>216</v>
+        <v>341</v>
       </c>
       <c r="C641" t="s">
         <v>5</v>
@@ -9871,7 +9958,7 @@
         <v>751</v>
       </c>
       <c r="B642" t="s">
-        <v>216</v>
+        <v>311</v>
       </c>
       <c r="C642" t="s">
         <v>5</v>
@@ -9882,7 +9969,7 @@
         <v>752</v>
       </c>
       <c r="B643" t="s">
-        <v>458</v>
+        <v>299</v>
       </c>
       <c r="C643" t="s">
         <v>5</v>
@@ -9893,7 +9980,7 @@
         <v>753</v>
       </c>
       <c r="B644" t="s">
-        <v>226</v>
+        <v>306</v>
       </c>
       <c r="C644" t="s">
         <v>5</v>
@@ -9904,7 +9991,7 @@
         <v>754</v>
       </c>
       <c r="B645" t="s">
-        <v>222</v>
+        <v>352</v>
       </c>
       <c r="C645" t="s">
         <v>5</v>
@@ -9915,7 +10002,7 @@
         <v>755</v>
       </c>
       <c r="B646" t="s">
-        <v>214</v>
+        <v>282</v>
       </c>
       <c r="C646" t="s">
         <v>5</v>
@@ -9926,7 +10013,7 @@
         <v>756</v>
       </c>
       <c r="B647" t="s">
-        <v>222</v>
+        <v>282</v>
       </c>
       <c r="C647" t="s">
         <v>5</v>
@@ -9937,7 +10024,7 @@
         <v>757</v>
       </c>
       <c r="B648" t="s">
-        <v>211</v>
+        <v>588</v>
       </c>
       <c r="C648" t="s">
         <v>5</v>
@@ -9948,7 +10035,7 @@
         <v>758</v>
       </c>
       <c r="B649" t="s">
-        <v>90</v>
+        <v>282</v>
       </c>
       <c r="C649" t="s">
         <v>5</v>
@@ -9959,7 +10046,7 @@
         <v>759</v>
       </c>
       <c r="B650" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="C650" t="s">
         <v>5</v>
@@ -9970,7 +10057,7 @@
         <v>760</v>
       </c>
       <c r="B651" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C651" t="s">
         <v>5</v>
@@ -9981,7 +10068,7 @@
         <v>761</v>
       </c>
       <c r="B652" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="C652" t="s">
         <v>5</v>
@@ -9992,7 +10079,7 @@
         <v>762</v>
       </c>
       <c r="B653" t="s">
-        <v>453</v>
+        <v>285</v>
       </c>
       <c r="C653" t="s">
         <v>5</v>
@@ -10003,7 +10090,7 @@
         <v>763</v>
       </c>
       <c r="B654" t="s">
-        <v>474</v>
+        <v>264</v>
       </c>
       <c r="C654" t="s">
         <v>5</v>
@@ -10014,7 +10101,7 @@
         <v>764</v>
       </c>
       <c r="B655" t="s">
-        <v>333</v>
+        <v>271</v>
       </c>
       <c r="C655" t="s">
         <v>5</v>
@@ -10025,7 +10112,7 @@
         <v>765</v>
       </c>
       <c r="B656" t="s">
-        <v>333</v>
+        <v>38</v>
       </c>
       <c r="C656" t="s">
         <v>5</v>
@@ -10036,7 +10123,7 @@
         <v>766</v>
       </c>
       <c r="B657" t="s">
-        <v>184</v>
+        <v>264</v>
       </c>
       <c r="C657" t="s">
         <v>5</v>
@@ -10047,7 +10134,7 @@
         <v>767</v>
       </c>
       <c r="B658" t="s">
-        <v>96</v>
+        <v>352</v>
       </c>
       <c r="C658" t="s">
         <v>5</v>
@@ -10058,7 +10145,7 @@
         <v>768</v>
       </c>
       <c r="B659" t="s">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="C659" t="s">
         <v>5</v>
@@ -10069,7 +10156,7 @@
         <v>769</v>
       </c>
       <c r="B660" t="s">
-        <v>69</v>
+        <v>770</v>
       </c>
       <c r="C660" t="s">
         <v>5</v>
@@ -10077,10 +10164,10 @@
     </row>
     <row r="661">
       <c r="A661" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B661" t="s">
-        <v>4</v>
+        <v>352</v>
       </c>
       <c r="C661" t="s">
         <v>5</v>
@@ -10088,10 +10175,10 @@
     </row>
     <row r="662">
       <c r="A662" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B662" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="C662" t="s">
         <v>5</v>
@@ -10099,10 +10186,10 @@
     </row>
     <row r="663">
       <c r="A663" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B663" t="s">
-        <v>333</v>
+        <v>770</v>
       </c>
       <c r="C663" t="s">
         <v>5</v>
@@ -10110,10 +10197,10 @@
     </row>
     <row r="664">
       <c r="A664" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B664" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="C664" t="s">
         <v>5</v>
@@ -10121,10 +10208,10 @@
     </row>
     <row r="665">
       <c r="A665" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B665" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="C665" t="s">
         <v>5</v>
@@ -10132,10 +10219,10 @@
     </row>
     <row r="666">
       <c r="A666" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B666" t="s">
-        <v>216</v>
+        <v>360</v>
       </c>
       <c r="C666" t="s">
         <v>5</v>
@@ -10143,10 +10230,10 @@
     </row>
     <row r="667">
       <c r="A667" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B667" t="s">
-        <v>219</v>
+        <v>23</v>
       </c>
       <c r="C667" t="s">
         <v>5</v>
@@ -10154,10 +10241,10 @@
     </row>
     <row r="668">
       <c r="A668" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B668" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="C668" t="s">
         <v>5</v>
@@ -10165,10 +10252,10 @@
     </row>
     <row r="669">
       <c r="A669" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B669" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="C669" t="s">
         <v>5</v>
@@ -10176,10 +10263,10 @@
     </row>
     <row r="670">
       <c r="A670" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B670" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="C670" t="s">
         <v>5</v>
@@ -10187,10 +10274,10 @@
     </row>
     <row r="671">
       <c r="A671" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B671" t="s">
-        <v>214</v>
+        <v>491</v>
       </c>
       <c r="C671" t="s">
         <v>5</v>
@@ -10198,10 +10285,10 @@
     </row>
     <row r="672">
       <c r="A672" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B672" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="C672" t="s">
         <v>5</v>
@@ -10209,10 +10296,10 @@
     </row>
     <row r="673">
       <c r="A673" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B673" t="s">
-        <v>556</v>
+        <v>267</v>
       </c>
       <c r="C673" t="s">
         <v>5</v>
@@ -10220,10 +10307,10 @@
     </row>
     <row r="674">
       <c r="A674" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B674" t="s">
-        <v>558</v>
+        <v>36</v>
       </c>
       <c r="C674" t="s">
         <v>5</v>
@@ -10231,10 +10318,10 @@
     </row>
     <row r="675">
       <c r="A675" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B675" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="C675" t="s">
         <v>5</v>
@@ -10242,10 +10329,10 @@
     </row>
     <row r="676">
       <c r="A676" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B676" t="s">
-        <v>309</v>
+        <v>51</v>
       </c>
       <c r="C676" t="s">
         <v>5</v>
@@ -10253,10 +10340,10 @@
     </row>
     <row r="677">
       <c r="A677" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B677" t="s">
-        <v>216</v>
+        <v>139</v>
       </c>
       <c r="C677" t="s">
         <v>5</v>
@@ -10264,10 +10351,10 @@
     </row>
     <row r="678">
       <c r="A678" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B678" t="s">
-        <v>226</v>
+        <v>120</v>
       </c>
       <c r="C678" t="s">
         <v>5</v>
@@ -10275,10 +10362,10 @@
     </row>
     <row r="679">
       <c r="A679" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B679" t="s">
-        <v>224</v>
+        <v>139</v>
       </c>
       <c r="C679" t="s">
         <v>5</v>
@@ -10286,10 +10373,10 @@
     </row>
     <row r="680">
       <c r="A680" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B680" t="s">
-        <v>366</v>
+        <v>53</v>
       </c>
       <c r="C680" t="s">
         <v>5</v>
@@ -10297,10 +10384,10 @@
     </row>
     <row r="681">
       <c r="A681" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B681" t="s">
-        <v>229</v>
+        <v>43</v>
       </c>
       <c r="C681" t="s">
         <v>5</v>
@@ -10308,10 +10395,10 @@
     </row>
     <row r="682">
       <c r="A682" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B682" t="s">
-        <v>229</v>
+        <v>4</v>
       </c>
       <c r="C682" t="s">
         <v>5</v>
@@ -10319,10 +10406,10 @@
     </row>
     <row r="683">
       <c r="A683" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B683" t="s">
-        <v>214</v>
+        <v>7</v>
       </c>
       <c r="C683" t="s">
         <v>5</v>
@@ -10330,10 +10417,10 @@
     </row>
     <row r="684">
       <c r="A684" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B684" t="s">
-        <v>216</v>
+        <v>7</v>
       </c>
       <c r="C684" t="s">
         <v>5</v>
@@ -10341,10 +10428,10 @@
     </row>
     <row r="685">
       <c r="A685" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B685" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C685" t="s">
         <v>5</v>
@@ -10352,10 +10439,10 @@
     </row>
     <row r="686">
       <c r="A686" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B686" t="s">
-        <v>556</v>
+        <v>53</v>
       </c>
       <c r="C686" t="s">
         <v>5</v>
@@ -10363,10 +10450,10 @@
     </row>
     <row r="687">
       <c r="A687" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B687" t="s">
-        <v>216</v>
+        <v>55</v>
       </c>
       <c r="C687" t="s">
         <v>5</v>
@@ -10374,10 +10461,10 @@
     </row>
     <row r="688">
       <c r="A688" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B688" t="s">
-        <v>558</v>
+        <v>47</v>
       </c>
       <c r="C688" t="s">
         <v>5</v>
@@ -10385,10 +10472,10 @@
     </row>
     <row r="689">
       <c r="A689" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B689" t="s">
-        <v>558</v>
+        <v>55</v>
       </c>
       <c r="C689" t="s">
         <v>5</v>
@@ -10396,10 +10483,10 @@
     </row>
     <row r="690">
       <c r="A690" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B690" t="s">
-        <v>264</v>
+        <v>139</v>
       </c>
       <c r="C690" t="s">
         <v>5</v>
@@ -10407,10 +10494,10 @@
     </row>
     <row r="691">
       <c r="A691" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B691" t="s">
-        <v>264</v>
+        <v>7</v>
       </c>
       <c r="C691" t="s">
         <v>5</v>
@@ -10418,10 +10505,10 @@
     </row>
     <row r="692">
       <c r="A692" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B692" t="s">
-        <v>312</v>
+        <v>40</v>
       </c>
       <c r="C692" t="s">
         <v>5</v>
@@ -10429,10 +10516,10 @@
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B693" t="s">
-        <v>659</v>
+        <v>261</v>
       </c>
       <c r="C693" t="s">
         <v>5</v>
@@ -10440,10 +10527,10 @@
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B694" t="s">
-        <v>659</v>
+        <v>261</v>
       </c>
       <c r="C694" t="s">
         <v>5</v>
@@ -10451,10 +10538,10 @@
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B695" t="s">
-        <v>664</v>
+        <v>264</v>
       </c>
       <c r="C695" t="s">
         <v>5</v>
@@ -10462,10 +10549,10 @@
     </row>
     <row r="696">
       <c r="A696" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B696" t="s">
-        <v>666</v>
+        <v>269</v>
       </c>
       <c r="C696" t="s">
         <v>5</v>
@@ -10473,10 +10560,10 @@
     </row>
     <row r="697">
       <c r="A697" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B697" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C697" t="s">
         <v>5</v>
@@ -10484,10 +10571,10 @@
     </row>
     <row r="698">
       <c r="A698" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B698" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C698" t="s">
         <v>5</v>
@@ -10495,10 +10582,10 @@
     </row>
     <row r="699">
       <c r="A699" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B699" t="s">
-        <v>741</v>
+        <v>36</v>
       </c>
       <c r="C699" t="s">
         <v>5</v>
@@ -10506,10 +10593,10 @@
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B700" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="C700" t="s">
         <v>5</v>
@@ -10517,10 +10604,10 @@
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B701" t="s">
-        <v>269</v>
+        <v>588</v>
       </c>
       <c r="C701" t="s">
         <v>5</v>
@@ -10528,10 +10615,10 @@
     </row>
     <row r="702">
       <c r="A702" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B702" t="s">
-        <v>301</v>
+        <v>27</v>
       </c>
       <c r="C702" t="s">
         <v>5</v>
@@ -10539,10 +10626,10 @@
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B703" t="s">
-        <v>301</v>
+        <v>23</v>
       </c>
       <c r="C703" t="s">
         <v>5</v>
@@ -10550,10 +10637,10 @@
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B704" t="s">
-        <v>264</v>
+        <v>23</v>
       </c>
       <c r="C704" t="s">
         <v>5</v>
@@ -10561,10 +10648,10 @@
     </row>
     <row r="705">
       <c r="A705" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B705" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C705" t="s">
         <v>5</v>
@@ -10572,10 +10659,10 @@
     </row>
     <row r="706">
       <c r="A706" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B706" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C706" t="s">
         <v>5</v>
@@ -10583,10 +10670,10 @@
     </row>
     <row r="707">
       <c r="A707" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B707" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="C707" t="s">
         <v>5</v>
@@ -10594,10 +10681,10 @@
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B708" t="s">
-        <v>301</v>
+        <v>401</v>
       </c>
       <c r="C708" t="s">
         <v>5</v>
@@ -10605,10 +10692,10 @@
     </row>
     <row r="709">
       <c r="A709" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B709" t="s">
-        <v>819</v>
+        <v>274</v>
       </c>
       <c r="C709" t="s">
         <v>5</v>
@@ -10619,7 +10706,7 @@
         <v>820</v>
       </c>
       <c r="B710" t="s">
-        <v>666</v>
+        <v>274</v>
       </c>
       <c r="C710" t="s">
         <v>5</v>
@@ -10630,7 +10717,7 @@
         <v>821</v>
       </c>
       <c r="B711" t="s">
-        <v>666</v>
+        <v>36</v>
       </c>
       <c r="C711" t="s">
         <v>5</v>
@@ -10641,7 +10728,7 @@
         <v>822</v>
       </c>
       <c r="B712" t="s">
-        <v>823</v>
+        <v>261</v>
       </c>
       <c r="C712" t="s">
         <v>5</v>
@@ -10649,12 +10736,320 @@
     </row>
     <row r="713">
       <c r="A713" t="s">
+        <v>823</v>
+      </c>
+      <c r="B713" t="s">
+        <v>261</v>
+      </c>
+      <c r="C713" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="s">
         <v>824</v>
       </c>
-      <c r="B713" t="s">
-        <v>664</v>
-      </c>
-      <c r="C713" t="s">
+      <c r="B714" t="s">
+        <v>588</v>
+      </c>
+      <c r="C714" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="s">
+        <v>825</v>
+      </c>
+      <c r="B715" t="s">
+        <v>261</v>
+      </c>
+      <c r="C715" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="s">
+        <v>826</v>
+      </c>
+      <c r="B716" t="s">
+        <v>27</v>
+      </c>
+      <c r="C716" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="s">
+        <v>827</v>
+      </c>
+      <c r="B717" t="s">
+        <v>27</v>
+      </c>
+      <c r="C717" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="s">
+        <v>828</v>
+      </c>
+      <c r="B718" t="s">
+        <v>306</v>
+      </c>
+      <c r="C718" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="s">
+        <v>829</v>
+      </c>
+      <c r="B719" t="s">
+        <v>306</v>
+      </c>
+      <c r="C719" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="s">
+        <v>830</v>
+      </c>
+      <c r="B720" t="s">
+        <v>11</v>
+      </c>
+      <c r="C720" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="s">
+        <v>831</v>
+      </c>
+      <c r="B721" t="s">
+        <v>689</v>
+      </c>
+      <c r="C721" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="s">
+        <v>832</v>
+      </c>
+      <c r="B722" t="s">
+        <v>689</v>
+      </c>
+      <c r="C722" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="s">
+        <v>833</v>
+      </c>
+      <c r="B723" t="s">
+        <v>694</v>
+      </c>
+      <c r="C723" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="s">
+        <v>834</v>
+      </c>
+      <c r="B724" t="s">
+        <v>16</v>
+      </c>
+      <c r="C724" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="s">
+        <v>835</v>
+      </c>
+      <c r="B725" t="s">
+        <v>306</v>
+      </c>
+      <c r="C725" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="s">
+        <v>836</v>
+      </c>
+      <c r="B726" t="s">
+        <v>306</v>
+      </c>
+      <c r="C726" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="s">
+        <v>837</v>
+      </c>
+      <c r="B727" t="s">
+        <v>770</v>
+      </c>
+      <c r="C727" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="s">
+        <v>838</v>
+      </c>
+      <c r="B728" t="s">
+        <v>311</v>
+      </c>
+      <c r="C728" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="s">
+        <v>839</v>
+      </c>
+      <c r="B729" t="s">
+        <v>311</v>
+      </c>
+      <c r="C729" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="s">
+        <v>840</v>
+      </c>
+      <c r="B730" t="s">
+        <v>343</v>
+      </c>
+      <c r="C730" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="s">
+        <v>841</v>
+      </c>
+      <c r="B731" t="s">
+        <v>343</v>
+      </c>
+      <c r="C731" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="s">
+        <v>842</v>
+      </c>
+      <c r="B732" t="s">
+        <v>306</v>
+      </c>
+      <c r="C732" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="s">
+        <v>843</v>
+      </c>
+      <c r="B733" t="s">
+        <v>302</v>
+      </c>
+      <c r="C733" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="s">
+        <v>844</v>
+      </c>
+      <c r="B734" t="s">
+        <v>306</v>
+      </c>
+      <c r="C734" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="s">
+        <v>845</v>
+      </c>
+      <c r="B735" t="s">
+        <v>343</v>
+      </c>
+      <c r="C735" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="s">
+        <v>846</v>
+      </c>
+      <c r="B736" t="s">
+        <v>343</v>
+      </c>
+      <c r="C736" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="s">
+        <v>847</v>
+      </c>
+      <c r="B737" t="s">
+        <v>848</v>
+      </c>
+      <c r="C737" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="s">
+        <v>849</v>
+      </c>
+      <c r="B738" t="s">
+        <v>16</v>
+      </c>
+      <c r="C738" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="s">
+        <v>850</v>
+      </c>
+      <c r="B739" t="s">
+        <v>16</v>
+      </c>
+      <c r="C739" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="s">
+        <v>851</v>
+      </c>
+      <c r="B740" t="s">
+        <v>852</v>
+      </c>
+      <c r="C740" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="s">
+        <v>853</v>
+      </c>
+      <c r="B741" t="s">
+        <v>694</v>
+      </c>
+      <c r="C741" t="s">
         <v>5</v>
       </c>
     </row>
